--- a/produits/templates-entreprises/automatisation-n8n/gestion_de_stock_auto.xlsx
+++ b/produits/templates-entreprises/automatisation-n8n/gestion_de_stock_auto.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Tableau de bord" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Produits" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Commandes" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Mouvements" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Arrivages" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Mouvements" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="91">
   <si>
     <t xml:space="preserve">Gestion de stock : mode d'emploi</t>
   </si>
@@ -57,6 +58,9 @@
   </si>
   <si>
     <t xml:space="preserve">4. Le seuil d'alerte : en dessous de cette quantité, le produit passe en « À commander ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Facultatif : le fournisseur et son téléphone. La colonne « Quantité à commander » propose de quoi remonter le stock au double du seuil d'alerte.</t>
   </si>
   <si>
     <t xml:space="preserve">Étape 2 : chaque jour (onglet Mouvements)</t>
@@ -96,6 +100,12 @@
   </si>
   <si>
     <t xml:space="preserve">Vous pouvez seulement changer la colonne Statut : Nouvelle, Livrée, Payée ou Annulée. Une commande Annulée ne compte plus dans le stock ni dans les ventes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onglet Arrivages (automatique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaque marchandise reçue et saisie dans le formulaire « Arrivage » arrive ici toute seule et augmente le stock. N'ajoutez pas de ligne à la main.</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de bord du stock</t>
@@ -191,6 +201,15 @@
     <t xml:space="preserve">État</t>
   </si>
   <si>
+    <t xml:space="preserve">Fournisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tél. fournisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantité à commander</t>
+  </si>
+  <si>
     <t xml:space="preserve">P001</t>
   </si>
   <si>
@@ -203,6 +222,9 @@
     <t xml:space="preserve">sac</t>
   </si>
   <si>
+    <t xml:space="preserve">EXEMPLE - Grossiste A</t>
+  </si>
+  <si>
     <t xml:space="preserve">P002</t>
   </si>
   <si>
@@ -210,6 +232,9 @@
   </si>
   <si>
     <t xml:space="preserve">bidon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXEMPLE - Grossiste B</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -243,6 +268,9 @@
   </si>
   <si>
     <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prix d'achat unitaire</t>
   </si>
   <si>
     <t xml:space="preserve">Mouvements de stock</t>
@@ -693,7 +721,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF1E7A46"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
@@ -921,7 +949,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:B32"/>
+  <dimension ref="B1:B35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -983,47 +1011,47 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
+    <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
         <v>19</v>
       </c>
@@ -1033,19 +1061,34 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="6" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="7" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1075,40 +1118,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" s="11" t="n">
         <f aca="true">TODAY()</f>
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">COUNTA(Produits!$A$5:$A$204)</f>
@@ -1127,31 +1170,31 @@
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">COUNTIF(Produits!$M$5:$M$204,"À commander")</f>
         <v>1</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">COUNTIF(Produits!$M$5:$M$204,"Rupture")</f>
         <v>0</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1170,7 +1213,7 @@
         <v>Achats de marchandise ($)</v>
       </c>
       <c r="C13" s="15" t="n">
-        <f aca="false">SUMIFS(Mouvements!$G$5:$G$1004,Mouvements!$A$5:$A$1004,"&gt;="&amp;DATE(YEAR($C$4),MONTH($C$4),1),Mouvements!$A$5:$A$1004,"&lt;"&amp;DATE(YEAR($C$4),MONTH($C$4)+1,1),Mouvements!$D$5:$D$1004,"Entrée")</f>
+        <f aca="false">SUMIFS(Mouvements!$G$5:$G$1004,Mouvements!$A$5:$A$1004,"&gt;="&amp;DATE(YEAR($C$4),MONTH($C$4),1),Mouvements!$A$5:$A$1004,"&lt;"&amp;DATE(YEAR($C$4),MONTH($C$4)+1,1),Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$F$2:$F$5000,Arrivages!$A$2:$A$5000,"&gt;="&amp;DATE(YEAR($C$4),MONTH($C$4),1),Arrivages!$A$2:$A$5000,"&lt;"&amp;DATE(YEAR($C$4),MONTH($C$4)+1,1))</f>
         <v>300</v>
       </c>
     </row>
@@ -1194,12 +1237,12 @@
         <v>45</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">IF(C12=0,"-",C15/C12)</f>
@@ -1208,7 +1251,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">COUNTIFS(Commandes!$A$2:$A$5000,"&gt;="&amp;DATE(YEAR($C$4),MONTH($C$4),1),Commandes!$A$2:$A$5000,"&lt;"&amp;DATE(YEAR($C$4),MONTH($C$4)+1,1),Commandes!$J$2:$J$5000,"&lt;&gt;Annulée")</f>
@@ -1241,7 +1284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M204"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1254,71 +1297,83 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M4" s="21" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>30</v>
@@ -1333,7 +1388,7 @@
         <v>5</v>
       </c>
       <c r="I5" s="24" t="n">
-        <f aca="false">IF($A5="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A5,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A5="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A5,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A5))</f>
         <v>10</v>
       </c>
       <c r="J5" s="24" t="n">
@@ -1352,19 +1407,27 @@
         <f aca="false">IF($A5="","",IF($K5&lt;=0,"Rupture",IF($K5&lt;=N($H5),"À commander","OK")))</f>
         <v>OK</v>
       </c>
+      <c r="N5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="26"/>
+      <c r="P5" s="24" t="n">
+        <f aca="false">IF($A5="","",IF($K5&lt;=N($H5),MAX(0,2*N($H5)-$K5),0))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>12</v>
@@ -1379,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="24" t="n">
-        <f aca="false">IF($A6="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A6,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A6="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A6,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A6))</f>
         <v>0</v>
       </c>
       <c r="J6" s="24" t="n">
@@ -1397,6 +1460,14 @@
       <c r="M6" s="25" t="str">
         <f aca="false">IF($A6="","",IF($K6&lt;=0,"Rupture",IF($K6&lt;=N($H6),"À commander","OK")))</f>
         <v>À commander</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="26"/>
+      <c r="P6" s="24" t="n">
+        <f aca="false">IF($A6="","",IF($K6&lt;=N($H6),MAX(0,2*N($H6)-$K6),0))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1409,7 +1480,7 @@
       <c r="G7" s="27"/>
       <c r="H7" s="27"/>
       <c r="I7" s="24" t="str">
-        <f aca="false">IF($A7="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A7,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A7="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A7,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A7))</f>
         <v/>
       </c>
       <c r="J7" s="24" t="str">
@@ -1426,6 +1497,12 @@
       </c>
       <c r="M7" s="25" t="str">
         <f aca="false">IF($A7="","",IF($K7&lt;=0,"Rupture",IF($K7&lt;=N($H7),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="24" t="str">
+        <f aca="false">IF($A7="","",IF($K7&lt;=N($H7),MAX(0,2*N($H7)-$K7),0))</f>
         <v/>
       </c>
     </row>
@@ -1439,7 +1516,7 @@
       <c r="G8" s="27"/>
       <c r="H8" s="27"/>
       <c r="I8" s="24" t="str">
-        <f aca="false">IF($A8="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A8,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A8="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A8,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A8))</f>
         <v/>
       </c>
       <c r="J8" s="24" t="str">
@@ -1456,6 +1533,12 @@
       </c>
       <c r="M8" s="25" t="str">
         <f aca="false">IF($A8="","",IF($K8&lt;=0,"Rupture",IF($K8&lt;=N($H8),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="24" t="str">
+        <f aca="false">IF($A8="","",IF($K8&lt;=N($H8),MAX(0,2*N($H8)-$K8),0))</f>
         <v/>
       </c>
     </row>
@@ -1469,7 +1552,7 @@
       <c r="G9" s="27"/>
       <c r="H9" s="27"/>
       <c r="I9" s="24" t="str">
-        <f aca="false">IF($A9="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A9,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A9="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A9,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A9))</f>
         <v/>
       </c>
       <c r="J9" s="24" t="str">
@@ -1486,6 +1569,12 @@
       </c>
       <c r="M9" s="25" t="str">
         <f aca="false">IF($A9="","",IF($K9&lt;=0,"Rupture",IF($K9&lt;=N($H9),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="24" t="str">
+        <f aca="false">IF($A9="","",IF($K9&lt;=N($H9),MAX(0,2*N($H9)-$K9),0))</f>
         <v/>
       </c>
     </row>
@@ -1499,7 +1588,7 @@
       <c r="G10" s="27"/>
       <c r="H10" s="27"/>
       <c r="I10" s="24" t="str">
-        <f aca="false">IF($A10="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A10,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A10="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A10,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A10))</f>
         <v/>
       </c>
       <c r="J10" s="24" t="str">
@@ -1516,6 +1605,12 @@
       </c>
       <c r="M10" s="25" t="str">
         <f aca="false">IF($A10="","",IF($K10&lt;=0,"Rupture",IF($K10&lt;=N($H10),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="24" t="str">
+        <f aca="false">IF($A10="","",IF($K10&lt;=N($H10),MAX(0,2*N($H10)-$K10),0))</f>
         <v/>
       </c>
     </row>
@@ -1529,7 +1624,7 @@
       <c r="G11" s="27"/>
       <c r="H11" s="27"/>
       <c r="I11" s="24" t="str">
-        <f aca="false">IF($A11="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A11,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A11="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A11,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A11))</f>
         <v/>
       </c>
       <c r="J11" s="24" t="str">
@@ -1546,6 +1641,12 @@
       </c>
       <c r="M11" s="25" t="str">
         <f aca="false">IF($A11="","",IF($K11&lt;=0,"Rupture",IF($K11&lt;=N($H11),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="24" t="str">
+        <f aca="false">IF($A11="","",IF($K11&lt;=N($H11),MAX(0,2*N($H11)-$K11),0))</f>
         <v/>
       </c>
     </row>
@@ -1559,7 +1660,7 @@
       <c r="G12" s="27"/>
       <c r="H12" s="27"/>
       <c r="I12" s="24" t="str">
-        <f aca="false">IF($A12="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A12,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A12="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A12,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A12))</f>
         <v/>
       </c>
       <c r="J12" s="24" t="str">
@@ -1576,6 +1677,12 @@
       </c>
       <c r="M12" s="25" t="str">
         <f aca="false">IF($A12="","",IF($K12&lt;=0,"Rupture",IF($K12&lt;=N($H12),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="24" t="str">
+        <f aca="false">IF($A12="","",IF($K12&lt;=N($H12),MAX(0,2*N($H12)-$K12),0))</f>
         <v/>
       </c>
     </row>
@@ -1589,7 +1696,7 @@
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
       <c r="I13" s="24" t="str">
-        <f aca="false">IF($A13="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A13,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A13="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A13,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A13))</f>
         <v/>
       </c>
       <c r="J13" s="24" t="str">
@@ -1606,6 +1713,12 @@
       </c>
       <c r="M13" s="25" t="str">
         <f aca="false">IF($A13="","",IF($K13&lt;=0,"Rupture",IF($K13&lt;=N($H13),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="24" t="str">
+        <f aca="false">IF($A13="","",IF($K13&lt;=N($H13),MAX(0,2*N($H13)-$K13),0))</f>
         <v/>
       </c>
     </row>
@@ -1619,7 +1732,7 @@
       <c r="G14" s="27"/>
       <c r="H14" s="27"/>
       <c r="I14" s="24" t="str">
-        <f aca="false">IF($A14="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A14,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A14="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A14,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A14))</f>
         <v/>
       </c>
       <c r="J14" s="24" t="str">
@@ -1636,6 +1749,12 @@
       </c>
       <c r="M14" s="25" t="str">
         <f aca="false">IF($A14="","",IF($K14&lt;=0,"Rupture",IF($K14&lt;=N($H14),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="24" t="str">
+        <f aca="false">IF($A14="","",IF($K14&lt;=N($H14),MAX(0,2*N($H14)-$K14),0))</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1768,7 @@
       <c r="G15" s="27"/>
       <c r="H15" s="27"/>
       <c r="I15" s="24" t="str">
-        <f aca="false">IF($A15="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A15,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A15="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A15,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A15))</f>
         <v/>
       </c>
       <c r="J15" s="24" t="str">
@@ -1666,6 +1785,12 @@
       </c>
       <c r="M15" s="25" t="str">
         <f aca="false">IF($A15="","",IF($K15&lt;=0,"Rupture",IF($K15&lt;=N($H15),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="24" t="str">
+        <f aca="false">IF($A15="","",IF($K15&lt;=N($H15),MAX(0,2*N($H15)-$K15),0))</f>
         <v/>
       </c>
     </row>
@@ -1679,7 +1804,7 @@
       <c r="G16" s="27"/>
       <c r="H16" s="27"/>
       <c r="I16" s="24" t="str">
-        <f aca="false">IF($A16="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A16,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A16="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A16,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A16))</f>
         <v/>
       </c>
       <c r="J16" s="24" t="str">
@@ -1696,6 +1821,12 @@
       </c>
       <c r="M16" s="25" t="str">
         <f aca="false">IF($A16="","",IF($K16&lt;=0,"Rupture",IF($K16&lt;=N($H16),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="24" t="str">
+        <f aca="false">IF($A16="","",IF($K16&lt;=N($H16),MAX(0,2*N($H16)-$K16),0))</f>
         <v/>
       </c>
     </row>
@@ -1709,7 +1840,7 @@
       <c r="G17" s="27"/>
       <c r="H17" s="27"/>
       <c r="I17" s="24" t="str">
-        <f aca="false">IF($A17="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A17,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A17="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A17,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A17))</f>
         <v/>
       </c>
       <c r="J17" s="24" t="str">
@@ -1726,6 +1857,12 @@
       </c>
       <c r="M17" s="25" t="str">
         <f aca="false">IF($A17="","",IF($K17&lt;=0,"Rupture",IF($K17&lt;=N($H17),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="24" t="str">
+        <f aca="false">IF($A17="","",IF($K17&lt;=N($H17),MAX(0,2*N($H17)-$K17),0))</f>
         <v/>
       </c>
     </row>
@@ -1739,7 +1876,7 @@
       <c r="G18" s="27"/>
       <c r="H18" s="27"/>
       <c r="I18" s="24" t="str">
-        <f aca="false">IF($A18="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A18,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A18="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A18,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A18))</f>
         <v/>
       </c>
       <c r="J18" s="24" t="str">
@@ -1756,6 +1893,12 @@
       </c>
       <c r="M18" s="25" t="str">
         <f aca="false">IF($A18="","",IF($K18&lt;=0,"Rupture",IF($K18&lt;=N($H18),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="24" t="str">
+        <f aca="false">IF($A18="","",IF($K18&lt;=N($H18),MAX(0,2*N($H18)-$K18),0))</f>
         <v/>
       </c>
     </row>
@@ -1769,7 +1912,7 @@
       <c r="G19" s="27"/>
       <c r="H19" s="27"/>
       <c r="I19" s="24" t="str">
-        <f aca="false">IF($A19="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A19,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A19="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A19,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A19))</f>
         <v/>
       </c>
       <c r="J19" s="24" t="str">
@@ -1786,6 +1929,12 @@
       </c>
       <c r="M19" s="25" t="str">
         <f aca="false">IF($A19="","",IF($K19&lt;=0,"Rupture",IF($K19&lt;=N($H19),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="24" t="str">
+        <f aca="false">IF($A19="","",IF($K19&lt;=N($H19),MAX(0,2*N($H19)-$K19),0))</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1948,7 @@
       <c r="G20" s="27"/>
       <c r="H20" s="27"/>
       <c r="I20" s="24" t="str">
-        <f aca="false">IF($A20="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A20,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A20="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A20,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A20))</f>
         <v/>
       </c>
       <c r="J20" s="24" t="str">
@@ -1816,6 +1965,12 @@
       </c>
       <c r="M20" s="25" t="str">
         <f aca="false">IF($A20="","",IF($K20&lt;=0,"Rupture",IF($K20&lt;=N($H20),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="24" t="str">
+        <f aca="false">IF($A20="","",IF($K20&lt;=N($H20),MAX(0,2*N($H20)-$K20),0))</f>
         <v/>
       </c>
     </row>
@@ -1829,7 +1984,7 @@
       <c r="G21" s="27"/>
       <c r="H21" s="27"/>
       <c r="I21" s="24" t="str">
-        <f aca="false">IF($A21="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A21,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A21="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A21,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A21))</f>
         <v/>
       </c>
       <c r="J21" s="24" t="str">
@@ -1846,6 +2001,12 @@
       </c>
       <c r="M21" s="25" t="str">
         <f aca="false">IF($A21="","",IF($K21&lt;=0,"Rupture",IF($K21&lt;=N($H21),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="24" t="str">
+        <f aca="false">IF($A21="","",IF($K21&lt;=N($H21),MAX(0,2*N($H21)-$K21),0))</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +2020,7 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="24" t="str">
-        <f aca="false">IF($A22="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A22,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A22="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A22,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A22))</f>
         <v/>
       </c>
       <c r="J22" s="24" t="str">
@@ -1876,6 +2037,12 @@
       </c>
       <c r="M22" s="25" t="str">
         <f aca="false">IF($A22="","",IF($K22&lt;=0,"Rupture",IF($K22&lt;=N($H22),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="24" t="str">
+        <f aca="false">IF($A22="","",IF($K22&lt;=N($H22),MAX(0,2*N($H22)-$K22),0))</f>
         <v/>
       </c>
     </row>
@@ -1889,7 +2056,7 @@
       <c r="G23" s="27"/>
       <c r="H23" s="27"/>
       <c r="I23" s="24" t="str">
-        <f aca="false">IF($A23="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A23,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A23="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A23,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A23))</f>
         <v/>
       </c>
       <c r="J23" s="24" t="str">
@@ -1906,6 +2073,12 @@
       </c>
       <c r="M23" s="25" t="str">
         <f aca="false">IF($A23="","",IF($K23&lt;=0,"Rupture",IF($K23&lt;=N($H23),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="24" t="str">
+        <f aca="false">IF($A23="","",IF($K23&lt;=N($H23),MAX(0,2*N($H23)-$K23),0))</f>
         <v/>
       </c>
     </row>
@@ -1919,7 +2092,7 @@
       <c r="G24" s="27"/>
       <c r="H24" s="27"/>
       <c r="I24" s="24" t="str">
-        <f aca="false">IF($A24="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A24,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A24="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A24,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A24))</f>
         <v/>
       </c>
       <c r="J24" s="24" t="str">
@@ -1936,6 +2109,12 @@
       </c>
       <c r="M24" s="25" t="str">
         <f aca="false">IF($A24="","",IF($K24&lt;=0,"Rupture",IF($K24&lt;=N($H24),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="24" t="str">
+        <f aca="false">IF($A24="","",IF($K24&lt;=N($H24),MAX(0,2*N($H24)-$K24),0))</f>
         <v/>
       </c>
     </row>
@@ -1949,7 +2128,7 @@
       <c r="G25" s="27"/>
       <c r="H25" s="27"/>
       <c r="I25" s="24" t="str">
-        <f aca="false">IF($A25="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A25,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A25="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A25,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A25))</f>
         <v/>
       </c>
       <c r="J25" s="24" t="str">
@@ -1966,6 +2145,12 @@
       </c>
       <c r="M25" s="25" t="str">
         <f aca="false">IF($A25="","",IF($K25&lt;=0,"Rupture",IF($K25&lt;=N($H25),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="24" t="str">
+        <f aca="false">IF($A25="","",IF($K25&lt;=N($H25),MAX(0,2*N($H25)-$K25),0))</f>
         <v/>
       </c>
     </row>
@@ -1979,7 +2164,7 @@
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="24" t="str">
-        <f aca="false">IF($A26="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A26,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A26="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A26,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A26))</f>
         <v/>
       </c>
       <c r="J26" s="24" t="str">
@@ -1996,6 +2181,12 @@
       </c>
       <c r="M26" s="25" t="str">
         <f aca="false">IF($A26="","",IF($K26&lt;=0,"Rupture",IF($K26&lt;=N($H26),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="24" t="str">
+        <f aca="false">IF($A26="","",IF($K26&lt;=N($H26),MAX(0,2*N($H26)-$K26),0))</f>
         <v/>
       </c>
     </row>
@@ -2009,7 +2200,7 @@
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="I27" s="24" t="str">
-        <f aca="false">IF($A27="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A27,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A27="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A27,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A27))</f>
         <v/>
       </c>
       <c r="J27" s="24" t="str">
@@ -2026,6 +2217,12 @@
       </c>
       <c r="M27" s="25" t="str">
         <f aca="false">IF($A27="","",IF($K27&lt;=0,"Rupture",IF($K27&lt;=N($H27),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="24" t="str">
+        <f aca="false">IF($A27="","",IF($K27&lt;=N($H27),MAX(0,2*N($H27)-$K27),0))</f>
         <v/>
       </c>
     </row>
@@ -2039,7 +2236,7 @@
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="I28" s="24" t="str">
-        <f aca="false">IF($A28="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A28,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A28="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A28,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A28))</f>
         <v/>
       </c>
       <c r="J28" s="24" t="str">
@@ -2056,6 +2253,12 @@
       </c>
       <c r="M28" s="25" t="str">
         <f aca="false">IF($A28="","",IF($K28&lt;=0,"Rupture",IF($K28&lt;=N($H28),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="24" t="str">
+        <f aca="false">IF($A28="","",IF($K28&lt;=N($H28),MAX(0,2*N($H28)-$K28),0))</f>
         <v/>
       </c>
     </row>
@@ -2069,7 +2272,7 @@
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="24" t="str">
-        <f aca="false">IF($A29="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A29,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A29="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A29,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A29))</f>
         <v/>
       </c>
       <c r="J29" s="24" t="str">
@@ -2086,6 +2289,12 @@
       </c>
       <c r="M29" s="25" t="str">
         <f aca="false">IF($A29="","",IF($K29&lt;=0,"Rupture",IF($K29&lt;=N($H29),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="24" t="str">
+        <f aca="false">IF($A29="","",IF($K29&lt;=N($H29),MAX(0,2*N($H29)-$K29),0))</f>
         <v/>
       </c>
     </row>
@@ -2099,7 +2308,7 @@
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="I30" s="24" t="str">
-        <f aca="false">IF($A30="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A30,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A30="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A30,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A30))</f>
         <v/>
       </c>
       <c r="J30" s="24" t="str">
@@ -2116,6 +2325,12 @@
       </c>
       <c r="M30" s="25" t="str">
         <f aca="false">IF($A30="","",IF($K30&lt;=0,"Rupture",IF($K30&lt;=N($H30),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="24" t="str">
+        <f aca="false">IF($A30="","",IF($K30&lt;=N($H30),MAX(0,2*N($H30)-$K30),0))</f>
         <v/>
       </c>
     </row>
@@ -2129,7 +2344,7 @@
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="24" t="str">
-        <f aca="false">IF($A31="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A31,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A31="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A31,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A31))</f>
         <v/>
       </c>
       <c r="J31" s="24" t="str">
@@ -2146,6 +2361,12 @@
       </c>
       <c r="M31" s="25" t="str">
         <f aca="false">IF($A31="","",IF($K31&lt;=0,"Rupture",IF($K31&lt;=N($H31),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="24" t="str">
+        <f aca="false">IF($A31="","",IF($K31&lt;=N($H31),MAX(0,2*N($H31)-$K31),0))</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2380,7 @@
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="I32" s="24" t="str">
-        <f aca="false">IF($A32="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A32,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A32="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A32,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A32))</f>
         <v/>
       </c>
       <c r="J32" s="24" t="str">
@@ -2176,6 +2397,12 @@
       </c>
       <c r="M32" s="25" t="str">
         <f aca="false">IF($A32="","",IF($K32&lt;=0,"Rupture",IF($K32&lt;=N($H32),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="24" t="str">
+        <f aca="false">IF($A32="","",IF($K32&lt;=N($H32),MAX(0,2*N($H32)-$K32),0))</f>
         <v/>
       </c>
     </row>
@@ -2189,7 +2416,7 @@
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="24" t="str">
-        <f aca="false">IF($A33="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A33,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A33="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A33,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A33))</f>
         <v/>
       </c>
       <c r="J33" s="24" t="str">
@@ -2206,6 +2433,12 @@
       </c>
       <c r="M33" s="25" t="str">
         <f aca="false">IF($A33="","",IF($K33&lt;=0,"Rupture",IF($K33&lt;=N($H33),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="24" t="str">
+        <f aca="false">IF($A33="","",IF($K33&lt;=N($H33),MAX(0,2*N($H33)-$K33),0))</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2452,7 @@
       <c r="G34" s="27"/>
       <c r="H34" s="27"/>
       <c r="I34" s="24" t="str">
-        <f aca="false">IF($A34="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A34,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A34="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A34,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A34))</f>
         <v/>
       </c>
       <c r="J34" s="24" t="str">
@@ -2236,6 +2469,12 @@
       </c>
       <c r="M34" s="25" t="str">
         <f aca="false">IF($A34="","",IF($K34&lt;=0,"Rupture",IF($K34&lt;=N($H34),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="24" t="str">
+        <f aca="false">IF($A34="","",IF($K34&lt;=N($H34),MAX(0,2*N($H34)-$K34),0))</f>
         <v/>
       </c>
     </row>
@@ -2249,7 +2488,7 @@
       <c r="G35" s="27"/>
       <c r="H35" s="27"/>
       <c r="I35" s="24" t="str">
-        <f aca="false">IF($A35="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A35,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A35="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A35,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A35))</f>
         <v/>
       </c>
       <c r="J35" s="24" t="str">
@@ -2266,6 +2505,12 @@
       </c>
       <c r="M35" s="25" t="str">
         <f aca="false">IF($A35="","",IF($K35&lt;=0,"Rupture",IF($K35&lt;=N($H35),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="24" t="str">
+        <f aca="false">IF($A35="","",IF($K35&lt;=N($H35),MAX(0,2*N($H35)-$K35),0))</f>
         <v/>
       </c>
     </row>
@@ -2279,7 +2524,7 @@
       <c r="G36" s="27"/>
       <c r="H36" s="27"/>
       <c r="I36" s="24" t="str">
-        <f aca="false">IF($A36="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A36,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A36="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A36,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A36))</f>
         <v/>
       </c>
       <c r="J36" s="24" t="str">
@@ -2296,6 +2541,12 @@
       </c>
       <c r="M36" s="25" t="str">
         <f aca="false">IF($A36="","",IF($K36&lt;=0,"Rupture",IF($K36&lt;=N($H36),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="24" t="str">
+        <f aca="false">IF($A36="","",IF($K36&lt;=N($H36),MAX(0,2*N($H36)-$K36),0))</f>
         <v/>
       </c>
     </row>
@@ -2309,7 +2560,7 @@
       <c r="G37" s="27"/>
       <c r="H37" s="27"/>
       <c r="I37" s="24" t="str">
-        <f aca="false">IF($A37="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A37,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A37="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A37,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A37))</f>
         <v/>
       </c>
       <c r="J37" s="24" t="str">
@@ -2326,6 +2577,12 @@
       </c>
       <c r="M37" s="25" t="str">
         <f aca="false">IF($A37="","",IF($K37&lt;=0,"Rupture",IF($K37&lt;=N($H37),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="24" t="str">
+        <f aca="false">IF($A37="","",IF($K37&lt;=N($H37),MAX(0,2*N($H37)-$K37),0))</f>
         <v/>
       </c>
     </row>
@@ -2339,7 +2596,7 @@
       <c r="G38" s="27"/>
       <c r="H38" s="27"/>
       <c r="I38" s="24" t="str">
-        <f aca="false">IF($A38="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A38,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A38="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A38,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A38))</f>
         <v/>
       </c>
       <c r="J38" s="24" t="str">
@@ -2356,6 +2613,12 @@
       </c>
       <c r="M38" s="25" t="str">
         <f aca="false">IF($A38="","",IF($K38&lt;=0,"Rupture",IF($K38&lt;=N($H38),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="24" t="str">
+        <f aca="false">IF($A38="","",IF($K38&lt;=N($H38),MAX(0,2*N($H38)-$K38),0))</f>
         <v/>
       </c>
     </row>
@@ -2369,7 +2632,7 @@
       <c r="G39" s="27"/>
       <c r="H39" s="27"/>
       <c r="I39" s="24" t="str">
-        <f aca="false">IF($A39="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A39,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A39="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A39,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A39))</f>
         <v/>
       </c>
       <c r="J39" s="24" t="str">
@@ -2386,6 +2649,12 @@
       </c>
       <c r="M39" s="25" t="str">
         <f aca="false">IF($A39="","",IF($K39&lt;=0,"Rupture",IF($K39&lt;=N($H39),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="24" t="str">
+        <f aca="false">IF($A39="","",IF($K39&lt;=N($H39),MAX(0,2*N($H39)-$K39),0))</f>
         <v/>
       </c>
     </row>
@@ -2399,7 +2668,7 @@
       <c r="G40" s="27"/>
       <c r="H40" s="27"/>
       <c r="I40" s="24" t="str">
-        <f aca="false">IF($A40="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A40,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A40="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A40,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A40))</f>
         <v/>
       </c>
       <c r="J40" s="24" t="str">
@@ -2416,6 +2685,12 @@
       </c>
       <c r="M40" s="25" t="str">
         <f aca="false">IF($A40="","",IF($K40&lt;=0,"Rupture",IF($K40&lt;=N($H40),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="24" t="str">
+        <f aca="false">IF($A40="","",IF($K40&lt;=N($H40),MAX(0,2*N($H40)-$K40),0))</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2704,7 @@
       <c r="G41" s="27"/>
       <c r="H41" s="27"/>
       <c r="I41" s="24" t="str">
-        <f aca="false">IF($A41="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A41,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A41="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A41,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A41))</f>
         <v/>
       </c>
       <c r="J41" s="24" t="str">
@@ -2446,6 +2721,12 @@
       </c>
       <c r="M41" s="25" t="str">
         <f aca="false">IF($A41="","",IF($K41&lt;=0,"Rupture",IF($K41&lt;=N($H41),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="24" t="str">
+        <f aca="false">IF($A41="","",IF($K41&lt;=N($H41),MAX(0,2*N($H41)-$K41),0))</f>
         <v/>
       </c>
     </row>
@@ -2459,7 +2740,7 @@
       <c r="G42" s="27"/>
       <c r="H42" s="27"/>
       <c r="I42" s="24" t="str">
-        <f aca="false">IF($A42="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A42,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A42="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A42,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A42))</f>
         <v/>
       </c>
       <c r="J42" s="24" t="str">
@@ -2476,6 +2757,12 @@
       </c>
       <c r="M42" s="25" t="str">
         <f aca="false">IF($A42="","",IF($K42&lt;=0,"Rupture",IF($K42&lt;=N($H42),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="24" t="str">
+        <f aca="false">IF($A42="","",IF($K42&lt;=N($H42),MAX(0,2*N($H42)-$K42),0))</f>
         <v/>
       </c>
     </row>
@@ -2489,7 +2776,7 @@
       <c r="G43" s="27"/>
       <c r="H43" s="27"/>
       <c r="I43" s="24" t="str">
-        <f aca="false">IF($A43="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A43,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A43="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A43,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A43))</f>
         <v/>
       </c>
       <c r="J43" s="24" t="str">
@@ -2506,6 +2793,12 @@
       </c>
       <c r="M43" s="25" t="str">
         <f aca="false">IF($A43="","",IF($K43&lt;=0,"Rupture",IF($K43&lt;=N($H43),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="24" t="str">
+        <f aca="false">IF($A43="","",IF($K43&lt;=N($H43),MAX(0,2*N($H43)-$K43),0))</f>
         <v/>
       </c>
     </row>
@@ -2519,7 +2812,7 @@
       <c r="G44" s="27"/>
       <c r="H44" s="27"/>
       <c r="I44" s="24" t="str">
-        <f aca="false">IF($A44="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A44,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A44="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A44,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A44))</f>
         <v/>
       </c>
       <c r="J44" s="24" t="str">
@@ -2536,6 +2829,12 @@
       </c>
       <c r="M44" s="25" t="str">
         <f aca="false">IF($A44="","",IF($K44&lt;=0,"Rupture",IF($K44&lt;=N($H44),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="24" t="str">
+        <f aca="false">IF($A44="","",IF($K44&lt;=N($H44),MAX(0,2*N($H44)-$K44),0))</f>
         <v/>
       </c>
     </row>
@@ -2549,7 +2848,7 @@
       <c r="G45" s="27"/>
       <c r="H45" s="27"/>
       <c r="I45" s="24" t="str">
-        <f aca="false">IF($A45="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A45,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A45="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A45,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A45))</f>
         <v/>
       </c>
       <c r="J45" s="24" t="str">
@@ -2566,6 +2865,12 @@
       </c>
       <c r="M45" s="25" t="str">
         <f aca="false">IF($A45="","",IF($K45&lt;=0,"Rupture",IF($K45&lt;=N($H45),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N45" s="26"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="24" t="str">
+        <f aca="false">IF($A45="","",IF($K45&lt;=N($H45),MAX(0,2*N($H45)-$K45),0))</f>
         <v/>
       </c>
     </row>
@@ -2579,7 +2884,7 @@
       <c r="G46" s="27"/>
       <c r="H46" s="27"/>
       <c r="I46" s="24" t="str">
-        <f aca="false">IF($A46="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A46,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A46="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A46,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A46))</f>
         <v/>
       </c>
       <c r="J46" s="24" t="str">
@@ -2596,6 +2901,12 @@
       </c>
       <c r="M46" s="25" t="str">
         <f aca="false">IF($A46="","",IF($K46&lt;=0,"Rupture",IF($K46&lt;=N($H46),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="24" t="str">
+        <f aca="false">IF($A46="","",IF($K46&lt;=N($H46),MAX(0,2*N($H46)-$K46),0))</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2920,7 @@
       <c r="G47" s="27"/>
       <c r="H47" s="27"/>
       <c r="I47" s="24" t="str">
-        <f aca="false">IF($A47="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A47,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A47="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A47,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A47))</f>
         <v/>
       </c>
       <c r="J47" s="24" t="str">
@@ -2626,6 +2937,12 @@
       </c>
       <c r="M47" s="25" t="str">
         <f aca="false">IF($A47="","",IF($K47&lt;=0,"Rupture",IF($K47&lt;=N($H47),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="24" t="str">
+        <f aca="false">IF($A47="","",IF($K47&lt;=N($H47),MAX(0,2*N($H47)-$K47),0))</f>
         <v/>
       </c>
     </row>
@@ -2639,7 +2956,7 @@
       <c r="G48" s="27"/>
       <c r="H48" s="27"/>
       <c r="I48" s="24" t="str">
-        <f aca="false">IF($A48="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A48,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A48="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A48,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A48))</f>
         <v/>
       </c>
       <c r="J48" s="24" t="str">
@@ -2656,6 +2973,12 @@
       </c>
       <c r="M48" s="25" t="str">
         <f aca="false">IF($A48="","",IF($K48&lt;=0,"Rupture",IF($K48&lt;=N($H48),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="24" t="str">
+        <f aca="false">IF($A48="","",IF($K48&lt;=N($H48),MAX(0,2*N($H48)-$K48),0))</f>
         <v/>
       </c>
     </row>
@@ -2669,7 +2992,7 @@
       <c r="G49" s="27"/>
       <c r="H49" s="27"/>
       <c r="I49" s="24" t="str">
-        <f aca="false">IF($A49="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A49,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A49="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A49,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A49))</f>
         <v/>
       </c>
       <c r="J49" s="24" t="str">
@@ -2686,6 +3009,12 @@
       </c>
       <c r="M49" s="25" t="str">
         <f aca="false">IF($A49="","",IF($K49&lt;=0,"Rupture",IF($K49&lt;=N($H49),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="24" t="str">
+        <f aca="false">IF($A49="","",IF($K49&lt;=N($H49),MAX(0,2*N($H49)-$K49),0))</f>
         <v/>
       </c>
     </row>
@@ -2699,7 +3028,7 @@
       <c r="G50" s="27"/>
       <c r="H50" s="27"/>
       <c r="I50" s="24" t="str">
-        <f aca="false">IF($A50="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A50,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A50="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A50,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A50))</f>
         <v/>
       </c>
       <c r="J50" s="24" t="str">
@@ -2716,6 +3045,12 @@
       </c>
       <c r="M50" s="25" t="str">
         <f aca="false">IF($A50="","",IF($K50&lt;=0,"Rupture",IF($K50&lt;=N($H50),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="24" t="str">
+        <f aca="false">IF($A50="","",IF($K50&lt;=N($H50),MAX(0,2*N($H50)-$K50),0))</f>
         <v/>
       </c>
     </row>
@@ -2729,7 +3064,7 @@
       <c r="G51" s="27"/>
       <c r="H51" s="27"/>
       <c r="I51" s="24" t="str">
-        <f aca="false">IF($A51="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A51,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A51="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A51,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A51))</f>
         <v/>
       </c>
       <c r="J51" s="24" t="str">
@@ -2746,6 +3081,12 @@
       </c>
       <c r="M51" s="25" t="str">
         <f aca="false">IF($A51="","",IF($K51&lt;=0,"Rupture",IF($K51&lt;=N($H51),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N51" s="26"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="24" t="str">
+        <f aca="false">IF($A51="","",IF($K51&lt;=N($H51),MAX(0,2*N($H51)-$K51),0))</f>
         <v/>
       </c>
     </row>
@@ -2759,7 +3100,7 @@
       <c r="G52" s="27"/>
       <c r="H52" s="27"/>
       <c r="I52" s="24" t="str">
-        <f aca="false">IF($A52="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A52,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A52="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A52,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A52))</f>
         <v/>
       </c>
       <c r="J52" s="24" t="str">
@@ -2776,6 +3117,12 @@
       </c>
       <c r="M52" s="25" t="str">
         <f aca="false">IF($A52="","",IF($K52&lt;=0,"Rupture",IF($K52&lt;=N($H52),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="24" t="str">
+        <f aca="false">IF($A52="","",IF($K52&lt;=N($H52),MAX(0,2*N($H52)-$K52),0))</f>
         <v/>
       </c>
     </row>
@@ -2789,7 +3136,7 @@
       <c r="G53" s="27"/>
       <c r="H53" s="27"/>
       <c r="I53" s="24" t="str">
-        <f aca="false">IF($A53="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A53,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A53="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A53,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A53))</f>
         <v/>
       </c>
       <c r="J53" s="24" t="str">
@@ -2806,6 +3153,12 @@
       </c>
       <c r="M53" s="25" t="str">
         <f aca="false">IF($A53="","",IF($K53&lt;=0,"Rupture",IF($K53&lt;=N($H53),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="24" t="str">
+        <f aca="false">IF($A53="","",IF($K53&lt;=N($H53),MAX(0,2*N($H53)-$K53),0))</f>
         <v/>
       </c>
     </row>
@@ -2819,7 +3172,7 @@
       <c r="G54" s="27"/>
       <c r="H54" s="27"/>
       <c r="I54" s="24" t="str">
-        <f aca="false">IF($A54="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A54,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A54="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A54,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A54))</f>
         <v/>
       </c>
       <c r="J54" s="24" t="str">
@@ -2836,6 +3189,12 @@
       </c>
       <c r="M54" s="25" t="str">
         <f aca="false">IF($A54="","",IF($K54&lt;=0,"Rupture",IF($K54&lt;=N($H54),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N54" s="26"/>
+      <c r="O54" s="26"/>
+      <c r="P54" s="24" t="str">
+        <f aca="false">IF($A54="","",IF($K54&lt;=N($H54),MAX(0,2*N($H54)-$K54),0))</f>
         <v/>
       </c>
     </row>
@@ -2849,7 +3208,7 @@
       <c r="G55" s="27"/>
       <c r="H55" s="27"/>
       <c r="I55" s="24" t="str">
-        <f aca="false">IF($A55="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A55,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A55="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A55,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A55))</f>
         <v/>
       </c>
       <c r="J55" s="24" t="str">
@@ -2866,6 +3225,12 @@
       </c>
       <c r="M55" s="25" t="str">
         <f aca="false">IF($A55="","",IF($K55&lt;=0,"Rupture",IF($K55&lt;=N($H55),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N55" s="26"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="24" t="str">
+        <f aca="false">IF($A55="","",IF($K55&lt;=N($H55),MAX(0,2*N($H55)-$K55),0))</f>
         <v/>
       </c>
     </row>
@@ -2879,7 +3244,7 @@
       <c r="G56" s="27"/>
       <c r="H56" s="27"/>
       <c r="I56" s="24" t="str">
-        <f aca="false">IF($A56="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A56,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A56="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A56,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A56))</f>
         <v/>
       </c>
       <c r="J56" s="24" t="str">
@@ -2896,6 +3261,12 @@
       </c>
       <c r="M56" s="25" t="str">
         <f aca="false">IF($A56="","",IF($K56&lt;=0,"Rupture",IF($K56&lt;=N($H56),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
+      <c r="P56" s="24" t="str">
+        <f aca="false">IF($A56="","",IF($K56&lt;=N($H56),MAX(0,2*N($H56)-$K56),0))</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +3280,7 @@
       <c r="G57" s="27"/>
       <c r="H57" s="27"/>
       <c r="I57" s="24" t="str">
-        <f aca="false">IF($A57="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A57,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A57="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A57,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A57))</f>
         <v/>
       </c>
       <c r="J57" s="24" t="str">
@@ -2926,6 +3297,12 @@
       </c>
       <c r="M57" s="25" t="str">
         <f aca="false">IF($A57="","",IF($K57&lt;=0,"Rupture",IF($K57&lt;=N($H57),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="24" t="str">
+        <f aca="false">IF($A57="","",IF($K57&lt;=N($H57),MAX(0,2*N($H57)-$K57),0))</f>
         <v/>
       </c>
     </row>
@@ -2939,7 +3316,7 @@
       <c r="G58" s="27"/>
       <c r="H58" s="27"/>
       <c r="I58" s="24" t="str">
-        <f aca="false">IF($A58="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A58,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A58="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A58,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A58))</f>
         <v/>
       </c>
       <c r="J58" s="24" t="str">
@@ -2956,6 +3333,12 @@
       </c>
       <c r="M58" s="25" t="str">
         <f aca="false">IF($A58="","",IF($K58&lt;=0,"Rupture",IF($K58&lt;=N($H58),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N58" s="26"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="24" t="str">
+        <f aca="false">IF($A58="","",IF($K58&lt;=N($H58),MAX(0,2*N($H58)-$K58),0))</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +3352,7 @@
       <c r="G59" s="27"/>
       <c r="H59" s="27"/>
       <c r="I59" s="24" t="str">
-        <f aca="false">IF($A59="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A59,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A59="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A59,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A59))</f>
         <v/>
       </c>
       <c r="J59" s="24" t="str">
@@ -2986,6 +3369,12 @@
       </c>
       <c r="M59" s="25" t="str">
         <f aca="false">IF($A59="","",IF($K59&lt;=0,"Rupture",IF($K59&lt;=N($H59),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N59" s="26"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="24" t="str">
+        <f aca="false">IF($A59="","",IF($K59&lt;=N($H59),MAX(0,2*N($H59)-$K59),0))</f>
         <v/>
       </c>
     </row>
@@ -2999,7 +3388,7 @@
       <c r="G60" s="27"/>
       <c r="H60" s="27"/>
       <c r="I60" s="24" t="str">
-        <f aca="false">IF($A60="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A60,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A60="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A60,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A60))</f>
         <v/>
       </c>
       <c r="J60" s="24" t="str">
@@ -3016,6 +3405,12 @@
       </c>
       <c r="M60" s="25" t="str">
         <f aca="false">IF($A60="","",IF($K60&lt;=0,"Rupture",IF($K60&lt;=N($H60),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="24" t="str">
+        <f aca="false">IF($A60="","",IF($K60&lt;=N($H60),MAX(0,2*N($H60)-$K60),0))</f>
         <v/>
       </c>
     </row>
@@ -3029,7 +3424,7 @@
       <c r="G61" s="27"/>
       <c r="H61" s="27"/>
       <c r="I61" s="24" t="str">
-        <f aca="false">IF($A61="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A61,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A61="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A61,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A61))</f>
         <v/>
       </c>
       <c r="J61" s="24" t="str">
@@ -3046,6 +3441,12 @@
       </c>
       <c r="M61" s="25" t="str">
         <f aca="false">IF($A61="","",IF($K61&lt;=0,"Rupture",IF($K61&lt;=N($H61),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="24" t="str">
+        <f aca="false">IF($A61="","",IF($K61&lt;=N($H61),MAX(0,2*N($H61)-$K61),0))</f>
         <v/>
       </c>
     </row>
@@ -3059,7 +3460,7 @@
       <c r="G62" s="27"/>
       <c r="H62" s="27"/>
       <c r="I62" s="24" t="str">
-        <f aca="false">IF($A62="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A62,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A62="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A62,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A62))</f>
         <v/>
       </c>
       <c r="J62" s="24" t="str">
@@ -3076,6 +3477,12 @@
       </c>
       <c r="M62" s="25" t="str">
         <f aca="false">IF($A62="","",IF($K62&lt;=0,"Rupture",IF($K62&lt;=N($H62),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N62" s="26"/>
+      <c r="O62" s="26"/>
+      <c r="P62" s="24" t="str">
+        <f aca="false">IF($A62="","",IF($K62&lt;=N($H62),MAX(0,2*N($H62)-$K62),0))</f>
         <v/>
       </c>
     </row>
@@ -3089,7 +3496,7 @@
       <c r="G63" s="27"/>
       <c r="H63" s="27"/>
       <c r="I63" s="24" t="str">
-        <f aca="false">IF($A63="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A63,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A63="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A63,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A63))</f>
         <v/>
       </c>
       <c r="J63" s="24" t="str">
@@ -3106,6 +3513,12 @@
       </c>
       <c r="M63" s="25" t="str">
         <f aca="false">IF($A63="","",IF($K63&lt;=0,"Rupture",IF($K63&lt;=N($H63),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="24" t="str">
+        <f aca="false">IF($A63="","",IF($K63&lt;=N($H63),MAX(0,2*N($H63)-$K63),0))</f>
         <v/>
       </c>
     </row>
@@ -3119,7 +3532,7 @@
       <c r="G64" s="27"/>
       <c r="H64" s="27"/>
       <c r="I64" s="24" t="str">
-        <f aca="false">IF($A64="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A64,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A64="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A64,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A64))</f>
         <v/>
       </c>
       <c r="J64" s="24" t="str">
@@ -3136,6 +3549,12 @@
       </c>
       <c r="M64" s="25" t="str">
         <f aca="false">IF($A64="","",IF($K64&lt;=0,"Rupture",IF($K64&lt;=N($H64),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="24" t="str">
+        <f aca="false">IF($A64="","",IF($K64&lt;=N($H64),MAX(0,2*N($H64)-$K64),0))</f>
         <v/>
       </c>
     </row>
@@ -3149,7 +3568,7 @@
       <c r="G65" s="27"/>
       <c r="H65" s="27"/>
       <c r="I65" s="24" t="str">
-        <f aca="false">IF($A65="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A65,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A65="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A65,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A65))</f>
         <v/>
       </c>
       <c r="J65" s="24" t="str">
@@ -3166,6 +3585,12 @@
       </c>
       <c r="M65" s="25" t="str">
         <f aca="false">IF($A65="","",IF($K65&lt;=0,"Rupture",IF($K65&lt;=N($H65),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="24" t="str">
+        <f aca="false">IF($A65="","",IF($K65&lt;=N($H65),MAX(0,2*N($H65)-$K65),0))</f>
         <v/>
       </c>
     </row>
@@ -3179,7 +3604,7 @@
       <c r="G66" s="27"/>
       <c r="H66" s="27"/>
       <c r="I66" s="24" t="str">
-        <f aca="false">IF($A66="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A66,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A66="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A66,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A66))</f>
         <v/>
       </c>
       <c r="J66" s="24" t="str">
@@ -3196,6 +3621,12 @@
       </c>
       <c r="M66" s="25" t="str">
         <f aca="false">IF($A66="","",IF($K66&lt;=0,"Rupture",IF($K66&lt;=N($H66),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N66" s="26"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="24" t="str">
+        <f aca="false">IF($A66="","",IF($K66&lt;=N($H66),MAX(0,2*N($H66)-$K66),0))</f>
         <v/>
       </c>
     </row>
@@ -3209,7 +3640,7 @@
       <c r="G67" s="27"/>
       <c r="H67" s="27"/>
       <c r="I67" s="24" t="str">
-        <f aca="false">IF($A67="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A67,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A67="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A67,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A67))</f>
         <v/>
       </c>
       <c r="J67" s="24" t="str">
@@ -3226,6 +3657,12 @@
       </c>
       <c r="M67" s="25" t="str">
         <f aca="false">IF($A67="","",IF($K67&lt;=0,"Rupture",IF($K67&lt;=N($H67),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N67" s="26"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="24" t="str">
+        <f aca="false">IF($A67="","",IF($K67&lt;=N($H67),MAX(0,2*N($H67)-$K67),0))</f>
         <v/>
       </c>
     </row>
@@ -3239,7 +3676,7 @@
       <c r="G68" s="27"/>
       <c r="H68" s="27"/>
       <c r="I68" s="24" t="str">
-        <f aca="false">IF($A68="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A68,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A68="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A68,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A68))</f>
         <v/>
       </c>
       <c r="J68" s="24" t="str">
@@ -3256,6 +3693,12 @@
       </c>
       <c r="M68" s="25" t="str">
         <f aca="false">IF($A68="","",IF($K68&lt;=0,"Rupture",IF($K68&lt;=N($H68),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N68" s="26"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="24" t="str">
+        <f aca="false">IF($A68="","",IF($K68&lt;=N($H68),MAX(0,2*N($H68)-$K68),0))</f>
         <v/>
       </c>
     </row>
@@ -3269,7 +3712,7 @@
       <c r="G69" s="27"/>
       <c r="H69" s="27"/>
       <c r="I69" s="24" t="str">
-        <f aca="false">IF($A69="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A69,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A69="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A69,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A69))</f>
         <v/>
       </c>
       <c r="J69" s="24" t="str">
@@ -3286,6 +3729,12 @@
       </c>
       <c r="M69" s="25" t="str">
         <f aca="false">IF($A69="","",IF($K69&lt;=0,"Rupture",IF($K69&lt;=N($H69),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N69" s="26"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="24" t="str">
+        <f aca="false">IF($A69="","",IF($K69&lt;=N($H69),MAX(0,2*N($H69)-$K69),0))</f>
         <v/>
       </c>
     </row>
@@ -3299,7 +3748,7 @@
       <c r="G70" s="27"/>
       <c r="H70" s="27"/>
       <c r="I70" s="24" t="str">
-        <f aca="false">IF($A70="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A70,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A70="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A70,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A70))</f>
         <v/>
       </c>
       <c r="J70" s="24" t="str">
@@ -3316,6 +3765,12 @@
       </c>
       <c r="M70" s="25" t="str">
         <f aca="false">IF($A70="","",IF($K70&lt;=0,"Rupture",IF($K70&lt;=N($H70),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="24" t="str">
+        <f aca="false">IF($A70="","",IF($K70&lt;=N($H70),MAX(0,2*N($H70)-$K70),0))</f>
         <v/>
       </c>
     </row>
@@ -3329,7 +3784,7 @@
       <c r="G71" s="27"/>
       <c r="H71" s="27"/>
       <c r="I71" s="24" t="str">
-        <f aca="false">IF($A71="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A71,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A71="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A71,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A71))</f>
         <v/>
       </c>
       <c r="J71" s="24" t="str">
@@ -3346,6 +3801,12 @@
       </c>
       <c r="M71" s="25" t="str">
         <f aca="false">IF($A71="","",IF($K71&lt;=0,"Rupture",IF($K71&lt;=N($H71),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="24" t="str">
+        <f aca="false">IF($A71="","",IF($K71&lt;=N($H71),MAX(0,2*N($H71)-$K71),0))</f>
         <v/>
       </c>
     </row>
@@ -3359,7 +3820,7 @@
       <c r="G72" s="27"/>
       <c r="H72" s="27"/>
       <c r="I72" s="24" t="str">
-        <f aca="false">IF($A72="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A72,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A72="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A72,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A72))</f>
         <v/>
       </c>
       <c r="J72" s="24" t="str">
@@ -3376,6 +3837,12 @@
       </c>
       <c r="M72" s="25" t="str">
         <f aca="false">IF($A72="","",IF($K72&lt;=0,"Rupture",IF($K72&lt;=N($H72),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="24" t="str">
+        <f aca="false">IF($A72="","",IF($K72&lt;=N($H72),MAX(0,2*N($H72)-$K72),0))</f>
         <v/>
       </c>
     </row>
@@ -3389,7 +3856,7 @@
       <c r="G73" s="27"/>
       <c r="H73" s="27"/>
       <c r="I73" s="24" t="str">
-        <f aca="false">IF($A73="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A73,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A73="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A73,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A73))</f>
         <v/>
       </c>
       <c r="J73" s="24" t="str">
@@ -3406,6 +3873,12 @@
       </c>
       <c r="M73" s="25" t="str">
         <f aca="false">IF($A73="","",IF($K73&lt;=0,"Rupture",IF($K73&lt;=N($H73),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="24" t="str">
+        <f aca="false">IF($A73="","",IF($K73&lt;=N($H73),MAX(0,2*N($H73)-$K73),0))</f>
         <v/>
       </c>
     </row>
@@ -3419,7 +3892,7 @@
       <c r="G74" s="27"/>
       <c r="H74" s="27"/>
       <c r="I74" s="24" t="str">
-        <f aca="false">IF($A74="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A74,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A74="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A74,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A74))</f>
         <v/>
       </c>
       <c r="J74" s="24" t="str">
@@ -3436,6 +3909,12 @@
       </c>
       <c r="M74" s="25" t="str">
         <f aca="false">IF($A74="","",IF($K74&lt;=0,"Rupture",IF($K74&lt;=N($H74),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="24" t="str">
+        <f aca="false">IF($A74="","",IF($K74&lt;=N($H74),MAX(0,2*N($H74)-$K74),0))</f>
         <v/>
       </c>
     </row>
@@ -3449,7 +3928,7 @@
       <c r="G75" s="27"/>
       <c r="H75" s="27"/>
       <c r="I75" s="24" t="str">
-        <f aca="false">IF($A75="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A75,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A75="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A75,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A75))</f>
         <v/>
       </c>
       <c r="J75" s="24" t="str">
@@ -3466,6 +3945,12 @@
       </c>
       <c r="M75" s="25" t="str">
         <f aca="false">IF($A75="","",IF($K75&lt;=0,"Rupture",IF($K75&lt;=N($H75),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="24" t="str">
+        <f aca="false">IF($A75="","",IF($K75&lt;=N($H75),MAX(0,2*N($H75)-$K75),0))</f>
         <v/>
       </c>
     </row>
@@ -3479,7 +3964,7 @@
       <c r="G76" s="27"/>
       <c r="H76" s="27"/>
       <c r="I76" s="24" t="str">
-        <f aca="false">IF($A76="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A76,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A76="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A76,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A76))</f>
         <v/>
       </c>
       <c r="J76" s="24" t="str">
@@ -3496,6 +3981,12 @@
       </c>
       <c r="M76" s="25" t="str">
         <f aca="false">IF($A76="","",IF($K76&lt;=0,"Rupture",IF($K76&lt;=N($H76),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="24" t="str">
+        <f aca="false">IF($A76="","",IF($K76&lt;=N($H76),MAX(0,2*N($H76)-$K76),0))</f>
         <v/>
       </c>
     </row>
@@ -3509,7 +4000,7 @@
       <c r="G77" s="27"/>
       <c r="H77" s="27"/>
       <c r="I77" s="24" t="str">
-        <f aca="false">IF($A77="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A77,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A77="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A77,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A77))</f>
         <v/>
       </c>
       <c r="J77" s="24" t="str">
@@ -3526,6 +4017,12 @@
       </c>
       <c r="M77" s="25" t="str">
         <f aca="false">IF($A77="","",IF($K77&lt;=0,"Rupture",IF($K77&lt;=N($H77),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="24" t="str">
+        <f aca="false">IF($A77="","",IF($K77&lt;=N($H77),MAX(0,2*N($H77)-$K77),0))</f>
         <v/>
       </c>
     </row>
@@ -3539,7 +4036,7 @@
       <c r="G78" s="27"/>
       <c r="H78" s="27"/>
       <c r="I78" s="24" t="str">
-        <f aca="false">IF($A78="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A78,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A78="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A78,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A78))</f>
         <v/>
       </c>
       <c r="J78" s="24" t="str">
@@ -3556,6 +4053,12 @@
       </c>
       <c r="M78" s="25" t="str">
         <f aca="false">IF($A78="","",IF($K78&lt;=0,"Rupture",IF($K78&lt;=N($H78),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="24" t="str">
+        <f aca="false">IF($A78="","",IF($K78&lt;=N($H78),MAX(0,2*N($H78)-$K78),0))</f>
         <v/>
       </c>
     </row>
@@ -3569,7 +4072,7 @@
       <c r="G79" s="27"/>
       <c r="H79" s="27"/>
       <c r="I79" s="24" t="str">
-        <f aca="false">IF($A79="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A79,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A79="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A79,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A79))</f>
         <v/>
       </c>
       <c r="J79" s="24" t="str">
@@ -3586,6 +4089,12 @@
       </c>
       <c r="M79" s="25" t="str">
         <f aca="false">IF($A79="","",IF($K79&lt;=0,"Rupture",IF($K79&lt;=N($H79),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="24" t="str">
+        <f aca="false">IF($A79="","",IF($K79&lt;=N($H79),MAX(0,2*N($H79)-$K79),0))</f>
         <v/>
       </c>
     </row>
@@ -3599,7 +4108,7 @@
       <c r="G80" s="27"/>
       <c r="H80" s="27"/>
       <c r="I80" s="24" t="str">
-        <f aca="false">IF($A80="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A80,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A80="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A80,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A80))</f>
         <v/>
       </c>
       <c r="J80" s="24" t="str">
@@ -3616,6 +4125,12 @@
       </c>
       <c r="M80" s="25" t="str">
         <f aca="false">IF($A80="","",IF($K80&lt;=0,"Rupture",IF($K80&lt;=N($H80),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="24" t="str">
+        <f aca="false">IF($A80="","",IF($K80&lt;=N($H80),MAX(0,2*N($H80)-$K80),0))</f>
         <v/>
       </c>
     </row>
@@ -3629,7 +4144,7 @@
       <c r="G81" s="27"/>
       <c r="H81" s="27"/>
       <c r="I81" s="24" t="str">
-        <f aca="false">IF($A81="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A81,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A81="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A81,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A81))</f>
         <v/>
       </c>
       <c r="J81" s="24" t="str">
@@ -3646,6 +4161,12 @@
       </c>
       <c r="M81" s="25" t="str">
         <f aca="false">IF($A81="","",IF($K81&lt;=0,"Rupture",IF($K81&lt;=N($H81),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="24" t="str">
+        <f aca="false">IF($A81="","",IF($K81&lt;=N($H81),MAX(0,2*N($H81)-$K81),0))</f>
         <v/>
       </c>
     </row>
@@ -3659,7 +4180,7 @@
       <c r="G82" s="27"/>
       <c r="H82" s="27"/>
       <c r="I82" s="24" t="str">
-        <f aca="false">IF($A82="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A82,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A82="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A82,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A82))</f>
         <v/>
       </c>
       <c r="J82" s="24" t="str">
@@ -3676,6 +4197,12 @@
       </c>
       <c r="M82" s="25" t="str">
         <f aca="false">IF($A82="","",IF($K82&lt;=0,"Rupture",IF($K82&lt;=N($H82),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="26"/>
+      <c r="O82" s="26"/>
+      <c r="P82" s="24" t="str">
+        <f aca="false">IF($A82="","",IF($K82&lt;=N($H82),MAX(0,2*N($H82)-$K82),0))</f>
         <v/>
       </c>
     </row>
@@ -3689,7 +4216,7 @@
       <c r="G83" s="27"/>
       <c r="H83" s="27"/>
       <c r="I83" s="24" t="str">
-        <f aca="false">IF($A83="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A83,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A83="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A83,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A83))</f>
         <v/>
       </c>
       <c r="J83" s="24" t="str">
@@ -3706,6 +4233,12 @@
       </c>
       <c r="M83" s="25" t="str">
         <f aca="false">IF($A83="","",IF($K83&lt;=0,"Rupture",IF($K83&lt;=N($H83),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N83" s="26"/>
+      <c r="O83" s="26"/>
+      <c r="P83" s="24" t="str">
+        <f aca="false">IF($A83="","",IF($K83&lt;=N($H83),MAX(0,2*N($H83)-$K83),0))</f>
         <v/>
       </c>
     </row>
@@ -3719,7 +4252,7 @@
       <c r="G84" s="27"/>
       <c r="H84" s="27"/>
       <c r="I84" s="24" t="str">
-        <f aca="false">IF($A84="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A84,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A84="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A84,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A84))</f>
         <v/>
       </c>
       <c r="J84" s="24" t="str">
@@ -3736,6 +4269,12 @@
       </c>
       <c r="M84" s="25" t="str">
         <f aca="false">IF($A84="","",IF($K84&lt;=0,"Rupture",IF($K84&lt;=N($H84),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N84" s="26"/>
+      <c r="O84" s="26"/>
+      <c r="P84" s="24" t="str">
+        <f aca="false">IF($A84="","",IF($K84&lt;=N($H84),MAX(0,2*N($H84)-$K84),0))</f>
         <v/>
       </c>
     </row>
@@ -3749,7 +4288,7 @@
       <c r="G85" s="27"/>
       <c r="H85" s="27"/>
       <c r="I85" s="24" t="str">
-        <f aca="false">IF($A85="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A85,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A85="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A85,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A85))</f>
         <v/>
       </c>
       <c r="J85" s="24" t="str">
@@ -3766,6 +4305,12 @@
       </c>
       <c r="M85" s="25" t="str">
         <f aca="false">IF($A85="","",IF($K85&lt;=0,"Rupture",IF($K85&lt;=N($H85),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="26"/>
+      <c r="O85" s="26"/>
+      <c r="P85" s="24" t="str">
+        <f aca="false">IF($A85="","",IF($K85&lt;=N($H85),MAX(0,2*N($H85)-$K85),0))</f>
         <v/>
       </c>
     </row>
@@ -3779,7 +4324,7 @@
       <c r="G86" s="27"/>
       <c r="H86" s="27"/>
       <c r="I86" s="24" t="str">
-        <f aca="false">IF($A86="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A86,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A86="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A86,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A86))</f>
         <v/>
       </c>
       <c r="J86" s="24" t="str">
@@ -3796,6 +4341,12 @@
       </c>
       <c r="M86" s="25" t="str">
         <f aca="false">IF($A86="","",IF($K86&lt;=0,"Rupture",IF($K86&lt;=N($H86),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="26"/>
+      <c r="O86" s="26"/>
+      <c r="P86" s="24" t="str">
+        <f aca="false">IF($A86="","",IF($K86&lt;=N($H86),MAX(0,2*N($H86)-$K86),0))</f>
         <v/>
       </c>
     </row>
@@ -3809,7 +4360,7 @@
       <c r="G87" s="27"/>
       <c r="H87" s="27"/>
       <c r="I87" s="24" t="str">
-        <f aca="false">IF($A87="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A87,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A87="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A87,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A87))</f>
         <v/>
       </c>
       <c r="J87" s="24" t="str">
@@ -3826,6 +4377,12 @@
       </c>
       <c r="M87" s="25" t="str">
         <f aca="false">IF($A87="","",IF($K87&lt;=0,"Rupture",IF($K87&lt;=N($H87),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N87" s="26"/>
+      <c r="O87" s="26"/>
+      <c r="P87" s="24" t="str">
+        <f aca="false">IF($A87="","",IF($K87&lt;=N($H87),MAX(0,2*N($H87)-$K87),0))</f>
         <v/>
       </c>
     </row>
@@ -3839,7 +4396,7 @@
       <c r="G88" s="27"/>
       <c r="H88" s="27"/>
       <c r="I88" s="24" t="str">
-        <f aca="false">IF($A88="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A88,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A88="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A88,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A88))</f>
         <v/>
       </c>
       <c r="J88" s="24" t="str">
@@ -3856,6 +4413,12 @@
       </c>
       <c r="M88" s="25" t="str">
         <f aca="false">IF($A88="","",IF($K88&lt;=0,"Rupture",IF($K88&lt;=N($H88),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="26"/>
+      <c r="O88" s="26"/>
+      <c r="P88" s="24" t="str">
+        <f aca="false">IF($A88="","",IF($K88&lt;=N($H88),MAX(0,2*N($H88)-$K88),0))</f>
         <v/>
       </c>
     </row>
@@ -3869,7 +4432,7 @@
       <c r="G89" s="27"/>
       <c r="H89" s="27"/>
       <c r="I89" s="24" t="str">
-        <f aca="false">IF($A89="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A89,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A89="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A89,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A89))</f>
         <v/>
       </c>
       <c r="J89" s="24" t="str">
@@ -3886,6 +4449,12 @@
       </c>
       <c r="M89" s="25" t="str">
         <f aca="false">IF($A89="","",IF($K89&lt;=0,"Rupture",IF($K89&lt;=N($H89),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N89" s="26"/>
+      <c r="O89" s="26"/>
+      <c r="P89" s="24" t="str">
+        <f aca="false">IF($A89="","",IF($K89&lt;=N($H89),MAX(0,2*N($H89)-$K89),0))</f>
         <v/>
       </c>
     </row>
@@ -3899,7 +4468,7 @@
       <c r="G90" s="27"/>
       <c r="H90" s="27"/>
       <c r="I90" s="24" t="str">
-        <f aca="false">IF($A90="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A90,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A90="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A90,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A90))</f>
         <v/>
       </c>
       <c r="J90" s="24" t="str">
@@ -3916,6 +4485,12 @@
       </c>
       <c r="M90" s="25" t="str">
         <f aca="false">IF($A90="","",IF($K90&lt;=0,"Rupture",IF($K90&lt;=N($H90),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N90" s="26"/>
+      <c r="O90" s="26"/>
+      <c r="P90" s="24" t="str">
+        <f aca="false">IF($A90="","",IF($K90&lt;=N($H90),MAX(0,2*N($H90)-$K90),0))</f>
         <v/>
       </c>
     </row>
@@ -3929,7 +4504,7 @@
       <c r="G91" s="27"/>
       <c r="H91" s="27"/>
       <c r="I91" s="24" t="str">
-        <f aca="false">IF($A91="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A91,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A91="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A91,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A91))</f>
         <v/>
       </c>
       <c r="J91" s="24" t="str">
@@ -3946,6 +4521,12 @@
       </c>
       <c r="M91" s="25" t="str">
         <f aca="false">IF($A91="","",IF($K91&lt;=0,"Rupture",IF($K91&lt;=N($H91),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N91" s="26"/>
+      <c r="O91" s="26"/>
+      <c r="P91" s="24" t="str">
+        <f aca="false">IF($A91="","",IF($K91&lt;=N($H91),MAX(0,2*N($H91)-$K91),0))</f>
         <v/>
       </c>
     </row>
@@ -3959,7 +4540,7 @@
       <c r="G92" s="27"/>
       <c r="H92" s="27"/>
       <c r="I92" s="24" t="str">
-        <f aca="false">IF($A92="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A92,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A92="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A92,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A92))</f>
         <v/>
       </c>
       <c r="J92" s="24" t="str">
@@ -3976,6 +4557,12 @@
       </c>
       <c r="M92" s="25" t="str">
         <f aca="false">IF($A92="","",IF($K92&lt;=0,"Rupture",IF($K92&lt;=N($H92),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N92" s="26"/>
+      <c r="O92" s="26"/>
+      <c r="P92" s="24" t="str">
+        <f aca="false">IF($A92="","",IF($K92&lt;=N($H92),MAX(0,2*N($H92)-$K92),0))</f>
         <v/>
       </c>
     </row>
@@ -3989,7 +4576,7 @@
       <c r="G93" s="27"/>
       <c r="H93" s="27"/>
       <c r="I93" s="24" t="str">
-        <f aca="false">IF($A93="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A93,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A93="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A93,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A93))</f>
         <v/>
       </c>
       <c r="J93" s="24" t="str">
@@ -4006,6 +4593,12 @@
       </c>
       <c r="M93" s="25" t="str">
         <f aca="false">IF($A93="","",IF($K93&lt;=0,"Rupture",IF($K93&lt;=N($H93),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N93" s="26"/>
+      <c r="O93" s="26"/>
+      <c r="P93" s="24" t="str">
+        <f aca="false">IF($A93="","",IF($K93&lt;=N($H93),MAX(0,2*N($H93)-$K93),0))</f>
         <v/>
       </c>
     </row>
@@ -4019,7 +4612,7 @@
       <c r="G94" s="27"/>
       <c r="H94" s="27"/>
       <c r="I94" s="24" t="str">
-        <f aca="false">IF($A94="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A94,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A94="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A94,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A94))</f>
         <v/>
       </c>
       <c r="J94" s="24" t="str">
@@ -4036,6 +4629,12 @@
       </c>
       <c r="M94" s="25" t="str">
         <f aca="false">IF($A94="","",IF($K94&lt;=0,"Rupture",IF($K94&lt;=N($H94),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N94" s="26"/>
+      <c r="O94" s="26"/>
+      <c r="P94" s="24" t="str">
+        <f aca="false">IF($A94="","",IF($K94&lt;=N($H94),MAX(0,2*N($H94)-$K94),0))</f>
         <v/>
       </c>
     </row>
@@ -4049,7 +4648,7 @@
       <c r="G95" s="27"/>
       <c r="H95" s="27"/>
       <c r="I95" s="24" t="str">
-        <f aca="false">IF($A95="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A95,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A95="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A95,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A95))</f>
         <v/>
       </c>
       <c r="J95" s="24" t="str">
@@ -4066,6 +4665,12 @@
       </c>
       <c r="M95" s="25" t="str">
         <f aca="false">IF($A95="","",IF($K95&lt;=0,"Rupture",IF($K95&lt;=N($H95),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N95" s="26"/>
+      <c r="O95" s="26"/>
+      <c r="P95" s="24" t="str">
+        <f aca="false">IF($A95="","",IF($K95&lt;=N($H95),MAX(0,2*N($H95)-$K95),0))</f>
         <v/>
       </c>
     </row>
@@ -4079,7 +4684,7 @@
       <c r="G96" s="27"/>
       <c r="H96" s="27"/>
       <c r="I96" s="24" t="str">
-        <f aca="false">IF($A96="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A96,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A96="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A96,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A96))</f>
         <v/>
       </c>
       <c r="J96" s="24" t="str">
@@ -4096,6 +4701,12 @@
       </c>
       <c r="M96" s="25" t="str">
         <f aca="false">IF($A96="","",IF($K96&lt;=0,"Rupture",IF($K96&lt;=N($H96),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N96" s="26"/>
+      <c r="O96" s="26"/>
+      <c r="P96" s="24" t="str">
+        <f aca="false">IF($A96="","",IF($K96&lt;=N($H96),MAX(0,2*N($H96)-$K96),0))</f>
         <v/>
       </c>
     </row>
@@ -4109,7 +4720,7 @@
       <c r="G97" s="27"/>
       <c r="H97" s="27"/>
       <c r="I97" s="24" t="str">
-        <f aca="false">IF($A97="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A97,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A97="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A97,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A97))</f>
         <v/>
       </c>
       <c r="J97" s="24" t="str">
@@ -4126,6 +4737,12 @@
       </c>
       <c r="M97" s="25" t="str">
         <f aca="false">IF($A97="","",IF($K97&lt;=0,"Rupture",IF($K97&lt;=N($H97),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N97" s="26"/>
+      <c r="O97" s="26"/>
+      <c r="P97" s="24" t="str">
+        <f aca="false">IF($A97="","",IF($K97&lt;=N($H97),MAX(0,2*N($H97)-$K97),0))</f>
         <v/>
       </c>
     </row>
@@ -4139,7 +4756,7 @@
       <c r="G98" s="27"/>
       <c r="H98" s="27"/>
       <c r="I98" s="24" t="str">
-        <f aca="false">IF($A98="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A98,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A98="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A98,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A98))</f>
         <v/>
       </c>
       <c r="J98" s="24" t="str">
@@ -4156,6 +4773,12 @@
       </c>
       <c r="M98" s="25" t="str">
         <f aca="false">IF($A98="","",IF($K98&lt;=0,"Rupture",IF($K98&lt;=N($H98),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="24" t="str">
+        <f aca="false">IF($A98="","",IF($K98&lt;=N($H98),MAX(0,2*N($H98)-$K98),0))</f>
         <v/>
       </c>
     </row>
@@ -4169,7 +4792,7 @@
       <c r="G99" s="27"/>
       <c r="H99" s="27"/>
       <c r="I99" s="24" t="str">
-        <f aca="false">IF($A99="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A99,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A99="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A99,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A99))</f>
         <v/>
       </c>
       <c r="J99" s="24" t="str">
@@ -4186,6 +4809,12 @@
       </c>
       <c r="M99" s="25" t="str">
         <f aca="false">IF($A99="","",IF($K99&lt;=0,"Rupture",IF($K99&lt;=N($H99),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N99" s="26"/>
+      <c r="O99" s="26"/>
+      <c r="P99" s="24" t="str">
+        <f aca="false">IF($A99="","",IF($K99&lt;=N($H99),MAX(0,2*N($H99)-$K99),0))</f>
         <v/>
       </c>
     </row>
@@ -4199,7 +4828,7 @@
       <c r="G100" s="27"/>
       <c r="H100" s="27"/>
       <c r="I100" s="24" t="str">
-        <f aca="false">IF($A100="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A100,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A100="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A100,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A100))</f>
         <v/>
       </c>
       <c r="J100" s="24" t="str">
@@ -4216,6 +4845,12 @@
       </c>
       <c r="M100" s="25" t="str">
         <f aca="false">IF($A100="","",IF($K100&lt;=0,"Rupture",IF($K100&lt;=N($H100),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N100" s="26"/>
+      <c r="O100" s="26"/>
+      <c r="P100" s="24" t="str">
+        <f aca="false">IF($A100="","",IF($K100&lt;=N($H100),MAX(0,2*N($H100)-$K100),0))</f>
         <v/>
       </c>
     </row>
@@ -4229,7 +4864,7 @@
       <c r="G101" s="27"/>
       <c r="H101" s="27"/>
       <c r="I101" s="24" t="str">
-        <f aca="false">IF($A101="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A101,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A101="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A101,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A101))</f>
         <v/>
       </c>
       <c r="J101" s="24" t="str">
@@ -4246,6 +4881,12 @@
       </c>
       <c r="M101" s="25" t="str">
         <f aca="false">IF($A101="","",IF($K101&lt;=0,"Rupture",IF($K101&lt;=N($H101),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N101" s="26"/>
+      <c r="O101" s="26"/>
+      <c r="P101" s="24" t="str">
+        <f aca="false">IF($A101="","",IF($K101&lt;=N($H101),MAX(0,2*N($H101)-$K101),0))</f>
         <v/>
       </c>
     </row>
@@ -4259,7 +4900,7 @@
       <c r="G102" s="27"/>
       <c r="H102" s="27"/>
       <c r="I102" s="24" t="str">
-        <f aca="false">IF($A102="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A102,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A102="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A102,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A102))</f>
         <v/>
       </c>
       <c r="J102" s="24" t="str">
@@ -4276,6 +4917,12 @@
       </c>
       <c r="M102" s="25" t="str">
         <f aca="false">IF($A102="","",IF($K102&lt;=0,"Rupture",IF($K102&lt;=N($H102),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N102" s="26"/>
+      <c r="O102" s="26"/>
+      <c r="P102" s="24" t="str">
+        <f aca="false">IF($A102="","",IF($K102&lt;=N($H102),MAX(0,2*N($H102)-$K102),0))</f>
         <v/>
       </c>
     </row>
@@ -4289,7 +4936,7 @@
       <c r="G103" s="27"/>
       <c r="H103" s="27"/>
       <c r="I103" s="24" t="str">
-        <f aca="false">IF($A103="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A103,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A103="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A103,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A103))</f>
         <v/>
       </c>
       <c r="J103" s="24" t="str">
@@ -4306,6 +4953,12 @@
       </c>
       <c r="M103" s="25" t="str">
         <f aca="false">IF($A103="","",IF($K103&lt;=0,"Rupture",IF($K103&lt;=N($H103),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N103" s="26"/>
+      <c r="O103" s="26"/>
+      <c r="P103" s="24" t="str">
+        <f aca="false">IF($A103="","",IF($K103&lt;=N($H103),MAX(0,2*N($H103)-$K103),0))</f>
         <v/>
       </c>
     </row>
@@ -4319,7 +4972,7 @@
       <c r="G104" s="27"/>
       <c r="H104" s="27"/>
       <c r="I104" s="24" t="str">
-        <f aca="false">IF($A104="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A104,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A104="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A104,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A104))</f>
         <v/>
       </c>
       <c r="J104" s="24" t="str">
@@ -4336,6 +4989,12 @@
       </c>
       <c r="M104" s="25" t="str">
         <f aca="false">IF($A104="","",IF($K104&lt;=0,"Rupture",IF($K104&lt;=N($H104),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N104" s="26"/>
+      <c r="O104" s="26"/>
+      <c r="P104" s="24" t="str">
+        <f aca="false">IF($A104="","",IF($K104&lt;=N($H104),MAX(0,2*N($H104)-$K104),0))</f>
         <v/>
       </c>
     </row>
@@ -4349,7 +5008,7 @@
       <c r="G105" s="27"/>
       <c r="H105" s="27"/>
       <c r="I105" s="24" t="str">
-        <f aca="false">IF($A105="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A105,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A105="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A105,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A105))</f>
         <v/>
       </c>
       <c r="J105" s="24" t="str">
@@ -4366,6 +5025,12 @@
       </c>
       <c r="M105" s="25" t="str">
         <f aca="false">IF($A105="","",IF($K105&lt;=0,"Rupture",IF($K105&lt;=N($H105),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N105" s="26"/>
+      <c r="O105" s="26"/>
+      <c r="P105" s="24" t="str">
+        <f aca="false">IF($A105="","",IF($K105&lt;=N($H105),MAX(0,2*N($H105)-$K105),0))</f>
         <v/>
       </c>
     </row>
@@ -4379,7 +5044,7 @@
       <c r="G106" s="27"/>
       <c r="H106" s="27"/>
       <c r="I106" s="24" t="str">
-        <f aca="false">IF($A106="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A106,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A106="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A106,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A106))</f>
         <v/>
       </c>
       <c r="J106" s="24" t="str">
@@ -4396,6 +5061,12 @@
       </c>
       <c r="M106" s="25" t="str">
         <f aca="false">IF($A106="","",IF($K106&lt;=0,"Rupture",IF($K106&lt;=N($H106),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N106" s="26"/>
+      <c r="O106" s="26"/>
+      <c r="P106" s="24" t="str">
+        <f aca="false">IF($A106="","",IF($K106&lt;=N($H106),MAX(0,2*N($H106)-$K106),0))</f>
         <v/>
       </c>
     </row>
@@ -4409,7 +5080,7 @@
       <c r="G107" s="27"/>
       <c r="H107" s="27"/>
       <c r="I107" s="24" t="str">
-        <f aca="false">IF($A107="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A107,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A107="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A107,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A107))</f>
         <v/>
       </c>
       <c r="J107" s="24" t="str">
@@ -4426,6 +5097,12 @@
       </c>
       <c r="M107" s="25" t="str">
         <f aca="false">IF($A107="","",IF($K107&lt;=0,"Rupture",IF($K107&lt;=N($H107),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N107" s="26"/>
+      <c r="O107" s="26"/>
+      <c r="P107" s="24" t="str">
+        <f aca="false">IF($A107="","",IF($K107&lt;=N($H107),MAX(0,2*N($H107)-$K107),0))</f>
         <v/>
       </c>
     </row>
@@ -4439,7 +5116,7 @@
       <c r="G108" s="27"/>
       <c r="H108" s="27"/>
       <c r="I108" s="24" t="str">
-        <f aca="false">IF($A108="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A108,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A108="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A108,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A108))</f>
         <v/>
       </c>
       <c r="J108" s="24" t="str">
@@ -4456,6 +5133,12 @@
       </c>
       <c r="M108" s="25" t="str">
         <f aca="false">IF($A108="","",IF($K108&lt;=0,"Rupture",IF($K108&lt;=N($H108),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N108" s="26"/>
+      <c r="O108" s="26"/>
+      <c r="P108" s="24" t="str">
+        <f aca="false">IF($A108="","",IF($K108&lt;=N($H108),MAX(0,2*N($H108)-$K108),0))</f>
         <v/>
       </c>
     </row>
@@ -4469,7 +5152,7 @@
       <c r="G109" s="27"/>
       <c r="H109" s="27"/>
       <c r="I109" s="24" t="str">
-        <f aca="false">IF($A109="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A109,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A109="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A109,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A109))</f>
         <v/>
       </c>
       <c r="J109" s="24" t="str">
@@ -4486,6 +5169,12 @@
       </c>
       <c r="M109" s="25" t="str">
         <f aca="false">IF($A109="","",IF($K109&lt;=0,"Rupture",IF($K109&lt;=N($H109),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N109" s="26"/>
+      <c r="O109" s="26"/>
+      <c r="P109" s="24" t="str">
+        <f aca="false">IF($A109="","",IF($K109&lt;=N($H109),MAX(0,2*N($H109)-$K109),0))</f>
         <v/>
       </c>
     </row>
@@ -4499,7 +5188,7 @@
       <c r="G110" s="27"/>
       <c r="H110" s="27"/>
       <c r="I110" s="24" t="str">
-        <f aca="false">IF($A110="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A110,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A110="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A110,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A110))</f>
         <v/>
       </c>
       <c r="J110" s="24" t="str">
@@ -4516,6 +5205,12 @@
       </c>
       <c r="M110" s="25" t="str">
         <f aca="false">IF($A110="","",IF($K110&lt;=0,"Rupture",IF($K110&lt;=N($H110),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N110" s="26"/>
+      <c r="O110" s="26"/>
+      <c r="P110" s="24" t="str">
+        <f aca="false">IF($A110="","",IF($K110&lt;=N($H110),MAX(0,2*N($H110)-$K110),0))</f>
         <v/>
       </c>
     </row>
@@ -4529,7 +5224,7 @@
       <c r="G111" s="27"/>
       <c r="H111" s="27"/>
       <c r="I111" s="24" t="str">
-        <f aca="false">IF($A111="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A111,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A111="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A111,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A111))</f>
         <v/>
       </c>
       <c r="J111" s="24" t="str">
@@ -4546,6 +5241,12 @@
       </c>
       <c r="M111" s="25" t="str">
         <f aca="false">IF($A111="","",IF($K111&lt;=0,"Rupture",IF($K111&lt;=N($H111),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N111" s="26"/>
+      <c r="O111" s="26"/>
+      <c r="P111" s="24" t="str">
+        <f aca="false">IF($A111="","",IF($K111&lt;=N($H111),MAX(0,2*N($H111)-$K111),0))</f>
         <v/>
       </c>
     </row>
@@ -4559,7 +5260,7 @@
       <c r="G112" s="27"/>
       <c r="H112" s="27"/>
       <c r="I112" s="24" t="str">
-        <f aca="false">IF($A112="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A112,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A112="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A112,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A112))</f>
         <v/>
       </c>
       <c r="J112" s="24" t="str">
@@ -4576,6 +5277,12 @@
       </c>
       <c r="M112" s="25" t="str">
         <f aca="false">IF($A112="","",IF($K112&lt;=0,"Rupture",IF($K112&lt;=N($H112),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N112" s="26"/>
+      <c r="O112" s="26"/>
+      <c r="P112" s="24" t="str">
+        <f aca="false">IF($A112="","",IF($K112&lt;=N($H112),MAX(0,2*N($H112)-$K112),0))</f>
         <v/>
       </c>
     </row>
@@ -4589,7 +5296,7 @@
       <c r="G113" s="27"/>
       <c r="H113" s="27"/>
       <c r="I113" s="24" t="str">
-        <f aca="false">IF($A113="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A113,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A113="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A113,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A113))</f>
         <v/>
       </c>
       <c r="J113" s="24" t="str">
@@ -4606,6 +5313,12 @@
       </c>
       <c r="M113" s="25" t="str">
         <f aca="false">IF($A113="","",IF($K113&lt;=0,"Rupture",IF($K113&lt;=N($H113),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N113" s="26"/>
+      <c r="O113" s="26"/>
+      <c r="P113" s="24" t="str">
+        <f aca="false">IF($A113="","",IF($K113&lt;=N($H113),MAX(0,2*N($H113)-$K113),0))</f>
         <v/>
       </c>
     </row>
@@ -4619,7 +5332,7 @@
       <c r="G114" s="27"/>
       <c r="H114" s="27"/>
       <c r="I114" s="24" t="str">
-        <f aca="false">IF($A114="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A114,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A114="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A114,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A114))</f>
         <v/>
       </c>
       <c r="J114" s="24" t="str">
@@ -4636,6 +5349,12 @@
       </c>
       <c r="M114" s="25" t="str">
         <f aca="false">IF($A114="","",IF($K114&lt;=0,"Rupture",IF($K114&lt;=N($H114),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N114" s="26"/>
+      <c r="O114" s="26"/>
+      <c r="P114" s="24" t="str">
+        <f aca="false">IF($A114="","",IF($K114&lt;=N($H114),MAX(0,2*N($H114)-$K114),0))</f>
         <v/>
       </c>
     </row>
@@ -4649,7 +5368,7 @@
       <c r="G115" s="27"/>
       <c r="H115" s="27"/>
       <c r="I115" s="24" t="str">
-        <f aca="false">IF($A115="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A115,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A115="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A115,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A115))</f>
         <v/>
       </c>
       <c r="J115" s="24" t="str">
@@ -4666,6 +5385,12 @@
       </c>
       <c r="M115" s="25" t="str">
         <f aca="false">IF($A115="","",IF($K115&lt;=0,"Rupture",IF($K115&lt;=N($H115),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N115" s="26"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="24" t="str">
+        <f aca="false">IF($A115="","",IF($K115&lt;=N($H115),MAX(0,2*N($H115)-$K115),0))</f>
         <v/>
       </c>
     </row>
@@ -4679,7 +5404,7 @@
       <c r="G116" s="27"/>
       <c r="H116" s="27"/>
       <c r="I116" s="24" t="str">
-        <f aca="false">IF($A116="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A116,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A116="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A116,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A116))</f>
         <v/>
       </c>
       <c r="J116" s="24" t="str">
@@ -4696,6 +5421,12 @@
       </c>
       <c r="M116" s="25" t="str">
         <f aca="false">IF($A116="","",IF($K116&lt;=0,"Rupture",IF($K116&lt;=N($H116),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N116" s="26"/>
+      <c r="O116" s="26"/>
+      <c r="P116" s="24" t="str">
+        <f aca="false">IF($A116="","",IF($K116&lt;=N($H116),MAX(0,2*N($H116)-$K116),0))</f>
         <v/>
       </c>
     </row>
@@ -4709,7 +5440,7 @@
       <c r="G117" s="27"/>
       <c r="H117" s="27"/>
       <c r="I117" s="24" t="str">
-        <f aca="false">IF($A117="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A117,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A117="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A117,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A117))</f>
         <v/>
       </c>
       <c r="J117" s="24" t="str">
@@ -4726,6 +5457,12 @@
       </c>
       <c r="M117" s="25" t="str">
         <f aca="false">IF($A117="","",IF($K117&lt;=0,"Rupture",IF($K117&lt;=N($H117),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N117" s="26"/>
+      <c r="O117" s="26"/>
+      <c r="P117" s="24" t="str">
+        <f aca="false">IF($A117="","",IF($K117&lt;=N($H117),MAX(0,2*N($H117)-$K117),0))</f>
         <v/>
       </c>
     </row>
@@ -4739,7 +5476,7 @@
       <c r="G118" s="27"/>
       <c r="H118" s="27"/>
       <c r="I118" s="24" t="str">
-        <f aca="false">IF($A118="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A118,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A118="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A118,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A118))</f>
         <v/>
       </c>
       <c r="J118" s="24" t="str">
@@ -4756,6 +5493,12 @@
       </c>
       <c r="M118" s="25" t="str">
         <f aca="false">IF($A118="","",IF($K118&lt;=0,"Rupture",IF($K118&lt;=N($H118),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N118" s="26"/>
+      <c r="O118" s="26"/>
+      <c r="P118" s="24" t="str">
+        <f aca="false">IF($A118="","",IF($K118&lt;=N($H118),MAX(0,2*N($H118)-$K118),0))</f>
         <v/>
       </c>
     </row>
@@ -4769,7 +5512,7 @@
       <c r="G119" s="27"/>
       <c r="H119" s="27"/>
       <c r="I119" s="24" t="str">
-        <f aca="false">IF($A119="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A119,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A119="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A119,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A119))</f>
         <v/>
       </c>
       <c r="J119" s="24" t="str">
@@ -4786,6 +5529,12 @@
       </c>
       <c r="M119" s="25" t="str">
         <f aca="false">IF($A119="","",IF($K119&lt;=0,"Rupture",IF($K119&lt;=N($H119),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N119" s="26"/>
+      <c r="O119" s="26"/>
+      <c r="P119" s="24" t="str">
+        <f aca="false">IF($A119="","",IF($K119&lt;=N($H119),MAX(0,2*N($H119)-$K119),0))</f>
         <v/>
       </c>
     </row>
@@ -4799,7 +5548,7 @@
       <c r="G120" s="27"/>
       <c r="H120" s="27"/>
       <c r="I120" s="24" t="str">
-        <f aca="false">IF($A120="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A120,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A120="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A120,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A120))</f>
         <v/>
       </c>
       <c r="J120" s="24" t="str">
@@ -4816,6 +5565,12 @@
       </c>
       <c r="M120" s="25" t="str">
         <f aca="false">IF($A120="","",IF($K120&lt;=0,"Rupture",IF($K120&lt;=N($H120),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N120" s="26"/>
+      <c r="O120" s="26"/>
+      <c r="P120" s="24" t="str">
+        <f aca="false">IF($A120="","",IF($K120&lt;=N($H120),MAX(0,2*N($H120)-$K120),0))</f>
         <v/>
       </c>
     </row>
@@ -4829,7 +5584,7 @@
       <c r="G121" s="27"/>
       <c r="H121" s="27"/>
       <c r="I121" s="24" t="str">
-        <f aca="false">IF($A121="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A121,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A121="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A121,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A121))</f>
         <v/>
       </c>
       <c r="J121" s="24" t="str">
@@ -4846,6 +5601,12 @@
       </c>
       <c r="M121" s="25" t="str">
         <f aca="false">IF($A121="","",IF($K121&lt;=0,"Rupture",IF($K121&lt;=N($H121),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N121" s="26"/>
+      <c r="O121" s="26"/>
+      <c r="P121" s="24" t="str">
+        <f aca="false">IF($A121="","",IF($K121&lt;=N($H121),MAX(0,2*N($H121)-$K121),0))</f>
         <v/>
       </c>
     </row>
@@ -4859,7 +5620,7 @@
       <c r="G122" s="27"/>
       <c r="H122" s="27"/>
       <c r="I122" s="24" t="str">
-        <f aca="false">IF($A122="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A122,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A122="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A122,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A122))</f>
         <v/>
       </c>
       <c r="J122" s="24" t="str">
@@ -4876,6 +5637,12 @@
       </c>
       <c r="M122" s="25" t="str">
         <f aca="false">IF($A122="","",IF($K122&lt;=0,"Rupture",IF($K122&lt;=N($H122),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N122" s="26"/>
+      <c r="O122" s="26"/>
+      <c r="P122" s="24" t="str">
+        <f aca="false">IF($A122="","",IF($K122&lt;=N($H122),MAX(0,2*N($H122)-$K122),0))</f>
         <v/>
       </c>
     </row>
@@ -4889,7 +5656,7 @@
       <c r="G123" s="27"/>
       <c r="H123" s="27"/>
       <c r="I123" s="24" t="str">
-        <f aca="false">IF($A123="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A123,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A123="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A123,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A123))</f>
         <v/>
       </c>
       <c r="J123" s="24" t="str">
@@ -4906,6 +5673,12 @@
       </c>
       <c r="M123" s="25" t="str">
         <f aca="false">IF($A123="","",IF($K123&lt;=0,"Rupture",IF($K123&lt;=N($H123),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N123" s="26"/>
+      <c r="O123" s="26"/>
+      <c r="P123" s="24" t="str">
+        <f aca="false">IF($A123="","",IF($K123&lt;=N($H123),MAX(0,2*N($H123)-$K123),0))</f>
         <v/>
       </c>
     </row>
@@ -4919,7 +5692,7 @@
       <c r="G124" s="27"/>
       <c r="H124" s="27"/>
       <c r="I124" s="24" t="str">
-        <f aca="false">IF($A124="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A124,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A124="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A124,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A124))</f>
         <v/>
       </c>
       <c r="J124" s="24" t="str">
@@ -4936,6 +5709,12 @@
       </c>
       <c r="M124" s="25" t="str">
         <f aca="false">IF($A124="","",IF($K124&lt;=0,"Rupture",IF($K124&lt;=N($H124),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N124" s="26"/>
+      <c r="O124" s="26"/>
+      <c r="P124" s="24" t="str">
+        <f aca="false">IF($A124="","",IF($K124&lt;=N($H124),MAX(0,2*N($H124)-$K124),0))</f>
         <v/>
       </c>
     </row>
@@ -4949,7 +5728,7 @@
       <c r="G125" s="27"/>
       <c r="H125" s="27"/>
       <c r="I125" s="24" t="str">
-        <f aca="false">IF($A125="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A125,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A125="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A125,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A125))</f>
         <v/>
       </c>
       <c r="J125" s="24" t="str">
@@ -4966,6 +5745,12 @@
       </c>
       <c r="M125" s="25" t="str">
         <f aca="false">IF($A125="","",IF($K125&lt;=0,"Rupture",IF($K125&lt;=N($H125),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N125" s="26"/>
+      <c r="O125" s="26"/>
+      <c r="P125" s="24" t="str">
+        <f aca="false">IF($A125="","",IF($K125&lt;=N($H125),MAX(0,2*N($H125)-$K125),0))</f>
         <v/>
       </c>
     </row>
@@ -4979,7 +5764,7 @@
       <c r="G126" s="27"/>
       <c r="H126" s="27"/>
       <c r="I126" s="24" t="str">
-        <f aca="false">IF($A126="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A126,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A126="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A126,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A126))</f>
         <v/>
       </c>
       <c r="J126" s="24" t="str">
@@ -4996,6 +5781,12 @@
       </c>
       <c r="M126" s="25" t="str">
         <f aca="false">IF($A126="","",IF($K126&lt;=0,"Rupture",IF($K126&lt;=N($H126),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N126" s="26"/>
+      <c r="O126" s="26"/>
+      <c r="P126" s="24" t="str">
+        <f aca="false">IF($A126="","",IF($K126&lt;=N($H126),MAX(0,2*N($H126)-$K126),0))</f>
         <v/>
       </c>
     </row>
@@ -5009,7 +5800,7 @@
       <c r="G127" s="27"/>
       <c r="H127" s="27"/>
       <c r="I127" s="24" t="str">
-        <f aca="false">IF($A127="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A127,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A127="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A127,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A127))</f>
         <v/>
       </c>
       <c r="J127" s="24" t="str">
@@ -5026,6 +5817,12 @@
       </c>
       <c r="M127" s="25" t="str">
         <f aca="false">IF($A127="","",IF($K127&lt;=0,"Rupture",IF($K127&lt;=N($H127),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N127" s="26"/>
+      <c r="O127" s="26"/>
+      <c r="P127" s="24" t="str">
+        <f aca="false">IF($A127="","",IF($K127&lt;=N($H127),MAX(0,2*N($H127)-$K127),0))</f>
         <v/>
       </c>
     </row>
@@ -5039,7 +5836,7 @@
       <c r="G128" s="27"/>
       <c r="H128" s="27"/>
       <c r="I128" s="24" t="str">
-        <f aca="false">IF($A128="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A128,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A128="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A128,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A128))</f>
         <v/>
       </c>
       <c r="J128" s="24" t="str">
@@ -5056,6 +5853,12 @@
       </c>
       <c r="M128" s="25" t="str">
         <f aca="false">IF($A128="","",IF($K128&lt;=0,"Rupture",IF($K128&lt;=N($H128),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N128" s="26"/>
+      <c r="O128" s="26"/>
+      <c r="P128" s="24" t="str">
+        <f aca="false">IF($A128="","",IF($K128&lt;=N($H128),MAX(0,2*N($H128)-$K128),0))</f>
         <v/>
       </c>
     </row>
@@ -5069,7 +5872,7 @@
       <c r="G129" s="27"/>
       <c r="H129" s="27"/>
       <c r="I129" s="24" t="str">
-        <f aca="false">IF($A129="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A129,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A129="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A129,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A129))</f>
         <v/>
       </c>
       <c r="J129" s="24" t="str">
@@ -5086,6 +5889,12 @@
       </c>
       <c r="M129" s="25" t="str">
         <f aca="false">IF($A129="","",IF($K129&lt;=0,"Rupture",IF($K129&lt;=N($H129),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N129" s="26"/>
+      <c r="O129" s="26"/>
+      <c r="P129" s="24" t="str">
+        <f aca="false">IF($A129="","",IF($K129&lt;=N($H129),MAX(0,2*N($H129)-$K129),0))</f>
         <v/>
       </c>
     </row>
@@ -5099,7 +5908,7 @@
       <c r="G130" s="27"/>
       <c r="H130" s="27"/>
       <c r="I130" s="24" t="str">
-        <f aca="false">IF($A130="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A130,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A130="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A130,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A130))</f>
         <v/>
       </c>
       <c r="J130" s="24" t="str">
@@ -5116,6 +5925,12 @@
       </c>
       <c r="M130" s="25" t="str">
         <f aca="false">IF($A130="","",IF($K130&lt;=0,"Rupture",IF($K130&lt;=N($H130),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N130" s="26"/>
+      <c r="O130" s="26"/>
+      <c r="P130" s="24" t="str">
+        <f aca="false">IF($A130="","",IF($K130&lt;=N($H130),MAX(0,2*N($H130)-$K130),0))</f>
         <v/>
       </c>
     </row>
@@ -5129,7 +5944,7 @@
       <c r="G131" s="27"/>
       <c r="H131" s="27"/>
       <c r="I131" s="24" t="str">
-        <f aca="false">IF($A131="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A131,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A131="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A131,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A131))</f>
         <v/>
       </c>
       <c r="J131" s="24" t="str">
@@ -5146,6 +5961,12 @@
       </c>
       <c r="M131" s="25" t="str">
         <f aca="false">IF($A131="","",IF($K131&lt;=0,"Rupture",IF($K131&lt;=N($H131),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N131" s="26"/>
+      <c r="O131" s="26"/>
+      <c r="P131" s="24" t="str">
+        <f aca="false">IF($A131="","",IF($K131&lt;=N($H131),MAX(0,2*N($H131)-$K131),0))</f>
         <v/>
       </c>
     </row>
@@ -5159,7 +5980,7 @@
       <c r="G132" s="27"/>
       <c r="H132" s="27"/>
       <c r="I132" s="24" t="str">
-        <f aca="false">IF($A132="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A132,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A132="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A132,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A132))</f>
         <v/>
       </c>
       <c r="J132" s="24" t="str">
@@ -5176,6 +5997,12 @@
       </c>
       <c r="M132" s="25" t="str">
         <f aca="false">IF($A132="","",IF($K132&lt;=0,"Rupture",IF($K132&lt;=N($H132),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N132" s="26"/>
+      <c r="O132" s="26"/>
+      <c r="P132" s="24" t="str">
+        <f aca="false">IF($A132="","",IF($K132&lt;=N($H132),MAX(0,2*N($H132)-$K132),0))</f>
         <v/>
       </c>
     </row>
@@ -5189,7 +6016,7 @@
       <c r="G133" s="27"/>
       <c r="H133" s="27"/>
       <c r="I133" s="24" t="str">
-        <f aca="false">IF($A133="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A133,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A133="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A133,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A133))</f>
         <v/>
       </c>
       <c r="J133" s="24" t="str">
@@ -5206,6 +6033,12 @@
       </c>
       <c r="M133" s="25" t="str">
         <f aca="false">IF($A133="","",IF($K133&lt;=0,"Rupture",IF($K133&lt;=N($H133),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N133" s="26"/>
+      <c r="O133" s="26"/>
+      <c r="P133" s="24" t="str">
+        <f aca="false">IF($A133="","",IF($K133&lt;=N($H133),MAX(0,2*N($H133)-$K133),0))</f>
         <v/>
       </c>
     </row>
@@ -5219,7 +6052,7 @@
       <c r="G134" s="27"/>
       <c r="H134" s="27"/>
       <c r="I134" s="24" t="str">
-        <f aca="false">IF($A134="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A134,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A134="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A134,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A134))</f>
         <v/>
       </c>
       <c r="J134" s="24" t="str">
@@ -5236,6 +6069,12 @@
       </c>
       <c r="M134" s="25" t="str">
         <f aca="false">IF($A134="","",IF($K134&lt;=0,"Rupture",IF($K134&lt;=N($H134),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N134" s="26"/>
+      <c r="O134" s="26"/>
+      <c r="P134" s="24" t="str">
+        <f aca="false">IF($A134="","",IF($K134&lt;=N($H134),MAX(0,2*N($H134)-$K134),0))</f>
         <v/>
       </c>
     </row>
@@ -5249,7 +6088,7 @@
       <c r="G135" s="27"/>
       <c r="H135" s="27"/>
       <c r="I135" s="24" t="str">
-        <f aca="false">IF($A135="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A135,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A135="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A135,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A135))</f>
         <v/>
       </c>
       <c r="J135" s="24" t="str">
@@ -5266,6 +6105,12 @@
       </c>
       <c r="M135" s="25" t="str">
         <f aca="false">IF($A135="","",IF($K135&lt;=0,"Rupture",IF($K135&lt;=N($H135),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N135" s="26"/>
+      <c r="O135" s="26"/>
+      <c r="P135" s="24" t="str">
+        <f aca="false">IF($A135="","",IF($K135&lt;=N($H135),MAX(0,2*N($H135)-$K135),0))</f>
         <v/>
       </c>
     </row>
@@ -5279,7 +6124,7 @@
       <c r="G136" s="27"/>
       <c r="H136" s="27"/>
       <c r="I136" s="24" t="str">
-        <f aca="false">IF($A136="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A136,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A136="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A136,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A136))</f>
         <v/>
       </c>
       <c r="J136" s="24" t="str">
@@ -5296,6 +6141,12 @@
       </c>
       <c r="M136" s="25" t="str">
         <f aca="false">IF($A136="","",IF($K136&lt;=0,"Rupture",IF($K136&lt;=N($H136),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N136" s="26"/>
+      <c r="O136" s="26"/>
+      <c r="P136" s="24" t="str">
+        <f aca="false">IF($A136="","",IF($K136&lt;=N($H136),MAX(0,2*N($H136)-$K136),0))</f>
         <v/>
       </c>
     </row>
@@ -5309,7 +6160,7 @@
       <c r="G137" s="27"/>
       <c r="H137" s="27"/>
       <c r="I137" s="24" t="str">
-        <f aca="false">IF($A137="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A137,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A137="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A137,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A137))</f>
         <v/>
       </c>
       <c r="J137" s="24" t="str">
@@ -5326,6 +6177,12 @@
       </c>
       <c r="M137" s="25" t="str">
         <f aca="false">IF($A137="","",IF($K137&lt;=0,"Rupture",IF($K137&lt;=N($H137),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N137" s="26"/>
+      <c r="O137" s="26"/>
+      <c r="P137" s="24" t="str">
+        <f aca="false">IF($A137="","",IF($K137&lt;=N($H137),MAX(0,2*N($H137)-$K137),0))</f>
         <v/>
       </c>
     </row>
@@ -5339,7 +6196,7 @@
       <c r="G138" s="27"/>
       <c r="H138" s="27"/>
       <c r="I138" s="24" t="str">
-        <f aca="false">IF($A138="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A138,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A138="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A138,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A138))</f>
         <v/>
       </c>
       <c r="J138" s="24" t="str">
@@ -5356,6 +6213,12 @@
       </c>
       <c r="M138" s="25" t="str">
         <f aca="false">IF($A138="","",IF($K138&lt;=0,"Rupture",IF($K138&lt;=N($H138),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N138" s="26"/>
+      <c r="O138" s="26"/>
+      <c r="P138" s="24" t="str">
+        <f aca="false">IF($A138="","",IF($K138&lt;=N($H138),MAX(0,2*N($H138)-$K138),0))</f>
         <v/>
       </c>
     </row>
@@ -5369,7 +6232,7 @@
       <c r="G139" s="27"/>
       <c r="H139" s="27"/>
       <c r="I139" s="24" t="str">
-        <f aca="false">IF($A139="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A139,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A139="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A139,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A139))</f>
         <v/>
       </c>
       <c r="J139" s="24" t="str">
@@ -5386,6 +6249,12 @@
       </c>
       <c r="M139" s="25" t="str">
         <f aca="false">IF($A139="","",IF($K139&lt;=0,"Rupture",IF($K139&lt;=N($H139),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N139" s="26"/>
+      <c r="O139" s="26"/>
+      <c r="P139" s="24" t="str">
+        <f aca="false">IF($A139="","",IF($K139&lt;=N($H139),MAX(0,2*N($H139)-$K139),0))</f>
         <v/>
       </c>
     </row>
@@ -5399,7 +6268,7 @@
       <c r="G140" s="27"/>
       <c r="H140" s="27"/>
       <c r="I140" s="24" t="str">
-        <f aca="false">IF($A140="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A140,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A140="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A140,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A140))</f>
         <v/>
       </c>
       <c r="J140" s="24" t="str">
@@ -5416,6 +6285,12 @@
       </c>
       <c r="M140" s="25" t="str">
         <f aca="false">IF($A140="","",IF($K140&lt;=0,"Rupture",IF($K140&lt;=N($H140),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N140" s="26"/>
+      <c r="O140" s="26"/>
+      <c r="P140" s="24" t="str">
+        <f aca="false">IF($A140="","",IF($K140&lt;=N($H140),MAX(0,2*N($H140)-$K140),0))</f>
         <v/>
       </c>
     </row>
@@ -5429,7 +6304,7 @@
       <c r="G141" s="27"/>
       <c r="H141" s="27"/>
       <c r="I141" s="24" t="str">
-        <f aca="false">IF($A141="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A141,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A141="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A141,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A141))</f>
         <v/>
       </c>
       <c r="J141" s="24" t="str">
@@ -5446,6 +6321,12 @@
       </c>
       <c r="M141" s="25" t="str">
         <f aca="false">IF($A141="","",IF($K141&lt;=0,"Rupture",IF($K141&lt;=N($H141),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N141" s="26"/>
+      <c r="O141" s="26"/>
+      <c r="P141" s="24" t="str">
+        <f aca="false">IF($A141="","",IF($K141&lt;=N($H141),MAX(0,2*N($H141)-$K141),0))</f>
         <v/>
       </c>
     </row>
@@ -5459,7 +6340,7 @@
       <c r="G142" s="27"/>
       <c r="H142" s="27"/>
       <c r="I142" s="24" t="str">
-        <f aca="false">IF($A142="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A142,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A142="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A142,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A142))</f>
         <v/>
       </c>
       <c r="J142" s="24" t="str">
@@ -5476,6 +6357,12 @@
       </c>
       <c r="M142" s="25" t="str">
         <f aca="false">IF($A142="","",IF($K142&lt;=0,"Rupture",IF($K142&lt;=N($H142),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N142" s="26"/>
+      <c r="O142" s="26"/>
+      <c r="P142" s="24" t="str">
+        <f aca="false">IF($A142="","",IF($K142&lt;=N($H142),MAX(0,2*N($H142)-$K142),0))</f>
         <v/>
       </c>
     </row>
@@ -5489,7 +6376,7 @@
       <c r="G143" s="27"/>
       <c r="H143" s="27"/>
       <c r="I143" s="24" t="str">
-        <f aca="false">IF($A143="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A143,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A143="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A143,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A143))</f>
         <v/>
       </c>
       <c r="J143" s="24" t="str">
@@ -5506,6 +6393,12 @@
       </c>
       <c r="M143" s="25" t="str">
         <f aca="false">IF($A143="","",IF($K143&lt;=0,"Rupture",IF($K143&lt;=N($H143),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N143" s="26"/>
+      <c r="O143" s="26"/>
+      <c r="P143" s="24" t="str">
+        <f aca="false">IF($A143="","",IF($K143&lt;=N($H143),MAX(0,2*N($H143)-$K143),0))</f>
         <v/>
       </c>
     </row>
@@ -5519,7 +6412,7 @@
       <c r="G144" s="27"/>
       <c r="H144" s="27"/>
       <c r="I144" s="24" t="str">
-        <f aca="false">IF($A144="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A144,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A144="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A144,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A144))</f>
         <v/>
       </c>
       <c r="J144" s="24" t="str">
@@ -5536,6 +6429,12 @@
       </c>
       <c r="M144" s="25" t="str">
         <f aca="false">IF($A144="","",IF($K144&lt;=0,"Rupture",IF($K144&lt;=N($H144),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N144" s="26"/>
+      <c r="O144" s="26"/>
+      <c r="P144" s="24" t="str">
+        <f aca="false">IF($A144="","",IF($K144&lt;=N($H144),MAX(0,2*N($H144)-$K144),0))</f>
         <v/>
       </c>
     </row>
@@ -5549,7 +6448,7 @@
       <c r="G145" s="27"/>
       <c r="H145" s="27"/>
       <c r="I145" s="24" t="str">
-        <f aca="false">IF($A145="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A145,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A145="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A145,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A145))</f>
         <v/>
       </c>
       <c r="J145" s="24" t="str">
@@ -5566,6 +6465,12 @@
       </c>
       <c r="M145" s="25" t="str">
         <f aca="false">IF($A145="","",IF($K145&lt;=0,"Rupture",IF($K145&lt;=N($H145),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N145" s="26"/>
+      <c r="O145" s="26"/>
+      <c r="P145" s="24" t="str">
+        <f aca="false">IF($A145="","",IF($K145&lt;=N($H145),MAX(0,2*N($H145)-$K145),0))</f>
         <v/>
       </c>
     </row>
@@ -5579,7 +6484,7 @@
       <c r="G146" s="27"/>
       <c r="H146" s="27"/>
       <c r="I146" s="24" t="str">
-        <f aca="false">IF($A146="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A146,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A146="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A146,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A146))</f>
         <v/>
       </c>
       <c r="J146" s="24" t="str">
@@ -5596,6 +6501,12 @@
       </c>
       <c r="M146" s="25" t="str">
         <f aca="false">IF($A146="","",IF($K146&lt;=0,"Rupture",IF($K146&lt;=N($H146),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N146" s="26"/>
+      <c r="O146" s="26"/>
+      <c r="P146" s="24" t="str">
+        <f aca="false">IF($A146="","",IF($K146&lt;=N($H146),MAX(0,2*N($H146)-$K146),0))</f>
         <v/>
       </c>
     </row>
@@ -5609,7 +6520,7 @@
       <c r="G147" s="27"/>
       <c r="H147" s="27"/>
       <c r="I147" s="24" t="str">
-        <f aca="false">IF($A147="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A147,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A147="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A147,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A147))</f>
         <v/>
       </c>
       <c r="J147" s="24" t="str">
@@ -5626,6 +6537,12 @@
       </c>
       <c r="M147" s="25" t="str">
         <f aca="false">IF($A147="","",IF($K147&lt;=0,"Rupture",IF($K147&lt;=N($H147),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N147" s="26"/>
+      <c r="O147" s="26"/>
+      <c r="P147" s="24" t="str">
+        <f aca="false">IF($A147="","",IF($K147&lt;=N($H147),MAX(0,2*N($H147)-$K147),0))</f>
         <v/>
       </c>
     </row>
@@ -5639,7 +6556,7 @@
       <c r="G148" s="27"/>
       <c r="H148" s="27"/>
       <c r="I148" s="24" t="str">
-        <f aca="false">IF($A148="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A148,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A148="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A148,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A148))</f>
         <v/>
       </c>
       <c r="J148" s="24" t="str">
@@ -5656,6 +6573,12 @@
       </c>
       <c r="M148" s="25" t="str">
         <f aca="false">IF($A148="","",IF($K148&lt;=0,"Rupture",IF($K148&lt;=N($H148),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N148" s="26"/>
+      <c r="O148" s="26"/>
+      <c r="P148" s="24" t="str">
+        <f aca="false">IF($A148="","",IF($K148&lt;=N($H148),MAX(0,2*N($H148)-$K148),0))</f>
         <v/>
       </c>
     </row>
@@ -5669,7 +6592,7 @@
       <c r="G149" s="27"/>
       <c r="H149" s="27"/>
       <c r="I149" s="24" t="str">
-        <f aca="false">IF($A149="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A149,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A149="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A149,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A149))</f>
         <v/>
       </c>
       <c r="J149" s="24" t="str">
@@ -5686,6 +6609,12 @@
       </c>
       <c r="M149" s="25" t="str">
         <f aca="false">IF($A149="","",IF($K149&lt;=0,"Rupture",IF($K149&lt;=N($H149),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N149" s="26"/>
+      <c r="O149" s="26"/>
+      <c r="P149" s="24" t="str">
+        <f aca="false">IF($A149="","",IF($K149&lt;=N($H149),MAX(0,2*N($H149)-$K149),0))</f>
         <v/>
       </c>
     </row>
@@ -5699,7 +6628,7 @@
       <c r="G150" s="27"/>
       <c r="H150" s="27"/>
       <c r="I150" s="24" t="str">
-        <f aca="false">IF($A150="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A150,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A150="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A150,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A150))</f>
         <v/>
       </c>
       <c r="J150" s="24" t="str">
@@ -5716,6 +6645,12 @@
       </c>
       <c r="M150" s="25" t="str">
         <f aca="false">IF($A150="","",IF($K150&lt;=0,"Rupture",IF($K150&lt;=N($H150),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N150" s="26"/>
+      <c r="O150" s="26"/>
+      <c r="P150" s="24" t="str">
+        <f aca="false">IF($A150="","",IF($K150&lt;=N($H150),MAX(0,2*N($H150)-$K150),0))</f>
         <v/>
       </c>
     </row>
@@ -5729,7 +6664,7 @@
       <c r="G151" s="27"/>
       <c r="H151" s="27"/>
       <c r="I151" s="24" t="str">
-        <f aca="false">IF($A151="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A151,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A151="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A151,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A151))</f>
         <v/>
       </c>
       <c r="J151" s="24" t="str">
@@ -5746,6 +6681,12 @@
       </c>
       <c r="M151" s="25" t="str">
         <f aca="false">IF($A151="","",IF($K151&lt;=0,"Rupture",IF($K151&lt;=N($H151),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N151" s="26"/>
+      <c r="O151" s="26"/>
+      <c r="P151" s="24" t="str">
+        <f aca="false">IF($A151="","",IF($K151&lt;=N($H151),MAX(0,2*N($H151)-$K151),0))</f>
         <v/>
       </c>
     </row>
@@ -5759,7 +6700,7 @@
       <c r="G152" s="27"/>
       <c r="H152" s="27"/>
       <c r="I152" s="24" t="str">
-        <f aca="false">IF($A152="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A152,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A152="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A152,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A152))</f>
         <v/>
       </c>
       <c r="J152" s="24" t="str">
@@ -5776,6 +6717,12 @@
       </c>
       <c r="M152" s="25" t="str">
         <f aca="false">IF($A152="","",IF($K152&lt;=0,"Rupture",IF($K152&lt;=N($H152),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N152" s="26"/>
+      <c r="O152" s="26"/>
+      <c r="P152" s="24" t="str">
+        <f aca="false">IF($A152="","",IF($K152&lt;=N($H152),MAX(0,2*N($H152)-$K152),0))</f>
         <v/>
       </c>
     </row>
@@ -5789,7 +6736,7 @@
       <c r="G153" s="27"/>
       <c r="H153" s="27"/>
       <c r="I153" s="24" t="str">
-        <f aca="false">IF($A153="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A153,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A153="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A153,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A153))</f>
         <v/>
       </c>
       <c r="J153" s="24" t="str">
@@ -5806,6 +6753,12 @@
       </c>
       <c r="M153" s="25" t="str">
         <f aca="false">IF($A153="","",IF($K153&lt;=0,"Rupture",IF($K153&lt;=N($H153),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N153" s="26"/>
+      <c r="O153" s="26"/>
+      <c r="P153" s="24" t="str">
+        <f aca="false">IF($A153="","",IF($K153&lt;=N($H153),MAX(0,2*N($H153)-$K153),0))</f>
         <v/>
       </c>
     </row>
@@ -5819,7 +6772,7 @@
       <c r="G154" s="27"/>
       <c r="H154" s="27"/>
       <c r="I154" s="24" t="str">
-        <f aca="false">IF($A154="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A154,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A154="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A154,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A154))</f>
         <v/>
       </c>
       <c r="J154" s="24" t="str">
@@ -5836,6 +6789,12 @@
       </c>
       <c r="M154" s="25" t="str">
         <f aca="false">IF($A154="","",IF($K154&lt;=0,"Rupture",IF($K154&lt;=N($H154),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N154" s="26"/>
+      <c r="O154" s="26"/>
+      <c r="P154" s="24" t="str">
+        <f aca="false">IF($A154="","",IF($K154&lt;=N($H154),MAX(0,2*N($H154)-$K154),0))</f>
         <v/>
       </c>
     </row>
@@ -5849,7 +6808,7 @@
       <c r="G155" s="27"/>
       <c r="H155" s="27"/>
       <c r="I155" s="24" t="str">
-        <f aca="false">IF($A155="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A155,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A155="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A155,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A155))</f>
         <v/>
       </c>
       <c r="J155" s="24" t="str">
@@ -5866,6 +6825,12 @@
       </c>
       <c r="M155" s="25" t="str">
         <f aca="false">IF($A155="","",IF($K155&lt;=0,"Rupture",IF($K155&lt;=N($H155),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N155" s="26"/>
+      <c r="O155" s="26"/>
+      <c r="P155" s="24" t="str">
+        <f aca="false">IF($A155="","",IF($K155&lt;=N($H155),MAX(0,2*N($H155)-$K155),0))</f>
         <v/>
       </c>
     </row>
@@ -5879,7 +6844,7 @@
       <c r="G156" s="27"/>
       <c r="H156" s="27"/>
       <c r="I156" s="24" t="str">
-        <f aca="false">IF($A156="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A156,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A156="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A156,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A156))</f>
         <v/>
       </c>
       <c r="J156" s="24" t="str">
@@ -5896,6 +6861,12 @@
       </c>
       <c r="M156" s="25" t="str">
         <f aca="false">IF($A156="","",IF($K156&lt;=0,"Rupture",IF($K156&lt;=N($H156),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N156" s="26"/>
+      <c r="O156" s="26"/>
+      <c r="P156" s="24" t="str">
+        <f aca="false">IF($A156="","",IF($K156&lt;=N($H156),MAX(0,2*N($H156)-$K156),0))</f>
         <v/>
       </c>
     </row>
@@ -5909,7 +6880,7 @@
       <c r="G157" s="27"/>
       <c r="H157" s="27"/>
       <c r="I157" s="24" t="str">
-        <f aca="false">IF($A157="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A157,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A157="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A157,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A157))</f>
         <v/>
       </c>
       <c r="J157" s="24" t="str">
@@ -5926,6 +6897,12 @@
       </c>
       <c r="M157" s="25" t="str">
         <f aca="false">IF($A157="","",IF($K157&lt;=0,"Rupture",IF($K157&lt;=N($H157),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N157" s="26"/>
+      <c r="O157" s="26"/>
+      <c r="P157" s="24" t="str">
+        <f aca="false">IF($A157="","",IF($K157&lt;=N($H157),MAX(0,2*N($H157)-$K157),0))</f>
         <v/>
       </c>
     </row>
@@ -5939,7 +6916,7 @@
       <c r="G158" s="27"/>
       <c r="H158" s="27"/>
       <c r="I158" s="24" t="str">
-        <f aca="false">IF($A158="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A158,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A158="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A158,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A158))</f>
         <v/>
       </c>
       <c r="J158" s="24" t="str">
@@ -5956,6 +6933,12 @@
       </c>
       <c r="M158" s="25" t="str">
         <f aca="false">IF($A158="","",IF($K158&lt;=0,"Rupture",IF($K158&lt;=N($H158),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N158" s="26"/>
+      <c r="O158" s="26"/>
+      <c r="P158" s="24" t="str">
+        <f aca="false">IF($A158="","",IF($K158&lt;=N($H158),MAX(0,2*N($H158)-$K158),0))</f>
         <v/>
       </c>
     </row>
@@ -5969,7 +6952,7 @@
       <c r="G159" s="27"/>
       <c r="H159" s="27"/>
       <c r="I159" s="24" t="str">
-        <f aca="false">IF($A159="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A159,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A159="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A159,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A159))</f>
         <v/>
       </c>
       <c r="J159" s="24" t="str">
@@ -5986,6 +6969,12 @@
       </c>
       <c r="M159" s="25" t="str">
         <f aca="false">IF($A159="","",IF($K159&lt;=0,"Rupture",IF($K159&lt;=N($H159),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N159" s="26"/>
+      <c r="O159" s="26"/>
+      <c r="P159" s="24" t="str">
+        <f aca="false">IF($A159="","",IF($K159&lt;=N($H159),MAX(0,2*N($H159)-$K159),0))</f>
         <v/>
       </c>
     </row>
@@ -5999,7 +6988,7 @@
       <c r="G160" s="27"/>
       <c r="H160" s="27"/>
       <c r="I160" s="24" t="str">
-        <f aca="false">IF($A160="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A160,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A160="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A160,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A160))</f>
         <v/>
       </c>
       <c r="J160" s="24" t="str">
@@ -6016,6 +7005,12 @@
       </c>
       <c r="M160" s="25" t="str">
         <f aca="false">IF($A160="","",IF($K160&lt;=0,"Rupture",IF($K160&lt;=N($H160),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N160" s="26"/>
+      <c r="O160" s="26"/>
+      <c r="P160" s="24" t="str">
+        <f aca="false">IF($A160="","",IF($K160&lt;=N($H160),MAX(0,2*N($H160)-$K160),0))</f>
         <v/>
       </c>
     </row>
@@ -6029,7 +7024,7 @@
       <c r="G161" s="27"/>
       <c r="H161" s="27"/>
       <c r="I161" s="24" t="str">
-        <f aca="false">IF($A161="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A161,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A161="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A161,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A161))</f>
         <v/>
       </c>
       <c r="J161" s="24" t="str">
@@ -6046,6 +7041,12 @@
       </c>
       <c r="M161" s="25" t="str">
         <f aca="false">IF($A161="","",IF($K161&lt;=0,"Rupture",IF($K161&lt;=N($H161),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N161" s="26"/>
+      <c r="O161" s="26"/>
+      <c r="P161" s="24" t="str">
+        <f aca="false">IF($A161="","",IF($K161&lt;=N($H161),MAX(0,2*N($H161)-$K161),0))</f>
         <v/>
       </c>
     </row>
@@ -6059,7 +7060,7 @@
       <c r="G162" s="27"/>
       <c r="H162" s="27"/>
       <c r="I162" s="24" t="str">
-        <f aca="false">IF($A162="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A162,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A162="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A162,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A162))</f>
         <v/>
       </c>
       <c r="J162" s="24" t="str">
@@ -6076,6 +7077,12 @@
       </c>
       <c r="M162" s="25" t="str">
         <f aca="false">IF($A162="","",IF($K162&lt;=0,"Rupture",IF($K162&lt;=N($H162),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N162" s="26"/>
+      <c r="O162" s="26"/>
+      <c r="P162" s="24" t="str">
+        <f aca="false">IF($A162="","",IF($K162&lt;=N($H162),MAX(0,2*N($H162)-$K162),0))</f>
         <v/>
       </c>
     </row>
@@ -6089,7 +7096,7 @@
       <c r="G163" s="27"/>
       <c r="H163" s="27"/>
       <c r="I163" s="24" t="str">
-        <f aca="false">IF($A163="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A163,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A163="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A163,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A163))</f>
         <v/>
       </c>
       <c r="J163" s="24" t="str">
@@ -6106,6 +7113,12 @@
       </c>
       <c r="M163" s="25" t="str">
         <f aca="false">IF($A163="","",IF($K163&lt;=0,"Rupture",IF($K163&lt;=N($H163),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N163" s="26"/>
+      <c r="O163" s="26"/>
+      <c r="P163" s="24" t="str">
+        <f aca="false">IF($A163="","",IF($K163&lt;=N($H163),MAX(0,2*N($H163)-$K163),0))</f>
         <v/>
       </c>
     </row>
@@ -6119,7 +7132,7 @@
       <c r="G164" s="27"/>
       <c r="H164" s="27"/>
       <c r="I164" s="24" t="str">
-        <f aca="false">IF($A164="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A164,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A164="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A164,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A164))</f>
         <v/>
       </c>
       <c r="J164" s="24" t="str">
@@ -6136,6 +7149,12 @@
       </c>
       <c r="M164" s="25" t="str">
         <f aca="false">IF($A164="","",IF($K164&lt;=0,"Rupture",IF($K164&lt;=N($H164),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N164" s="26"/>
+      <c r="O164" s="26"/>
+      <c r="P164" s="24" t="str">
+        <f aca="false">IF($A164="","",IF($K164&lt;=N($H164),MAX(0,2*N($H164)-$K164),0))</f>
         <v/>
       </c>
     </row>
@@ -6149,7 +7168,7 @@
       <c r="G165" s="27"/>
       <c r="H165" s="27"/>
       <c r="I165" s="24" t="str">
-        <f aca="false">IF($A165="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A165,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A165="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A165,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A165))</f>
         <v/>
       </c>
       <c r="J165" s="24" t="str">
@@ -6166,6 +7185,12 @@
       </c>
       <c r="M165" s="25" t="str">
         <f aca="false">IF($A165="","",IF($K165&lt;=0,"Rupture",IF($K165&lt;=N($H165),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N165" s="26"/>
+      <c r="O165" s="26"/>
+      <c r="P165" s="24" t="str">
+        <f aca="false">IF($A165="","",IF($K165&lt;=N($H165),MAX(0,2*N($H165)-$K165),0))</f>
         <v/>
       </c>
     </row>
@@ -6179,7 +7204,7 @@
       <c r="G166" s="27"/>
       <c r="H166" s="27"/>
       <c r="I166" s="24" t="str">
-        <f aca="false">IF($A166="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A166,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A166="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A166,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A166))</f>
         <v/>
       </c>
       <c r="J166" s="24" t="str">
@@ -6196,6 +7221,12 @@
       </c>
       <c r="M166" s="25" t="str">
         <f aca="false">IF($A166="","",IF($K166&lt;=0,"Rupture",IF($K166&lt;=N($H166),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N166" s="26"/>
+      <c r="O166" s="26"/>
+      <c r="P166" s="24" t="str">
+        <f aca="false">IF($A166="","",IF($K166&lt;=N($H166),MAX(0,2*N($H166)-$K166),0))</f>
         <v/>
       </c>
     </row>
@@ -6209,7 +7240,7 @@
       <c r="G167" s="27"/>
       <c r="H167" s="27"/>
       <c r="I167" s="24" t="str">
-        <f aca="false">IF($A167="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A167,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A167="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A167,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A167))</f>
         <v/>
       </c>
       <c r="J167" s="24" t="str">
@@ -6226,6 +7257,12 @@
       </c>
       <c r="M167" s="25" t="str">
         <f aca="false">IF($A167="","",IF($K167&lt;=0,"Rupture",IF($K167&lt;=N($H167),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N167" s="26"/>
+      <c r="O167" s="26"/>
+      <c r="P167" s="24" t="str">
+        <f aca="false">IF($A167="","",IF($K167&lt;=N($H167),MAX(0,2*N($H167)-$K167),0))</f>
         <v/>
       </c>
     </row>
@@ -6239,7 +7276,7 @@
       <c r="G168" s="27"/>
       <c r="H168" s="27"/>
       <c r="I168" s="24" t="str">
-        <f aca="false">IF($A168="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A168,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A168="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A168,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A168))</f>
         <v/>
       </c>
       <c r="J168" s="24" t="str">
@@ -6256,6 +7293,12 @@
       </c>
       <c r="M168" s="25" t="str">
         <f aca="false">IF($A168="","",IF($K168&lt;=0,"Rupture",IF($K168&lt;=N($H168),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N168" s="26"/>
+      <c r="O168" s="26"/>
+      <c r="P168" s="24" t="str">
+        <f aca="false">IF($A168="","",IF($K168&lt;=N($H168),MAX(0,2*N($H168)-$K168),0))</f>
         <v/>
       </c>
     </row>
@@ -6269,7 +7312,7 @@
       <c r="G169" s="27"/>
       <c r="H169" s="27"/>
       <c r="I169" s="24" t="str">
-        <f aca="false">IF($A169="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A169,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A169="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A169,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A169))</f>
         <v/>
       </c>
       <c r="J169" s="24" t="str">
@@ -6286,6 +7329,12 @@
       </c>
       <c r="M169" s="25" t="str">
         <f aca="false">IF($A169="","",IF($K169&lt;=0,"Rupture",IF($K169&lt;=N($H169),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N169" s="26"/>
+      <c r="O169" s="26"/>
+      <c r="P169" s="24" t="str">
+        <f aca="false">IF($A169="","",IF($K169&lt;=N($H169),MAX(0,2*N($H169)-$K169),0))</f>
         <v/>
       </c>
     </row>
@@ -6299,7 +7348,7 @@
       <c r="G170" s="27"/>
       <c r="H170" s="27"/>
       <c r="I170" s="24" t="str">
-        <f aca="false">IF($A170="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A170,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A170="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A170,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A170))</f>
         <v/>
       </c>
       <c r="J170" s="24" t="str">
@@ -6316,6 +7365,12 @@
       </c>
       <c r="M170" s="25" t="str">
         <f aca="false">IF($A170="","",IF($K170&lt;=0,"Rupture",IF($K170&lt;=N($H170),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N170" s="26"/>
+      <c r="O170" s="26"/>
+      <c r="P170" s="24" t="str">
+        <f aca="false">IF($A170="","",IF($K170&lt;=N($H170),MAX(0,2*N($H170)-$K170),0))</f>
         <v/>
       </c>
     </row>
@@ -6329,7 +7384,7 @@
       <c r="G171" s="27"/>
       <c r="H171" s="27"/>
       <c r="I171" s="24" t="str">
-        <f aca="false">IF($A171="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A171,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A171="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A171,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A171))</f>
         <v/>
       </c>
       <c r="J171" s="24" t="str">
@@ -6346,6 +7401,12 @@
       </c>
       <c r="M171" s="25" t="str">
         <f aca="false">IF($A171="","",IF($K171&lt;=0,"Rupture",IF($K171&lt;=N($H171),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N171" s="26"/>
+      <c r="O171" s="26"/>
+      <c r="P171" s="24" t="str">
+        <f aca="false">IF($A171="","",IF($K171&lt;=N($H171),MAX(0,2*N($H171)-$K171),0))</f>
         <v/>
       </c>
     </row>
@@ -6359,7 +7420,7 @@
       <c r="G172" s="27"/>
       <c r="H172" s="27"/>
       <c r="I172" s="24" t="str">
-        <f aca="false">IF($A172="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A172,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A172="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A172,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A172))</f>
         <v/>
       </c>
       <c r="J172" s="24" t="str">
@@ -6376,6 +7437,12 @@
       </c>
       <c r="M172" s="25" t="str">
         <f aca="false">IF($A172="","",IF($K172&lt;=0,"Rupture",IF($K172&lt;=N($H172),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N172" s="26"/>
+      <c r="O172" s="26"/>
+      <c r="P172" s="24" t="str">
+        <f aca="false">IF($A172="","",IF($K172&lt;=N($H172),MAX(0,2*N($H172)-$K172),0))</f>
         <v/>
       </c>
     </row>
@@ -6389,7 +7456,7 @@
       <c r="G173" s="27"/>
       <c r="H173" s="27"/>
       <c r="I173" s="24" t="str">
-        <f aca="false">IF($A173="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A173,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A173="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A173,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A173))</f>
         <v/>
       </c>
       <c r="J173" s="24" t="str">
@@ -6406,6 +7473,12 @@
       </c>
       <c r="M173" s="25" t="str">
         <f aca="false">IF($A173="","",IF($K173&lt;=0,"Rupture",IF($K173&lt;=N($H173),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N173" s="26"/>
+      <c r="O173" s="26"/>
+      <c r="P173" s="24" t="str">
+        <f aca="false">IF($A173="","",IF($K173&lt;=N($H173),MAX(0,2*N($H173)-$K173),0))</f>
         <v/>
       </c>
     </row>
@@ -6419,7 +7492,7 @@
       <c r="G174" s="27"/>
       <c r="H174" s="27"/>
       <c r="I174" s="24" t="str">
-        <f aca="false">IF($A174="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A174,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A174="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A174,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A174))</f>
         <v/>
       </c>
       <c r="J174" s="24" t="str">
@@ -6436,6 +7509,12 @@
       </c>
       <c r="M174" s="25" t="str">
         <f aca="false">IF($A174="","",IF($K174&lt;=0,"Rupture",IF($K174&lt;=N($H174),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N174" s="26"/>
+      <c r="O174" s="26"/>
+      <c r="P174" s="24" t="str">
+        <f aca="false">IF($A174="","",IF($K174&lt;=N($H174),MAX(0,2*N($H174)-$K174),0))</f>
         <v/>
       </c>
     </row>
@@ -6449,7 +7528,7 @@
       <c r="G175" s="27"/>
       <c r="H175" s="27"/>
       <c r="I175" s="24" t="str">
-        <f aca="false">IF($A175="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A175,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A175="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A175,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A175))</f>
         <v/>
       </c>
       <c r="J175" s="24" t="str">
@@ -6466,6 +7545,12 @@
       </c>
       <c r="M175" s="25" t="str">
         <f aca="false">IF($A175="","",IF($K175&lt;=0,"Rupture",IF($K175&lt;=N($H175),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N175" s="26"/>
+      <c r="O175" s="26"/>
+      <c r="P175" s="24" t="str">
+        <f aca="false">IF($A175="","",IF($K175&lt;=N($H175),MAX(0,2*N($H175)-$K175),0))</f>
         <v/>
       </c>
     </row>
@@ -6479,7 +7564,7 @@
       <c r="G176" s="27"/>
       <c r="H176" s="27"/>
       <c r="I176" s="24" t="str">
-        <f aca="false">IF($A176="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A176,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A176="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A176,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A176))</f>
         <v/>
       </c>
       <c r="J176" s="24" t="str">
@@ -6496,6 +7581,12 @@
       </c>
       <c r="M176" s="25" t="str">
         <f aca="false">IF($A176="","",IF($K176&lt;=0,"Rupture",IF($K176&lt;=N($H176),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N176" s="26"/>
+      <c r="O176" s="26"/>
+      <c r="P176" s="24" t="str">
+        <f aca="false">IF($A176="","",IF($K176&lt;=N($H176),MAX(0,2*N($H176)-$K176),0))</f>
         <v/>
       </c>
     </row>
@@ -6509,7 +7600,7 @@
       <c r="G177" s="27"/>
       <c r="H177" s="27"/>
       <c r="I177" s="24" t="str">
-        <f aca="false">IF($A177="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A177,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A177="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A177,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A177))</f>
         <v/>
       </c>
       <c r="J177" s="24" t="str">
@@ -6526,6 +7617,12 @@
       </c>
       <c r="M177" s="25" t="str">
         <f aca="false">IF($A177="","",IF($K177&lt;=0,"Rupture",IF($K177&lt;=N($H177),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N177" s="26"/>
+      <c r="O177" s="26"/>
+      <c r="P177" s="24" t="str">
+        <f aca="false">IF($A177="","",IF($K177&lt;=N($H177),MAX(0,2*N($H177)-$K177),0))</f>
         <v/>
       </c>
     </row>
@@ -6539,7 +7636,7 @@
       <c r="G178" s="27"/>
       <c r="H178" s="27"/>
       <c r="I178" s="24" t="str">
-        <f aca="false">IF($A178="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A178,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A178="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A178,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A178))</f>
         <v/>
       </c>
       <c r="J178" s="24" t="str">
@@ -6556,6 +7653,12 @@
       </c>
       <c r="M178" s="25" t="str">
         <f aca="false">IF($A178="","",IF($K178&lt;=0,"Rupture",IF($K178&lt;=N($H178),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N178" s="26"/>
+      <c r="O178" s="26"/>
+      <c r="P178" s="24" t="str">
+        <f aca="false">IF($A178="","",IF($K178&lt;=N($H178),MAX(0,2*N($H178)-$K178),0))</f>
         <v/>
       </c>
     </row>
@@ -6569,7 +7672,7 @@
       <c r="G179" s="27"/>
       <c r="H179" s="27"/>
       <c r="I179" s="24" t="str">
-        <f aca="false">IF($A179="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A179,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A179="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A179,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A179))</f>
         <v/>
       </c>
       <c r="J179" s="24" t="str">
@@ -6586,6 +7689,12 @@
       </c>
       <c r="M179" s="25" t="str">
         <f aca="false">IF($A179="","",IF($K179&lt;=0,"Rupture",IF($K179&lt;=N($H179),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N179" s="26"/>
+      <c r="O179" s="26"/>
+      <c r="P179" s="24" t="str">
+        <f aca="false">IF($A179="","",IF($K179&lt;=N($H179),MAX(0,2*N($H179)-$K179),0))</f>
         <v/>
       </c>
     </row>
@@ -6599,7 +7708,7 @@
       <c r="G180" s="27"/>
       <c r="H180" s="27"/>
       <c r="I180" s="24" t="str">
-        <f aca="false">IF($A180="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A180,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A180="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A180,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A180))</f>
         <v/>
       </c>
       <c r="J180" s="24" t="str">
@@ -6616,6 +7725,12 @@
       </c>
       <c r="M180" s="25" t="str">
         <f aca="false">IF($A180="","",IF($K180&lt;=0,"Rupture",IF($K180&lt;=N($H180),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N180" s="26"/>
+      <c r="O180" s="26"/>
+      <c r="P180" s="24" t="str">
+        <f aca="false">IF($A180="","",IF($K180&lt;=N($H180),MAX(0,2*N($H180)-$K180),0))</f>
         <v/>
       </c>
     </row>
@@ -6629,7 +7744,7 @@
       <c r="G181" s="27"/>
       <c r="H181" s="27"/>
       <c r="I181" s="24" t="str">
-        <f aca="false">IF($A181="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A181,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A181="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A181,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A181))</f>
         <v/>
       </c>
       <c r="J181" s="24" t="str">
@@ -6646,6 +7761,12 @@
       </c>
       <c r="M181" s="25" t="str">
         <f aca="false">IF($A181="","",IF($K181&lt;=0,"Rupture",IF($K181&lt;=N($H181),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N181" s="26"/>
+      <c r="O181" s="26"/>
+      <c r="P181" s="24" t="str">
+        <f aca="false">IF($A181="","",IF($K181&lt;=N($H181),MAX(0,2*N($H181)-$K181),0))</f>
         <v/>
       </c>
     </row>
@@ -6659,7 +7780,7 @@
       <c r="G182" s="27"/>
       <c r="H182" s="27"/>
       <c r="I182" s="24" t="str">
-        <f aca="false">IF($A182="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A182,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A182="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A182,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A182))</f>
         <v/>
       </c>
       <c r="J182" s="24" t="str">
@@ -6676,6 +7797,12 @@
       </c>
       <c r="M182" s="25" t="str">
         <f aca="false">IF($A182="","",IF($K182&lt;=0,"Rupture",IF($K182&lt;=N($H182),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N182" s="26"/>
+      <c r="O182" s="26"/>
+      <c r="P182" s="24" t="str">
+        <f aca="false">IF($A182="","",IF($K182&lt;=N($H182),MAX(0,2*N($H182)-$K182),0))</f>
         <v/>
       </c>
     </row>
@@ -6689,7 +7816,7 @@
       <c r="G183" s="27"/>
       <c r="H183" s="27"/>
       <c r="I183" s="24" t="str">
-        <f aca="false">IF($A183="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A183,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A183="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A183,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A183))</f>
         <v/>
       </c>
       <c r="J183" s="24" t="str">
@@ -6706,6 +7833,12 @@
       </c>
       <c r="M183" s="25" t="str">
         <f aca="false">IF($A183="","",IF($K183&lt;=0,"Rupture",IF($K183&lt;=N($H183),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N183" s="26"/>
+      <c r="O183" s="26"/>
+      <c r="P183" s="24" t="str">
+        <f aca="false">IF($A183="","",IF($K183&lt;=N($H183),MAX(0,2*N($H183)-$K183),0))</f>
         <v/>
       </c>
     </row>
@@ -6719,7 +7852,7 @@
       <c r="G184" s="27"/>
       <c r="H184" s="27"/>
       <c r="I184" s="24" t="str">
-        <f aca="false">IF($A184="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A184,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A184="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A184,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A184))</f>
         <v/>
       </c>
       <c r="J184" s="24" t="str">
@@ -6736,6 +7869,12 @@
       </c>
       <c r="M184" s="25" t="str">
         <f aca="false">IF($A184="","",IF($K184&lt;=0,"Rupture",IF($K184&lt;=N($H184),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N184" s="26"/>
+      <c r="O184" s="26"/>
+      <c r="P184" s="24" t="str">
+        <f aca="false">IF($A184="","",IF($K184&lt;=N($H184),MAX(0,2*N($H184)-$K184),0))</f>
         <v/>
       </c>
     </row>
@@ -6749,7 +7888,7 @@
       <c r="G185" s="27"/>
       <c r="H185" s="27"/>
       <c r="I185" s="24" t="str">
-        <f aca="false">IF($A185="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A185,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A185="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A185,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A185))</f>
         <v/>
       </c>
       <c r="J185" s="24" t="str">
@@ -6766,6 +7905,12 @@
       </c>
       <c r="M185" s="25" t="str">
         <f aca="false">IF($A185="","",IF($K185&lt;=0,"Rupture",IF($K185&lt;=N($H185),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N185" s="26"/>
+      <c r="O185" s="26"/>
+      <c r="P185" s="24" t="str">
+        <f aca="false">IF($A185="","",IF($K185&lt;=N($H185),MAX(0,2*N($H185)-$K185),0))</f>
         <v/>
       </c>
     </row>
@@ -6779,7 +7924,7 @@
       <c r="G186" s="27"/>
       <c r="H186" s="27"/>
       <c r="I186" s="24" t="str">
-        <f aca="false">IF($A186="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A186,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A186="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A186,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A186))</f>
         <v/>
       </c>
       <c r="J186" s="24" t="str">
@@ -6796,6 +7941,12 @@
       </c>
       <c r="M186" s="25" t="str">
         <f aca="false">IF($A186="","",IF($K186&lt;=0,"Rupture",IF($K186&lt;=N($H186),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N186" s="26"/>
+      <c r="O186" s="26"/>
+      <c r="P186" s="24" t="str">
+        <f aca="false">IF($A186="","",IF($K186&lt;=N($H186),MAX(0,2*N($H186)-$K186),0))</f>
         <v/>
       </c>
     </row>
@@ -6809,7 +7960,7 @@
       <c r="G187" s="27"/>
       <c r="H187" s="27"/>
       <c r="I187" s="24" t="str">
-        <f aca="false">IF($A187="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A187,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A187="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A187,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A187))</f>
         <v/>
       </c>
       <c r="J187" s="24" t="str">
@@ -6826,6 +7977,12 @@
       </c>
       <c r="M187" s="25" t="str">
         <f aca="false">IF($A187="","",IF($K187&lt;=0,"Rupture",IF($K187&lt;=N($H187),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N187" s="26"/>
+      <c r="O187" s="26"/>
+      <c r="P187" s="24" t="str">
+        <f aca="false">IF($A187="","",IF($K187&lt;=N($H187),MAX(0,2*N($H187)-$K187),0))</f>
         <v/>
       </c>
     </row>
@@ -6839,7 +7996,7 @@
       <c r="G188" s="27"/>
       <c r="H188" s="27"/>
       <c r="I188" s="24" t="str">
-        <f aca="false">IF($A188="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A188,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A188="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A188,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A188))</f>
         <v/>
       </c>
       <c r="J188" s="24" t="str">
@@ -6856,6 +8013,12 @@
       </c>
       <c r="M188" s="25" t="str">
         <f aca="false">IF($A188="","",IF($K188&lt;=0,"Rupture",IF($K188&lt;=N($H188),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N188" s="26"/>
+      <c r="O188" s="26"/>
+      <c r="P188" s="24" t="str">
+        <f aca="false">IF($A188="","",IF($K188&lt;=N($H188),MAX(0,2*N($H188)-$K188),0))</f>
         <v/>
       </c>
     </row>
@@ -6869,7 +8032,7 @@
       <c r="G189" s="27"/>
       <c r="H189" s="27"/>
       <c r="I189" s="24" t="str">
-        <f aca="false">IF($A189="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A189,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A189="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A189,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A189))</f>
         <v/>
       </c>
       <c r="J189" s="24" t="str">
@@ -6886,6 +8049,12 @@
       </c>
       <c r="M189" s="25" t="str">
         <f aca="false">IF($A189="","",IF($K189&lt;=0,"Rupture",IF($K189&lt;=N($H189),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N189" s="26"/>
+      <c r="O189" s="26"/>
+      <c r="P189" s="24" t="str">
+        <f aca="false">IF($A189="","",IF($K189&lt;=N($H189),MAX(0,2*N($H189)-$K189),0))</f>
         <v/>
       </c>
     </row>
@@ -6899,7 +8068,7 @@
       <c r="G190" s="27"/>
       <c r="H190" s="27"/>
       <c r="I190" s="24" t="str">
-        <f aca="false">IF($A190="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A190,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A190="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A190,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A190))</f>
         <v/>
       </c>
       <c r="J190" s="24" t="str">
@@ -6916,6 +8085,12 @@
       </c>
       <c r="M190" s="25" t="str">
         <f aca="false">IF($A190="","",IF($K190&lt;=0,"Rupture",IF($K190&lt;=N($H190),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N190" s="26"/>
+      <c r="O190" s="26"/>
+      <c r="P190" s="24" t="str">
+        <f aca="false">IF($A190="","",IF($K190&lt;=N($H190),MAX(0,2*N($H190)-$K190),0))</f>
         <v/>
       </c>
     </row>
@@ -6929,7 +8104,7 @@
       <c r="G191" s="27"/>
       <c r="H191" s="27"/>
       <c r="I191" s="24" t="str">
-        <f aca="false">IF($A191="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A191,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A191="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A191,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A191))</f>
         <v/>
       </c>
       <c r="J191" s="24" t="str">
@@ -6946,6 +8121,12 @@
       </c>
       <c r="M191" s="25" t="str">
         <f aca="false">IF($A191="","",IF($K191&lt;=0,"Rupture",IF($K191&lt;=N($H191),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N191" s="26"/>
+      <c r="O191" s="26"/>
+      <c r="P191" s="24" t="str">
+        <f aca="false">IF($A191="","",IF($K191&lt;=N($H191),MAX(0,2*N($H191)-$K191),0))</f>
         <v/>
       </c>
     </row>
@@ -6959,7 +8140,7 @@
       <c r="G192" s="27"/>
       <c r="H192" s="27"/>
       <c r="I192" s="24" t="str">
-        <f aca="false">IF($A192="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A192,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A192="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A192,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A192))</f>
         <v/>
       </c>
       <c r="J192" s="24" t="str">
@@ -6976,6 +8157,12 @@
       </c>
       <c r="M192" s="25" t="str">
         <f aca="false">IF($A192="","",IF($K192&lt;=0,"Rupture",IF($K192&lt;=N($H192),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N192" s="26"/>
+      <c r="O192" s="26"/>
+      <c r="P192" s="24" t="str">
+        <f aca="false">IF($A192="","",IF($K192&lt;=N($H192),MAX(0,2*N($H192)-$K192),0))</f>
         <v/>
       </c>
     </row>
@@ -6989,7 +8176,7 @@
       <c r="G193" s="27"/>
       <c r="H193" s="27"/>
       <c r="I193" s="24" t="str">
-        <f aca="false">IF($A193="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A193,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A193="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A193,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A193))</f>
         <v/>
       </c>
       <c r="J193" s="24" t="str">
@@ -7006,6 +8193,12 @@
       </c>
       <c r="M193" s="25" t="str">
         <f aca="false">IF($A193="","",IF($K193&lt;=0,"Rupture",IF($K193&lt;=N($H193),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N193" s="26"/>
+      <c r="O193" s="26"/>
+      <c r="P193" s="24" t="str">
+        <f aca="false">IF($A193="","",IF($K193&lt;=N($H193),MAX(0,2*N($H193)-$K193),0))</f>
         <v/>
       </c>
     </row>
@@ -7019,7 +8212,7 @@
       <c r="G194" s="27"/>
       <c r="H194" s="27"/>
       <c r="I194" s="24" t="str">
-        <f aca="false">IF($A194="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A194,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A194="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A194,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A194))</f>
         <v/>
       </c>
       <c r="J194" s="24" t="str">
@@ -7036,6 +8229,12 @@
       </c>
       <c r="M194" s="25" t="str">
         <f aca="false">IF($A194="","",IF($K194&lt;=0,"Rupture",IF($K194&lt;=N($H194),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N194" s="26"/>
+      <c r="O194" s="26"/>
+      <c r="P194" s="24" t="str">
+        <f aca="false">IF($A194="","",IF($K194&lt;=N($H194),MAX(0,2*N($H194)-$K194),0))</f>
         <v/>
       </c>
     </row>
@@ -7049,7 +8248,7 @@
       <c r="G195" s="27"/>
       <c r="H195" s="27"/>
       <c r="I195" s="24" t="str">
-        <f aca="false">IF($A195="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A195,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A195="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A195,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A195))</f>
         <v/>
       </c>
       <c r="J195" s="24" t="str">
@@ -7066,6 +8265,12 @@
       </c>
       <c r="M195" s="25" t="str">
         <f aca="false">IF($A195="","",IF($K195&lt;=0,"Rupture",IF($K195&lt;=N($H195),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N195" s="26"/>
+      <c r="O195" s="26"/>
+      <c r="P195" s="24" t="str">
+        <f aca="false">IF($A195="","",IF($K195&lt;=N($H195),MAX(0,2*N($H195)-$K195),0))</f>
         <v/>
       </c>
     </row>
@@ -7079,7 +8284,7 @@
       <c r="G196" s="27"/>
       <c r="H196" s="27"/>
       <c r="I196" s="24" t="str">
-        <f aca="false">IF($A196="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A196,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A196="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A196,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A196))</f>
         <v/>
       </c>
       <c r="J196" s="24" t="str">
@@ -7096,6 +8301,12 @@
       </c>
       <c r="M196" s="25" t="str">
         <f aca="false">IF($A196="","",IF($K196&lt;=0,"Rupture",IF($K196&lt;=N($H196),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N196" s="26"/>
+      <c r="O196" s="26"/>
+      <c r="P196" s="24" t="str">
+        <f aca="false">IF($A196="","",IF($K196&lt;=N($H196),MAX(0,2*N($H196)-$K196),0))</f>
         <v/>
       </c>
     </row>
@@ -7109,7 +8320,7 @@
       <c r="G197" s="27"/>
       <c r="H197" s="27"/>
       <c r="I197" s="24" t="str">
-        <f aca="false">IF($A197="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A197,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A197="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A197,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A197))</f>
         <v/>
       </c>
       <c r="J197" s="24" t="str">
@@ -7126,6 +8337,12 @@
       </c>
       <c r="M197" s="25" t="str">
         <f aca="false">IF($A197="","",IF($K197&lt;=0,"Rupture",IF($K197&lt;=N($H197),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N197" s="26"/>
+      <c r="O197" s="26"/>
+      <c r="P197" s="24" t="str">
+        <f aca="false">IF($A197="","",IF($K197&lt;=N($H197),MAX(0,2*N($H197)-$K197),0))</f>
         <v/>
       </c>
     </row>
@@ -7139,7 +8356,7 @@
       <c r="G198" s="27"/>
       <c r="H198" s="27"/>
       <c r="I198" s="24" t="str">
-        <f aca="false">IF($A198="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A198,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A198="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A198,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A198))</f>
         <v/>
       </c>
       <c r="J198" s="24" t="str">
@@ -7156,6 +8373,12 @@
       </c>
       <c r="M198" s="25" t="str">
         <f aca="false">IF($A198="","",IF($K198&lt;=0,"Rupture",IF($K198&lt;=N($H198),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N198" s="26"/>
+      <c r="O198" s="26"/>
+      <c r="P198" s="24" t="str">
+        <f aca="false">IF($A198="","",IF($K198&lt;=N($H198),MAX(0,2*N($H198)-$K198),0))</f>
         <v/>
       </c>
     </row>
@@ -7169,7 +8392,7 @@
       <c r="G199" s="27"/>
       <c r="H199" s="27"/>
       <c r="I199" s="24" t="str">
-        <f aca="false">IF($A199="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A199,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A199="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A199,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A199))</f>
         <v/>
       </c>
       <c r="J199" s="24" t="str">
@@ -7186,6 +8409,12 @@
       </c>
       <c r="M199" s="25" t="str">
         <f aca="false">IF($A199="","",IF($K199&lt;=0,"Rupture",IF($K199&lt;=N($H199),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N199" s="26"/>
+      <c r="O199" s="26"/>
+      <c r="P199" s="24" t="str">
+        <f aca="false">IF($A199="","",IF($K199&lt;=N($H199),MAX(0,2*N($H199)-$K199),0))</f>
         <v/>
       </c>
     </row>
@@ -7199,7 +8428,7 @@
       <c r="G200" s="27"/>
       <c r="H200" s="27"/>
       <c r="I200" s="24" t="str">
-        <f aca="false">IF($A200="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A200,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A200="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A200,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A200))</f>
         <v/>
       </c>
       <c r="J200" s="24" t="str">
@@ -7216,6 +8445,12 @@
       </c>
       <c r="M200" s="25" t="str">
         <f aca="false">IF($A200="","",IF($K200&lt;=0,"Rupture",IF($K200&lt;=N($H200),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N200" s="26"/>
+      <c r="O200" s="26"/>
+      <c r="P200" s="24" t="str">
+        <f aca="false">IF($A200="","",IF($K200&lt;=N($H200),MAX(0,2*N($H200)-$K200),0))</f>
         <v/>
       </c>
     </row>
@@ -7229,7 +8464,7 @@
       <c r="G201" s="27"/>
       <c r="H201" s="27"/>
       <c r="I201" s="24" t="str">
-        <f aca="false">IF($A201="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A201,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A201="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A201,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A201))</f>
         <v/>
       </c>
       <c r="J201" s="24" t="str">
@@ -7246,6 +8481,12 @@
       </c>
       <c r="M201" s="25" t="str">
         <f aca="false">IF($A201="","",IF($K201&lt;=0,"Rupture",IF($K201&lt;=N($H201),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N201" s="26"/>
+      <c r="O201" s="26"/>
+      <c r="P201" s="24" t="str">
+        <f aca="false">IF($A201="","",IF($K201&lt;=N($H201),MAX(0,2*N($H201)-$K201),0))</f>
         <v/>
       </c>
     </row>
@@ -7259,7 +8500,7 @@
       <c r="G202" s="27"/>
       <c r="H202" s="27"/>
       <c r="I202" s="24" t="str">
-        <f aca="false">IF($A202="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A202,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A202="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A202,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A202))</f>
         <v/>
       </c>
       <c r="J202" s="24" t="str">
@@ -7276,6 +8517,12 @@
       </c>
       <c r="M202" s="25" t="str">
         <f aca="false">IF($A202="","",IF($K202&lt;=0,"Rupture",IF($K202&lt;=N($H202),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N202" s="26"/>
+      <c r="O202" s="26"/>
+      <c r="P202" s="24" t="str">
+        <f aca="false">IF($A202="","",IF($K202&lt;=N($H202),MAX(0,2*N($H202)-$K202),0))</f>
         <v/>
       </c>
     </row>
@@ -7289,7 +8536,7 @@
       <c r="G203" s="27"/>
       <c r="H203" s="27"/>
       <c r="I203" s="24" t="str">
-        <f aca="false">IF($A203="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A203,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A203="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A203,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A203))</f>
         <v/>
       </c>
       <c r="J203" s="24" t="str">
@@ -7306,6 +8553,12 @@
       </c>
       <c r="M203" s="25" t="str">
         <f aca="false">IF($A203="","",IF($K203&lt;=0,"Rupture",IF($K203&lt;=N($H203),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N203" s="26"/>
+      <c r="O203" s="26"/>
+      <c r="P203" s="24" t="str">
+        <f aca="false">IF($A203="","",IF($K203&lt;=N($H203),MAX(0,2*N($H203)-$K203),0))</f>
         <v/>
       </c>
     </row>
@@ -7319,7 +8572,7 @@
       <c r="G204" s="27"/>
       <c r="H204" s="27"/>
       <c r="I204" s="24" t="str">
-        <f aca="false">IF($A204="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A204,Mouvements!$D$5:$D$1004,"Entrée"))</f>
+        <f aca="false">IF($A204="","",SUMIFS(Mouvements!$E$5:$E$1004,Mouvements!$B$5:$B$1004,$A204,Mouvements!$D$5:$D$1004,"Entrée")+SUMIFS(Arrivages!$D$2:$D$5000,Arrivages!$B$2:$B$5000,$A204))</f>
         <v/>
       </c>
       <c r="J204" s="24" t="str">
@@ -7336,6 +8589,12 @@
       </c>
       <c r="M204" s="25" t="str">
         <f aca="false">IF($A204="","",IF($K204&lt;=0,"Rupture",IF($K204&lt;=N($H204),"À commander","OK")))</f>
+        <v/>
+      </c>
+      <c r="N204" s="26"/>
+      <c r="O204" s="26"/>
+      <c r="P204" s="24" t="str">
+        <f aca="false">IF($A204="","",IF($K204&lt;=N($H204),MAX(0,2*N($H204)-$K204),0))</f>
         <v/>
       </c>
     </row>
@@ -7389,40 +8648,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K1" s="21" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11645,6 +12904,3062 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1E7A46"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H301"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="28"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="28"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="28"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="28"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="28"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="28"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="28"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="28"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="28"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="28"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="28"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="28"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="28"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="28"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="28"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="28"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="28"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="28"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="29"/>
+      <c r="H73" s="29"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="28"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="29"/>
+      <c r="H74" s="29"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="28"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="29"/>
+      <c r="H75" s="29"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="28"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="28"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="29"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="28"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="29"/>
+      <c r="H78" s="29"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="28"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="29"/>
+      <c r="H79" s="29"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="28"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="28"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="29"/>
+      <c r="H81" s="29"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="28"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="28"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="28"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="28"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="28"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="29"/>
+      <c r="H86" s="29"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="28"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="29"/>
+      <c r="H87" s="29"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="28"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="29"/>
+      <c r="H88" s="29"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="28"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+      <c r="G89" s="29"/>
+      <c r="H89" s="29"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="28"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="29"/>
+      <c r="H90" s="29"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="28"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="29"/>
+      <c r="H91" s="29"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="28"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="29"/>
+      <c r="H92" s="29"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="28"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="29"/>
+      <c r="H93" s="29"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="28"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="29"/>
+      <c r="H94" s="29"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="28"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="29"/>
+      <c r="H95" s="29"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="28"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="28"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="28"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="28"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="28"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="29"/>
+      <c r="H100" s="29"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="28"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="29"/>
+      <c r="H101" s="29"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="28"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="29"/>
+      <c r="H102" s="29"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="28"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="29"/>
+      <c r="H103" s="29"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="28"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="29"/>
+      <c r="H104" s="29"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="28"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="29"/>
+      <c r="H105" s="29"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="28"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+      <c r="D106" s="30"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="29"/>
+      <c r="H106" s="29"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="28"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
+      <c r="D107" s="30"/>
+      <c r="E107" s="30"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="29"/>
+      <c r="H107" s="29"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="28"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="29"/>
+      <c r="D108" s="30"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="29"/>
+      <c r="H108" s="29"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="28"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="29"/>
+      <c r="D109" s="30"/>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="29"/>
+      <c r="H109" s="29"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="28"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
+      <c r="D110" s="30"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="29"/>
+      <c r="H110" s="29"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="28"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
+      <c r="D111" s="30"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="29"/>
+      <c r="H111" s="29"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="28"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="30"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="30"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="29"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="28"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="29"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="29"/>
+      <c r="H113" s="29"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="28"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="29"/>
+      <c r="D114" s="30"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="30"/>
+      <c r="G114" s="29"/>
+      <c r="H114" s="29"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="28"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
+      <c r="D115" s="30"/>
+      <c r="E115" s="30"/>
+      <c r="F115" s="30"/>
+      <c r="G115" s="29"/>
+      <c r="H115" s="29"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="28"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="29"/>
+      <c r="D116" s="30"/>
+      <c r="E116" s="30"/>
+      <c r="F116" s="30"/>
+      <c r="G116" s="29"/>
+      <c r="H116" s="29"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="28"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
+      <c r="D117" s="30"/>
+      <c r="E117" s="30"/>
+      <c r="F117" s="30"/>
+      <c r="G117" s="29"/>
+      <c r="H117" s="29"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="28"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="29"/>
+      <c r="H118" s="29"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="28"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
+      <c r="D119" s="30"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="30"/>
+      <c r="G119" s="29"/>
+      <c r="H119" s="29"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="28"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="29"/>
+      <c r="D120" s="30"/>
+      <c r="E120" s="30"/>
+      <c r="F120" s="30"/>
+      <c r="G120" s="29"/>
+      <c r="H120" s="29"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="28"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="29"/>
+      <c r="D121" s="30"/>
+      <c r="E121" s="30"/>
+      <c r="F121" s="30"/>
+      <c r="G121" s="29"/>
+      <c r="H121" s="29"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="28"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="29"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="30"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="29"/>
+      <c r="H122" s="29"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="28"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="29"/>
+      <c r="H123" s="29"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="28"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
+      <c r="D124" s="30"/>
+      <c r="E124" s="30"/>
+      <c r="F124" s="30"/>
+      <c r="G124" s="29"/>
+      <c r="H124" s="29"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="28"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="29"/>
+      <c r="D125" s="30"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="29"/>
+      <c r="H125" s="29"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="28"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
+      <c r="D126" s="30"/>
+      <c r="E126" s="30"/>
+      <c r="F126" s="30"/>
+      <c r="G126" s="29"/>
+      <c r="H126" s="29"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="28"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
+      <c r="D127" s="30"/>
+      <c r="E127" s="30"/>
+      <c r="F127" s="30"/>
+      <c r="G127" s="29"/>
+      <c r="H127" s="29"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="28"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="29"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="30"/>
+      <c r="G128" s="29"/>
+      <c r="H128" s="29"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="28"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="29"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="30"/>
+      <c r="F129" s="30"/>
+      <c r="G129" s="29"/>
+      <c r="H129" s="29"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="28"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="30"/>
+      <c r="F130" s="30"/>
+      <c r="G130" s="29"/>
+      <c r="H130" s="29"/>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="28"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="29"/>
+      <c r="D131" s="30"/>
+      <c r="E131" s="30"/>
+      <c r="F131" s="30"/>
+      <c r="G131" s="29"/>
+      <c r="H131" s="29"/>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="28"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
+      <c r="D132" s="30"/>
+      <c r="E132" s="30"/>
+      <c r="F132" s="30"/>
+      <c r="G132" s="29"/>
+      <c r="H132" s="29"/>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="28"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="29"/>
+      <c r="D133" s="30"/>
+      <c r="E133" s="30"/>
+      <c r="F133" s="30"/>
+      <c r="G133" s="29"/>
+      <c r="H133" s="29"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="28"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="29"/>
+      <c r="D134" s="30"/>
+      <c r="E134" s="30"/>
+      <c r="F134" s="30"/>
+      <c r="G134" s="29"/>
+      <c r="H134" s="29"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="28"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="29"/>
+      <c r="D135" s="30"/>
+      <c r="E135" s="30"/>
+      <c r="F135" s="30"/>
+      <c r="G135" s="29"/>
+      <c r="H135" s="29"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="28"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="30"/>
+      <c r="F136" s="30"/>
+      <c r="G136" s="29"/>
+      <c r="H136" s="29"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="28"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="29"/>
+      <c r="D137" s="30"/>
+      <c r="E137" s="30"/>
+      <c r="F137" s="30"/>
+      <c r="G137" s="29"/>
+      <c r="H137" s="29"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="28"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="29"/>
+      <c r="D138" s="30"/>
+      <c r="E138" s="30"/>
+      <c r="F138" s="30"/>
+      <c r="G138" s="29"/>
+      <c r="H138" s="29"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="28"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="29"/>
+      <c r="D139" s="30"/>
+      <c r="E139" s="30"/>
+      <c r="F139" s="30"/>
+      <c r="G139" s="29"/>
+      <c r="H139" s="29"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="28"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="29"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="30"/>
+      <c r="F140" s="30"/>
+      <c r="G140" s="29"/>
+      <c r="H140" s="29"/>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="28"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="29"/>
+      <c r="D141" s="30"/>
+      <c r="E141" s="30"/>
+      <c r="F141" s="30"/>
+      <c r="G141" s="29"/>
+      <c r="H141" s="29"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="28"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
+      <c r="D142" s="30"/>
+      <c r="E142" s="30"/>
+      <c r="F142" s="30"/>
+      <c r="G142" s="29"/>
+      <c r="H142" s="29"/>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="28"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="29"/>
+      <c r="D143" s="30"/>
+      <c r="E143" s="30"/>
+      <c r="F143" s="30"/>
+      <c r="G143" s="29"/>
+      <c r="H143" s="29"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="28"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="29"/>
+      <c r="D144" s="30"/>
+      <c r="E144" s="30"/>
+      <c r="F144" s="30"/>
+      <c r="G144" s="29"/>
+      <c r="H144" s="29"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="28"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="29"/>
+      <c r="D145" s="30"/>
+      <c r="E145" s="30"/>
+      <c r="F145" s="30"/>
+      <c r="G145" s="29"/>
+      <c r="H145" s="29"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="28"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="29"/>
+      <c r="D146" s="30"/>
+      <c r="E146" s="30"/>
+      <c r="F146" s="30"/>
+      <c r="G146" s="29"/>
+      <c r="H146" s="29"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="28"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="29"/>
+      <c r="D147" s="30"/>
+      <c r="E147" s="30"/>
+      <c r="F147" s="30"/>
+      <c r="G147" s="29"/>
+      <c r="H147" s="29"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="28"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
+      <c r="D148" s="30"/>
+      <c r="E148" s="30"/>
+      <c r="F148" s="30"/>
+      <c r="G148" s="29"/>
+      <c r="H148" s="29"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="28"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
+      <c r="D149" s="30"/>
+      <c r="E149" s="30"/>
+      <c r="F149" s="30"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="28"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="29"/>
+      <c r="D150" s="30"/>
+      <c r="E150" s="30"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="28"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="29"/>
+      <c r="D151" s="30"/>
+      <c r="E151" s="30"/>
+      <c r="F151" s="30"/>
+      <c r="G151" s="29"/>
+      <c r="H151" s="29"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="28"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="29"/>
+      <c r="D152" s="30"/>
+      <c r="E152" s="30"/>
+      <c r="F152" s="30"/>
+      <c r="G152" s="29"/>
+      <c r="H152" s="29"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="28"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="29"/>
+      <c r="D153" s="30"/>
+      <c r="E153" s="30"/>
+      <c r="F153" s="30"/>
+      <c r="G153" s="29"/>
+      <c r="H153" s="29"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="28"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
+      <c r="D154" s="30"/>
+      <c r="E154" s="30"/>
+      <c r="F154" s="30"/>
+      <c r="G154" s="29"/>
+      <c r="H154" s="29"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="28"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="29"/>
+      <c r="D155" s="30"/>
+      <c r="E155" s="30"/>
+      <c r="F155" s="30"/>
+      <c r="G155" s="29"/>
+      <c r="H155" s="29"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="28"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="29"/>
+      <c r="D156" s="30"/>
+      <c r="E156" s="30"/>
+      <c r="F156" s="30"/>
+      <c r="G156" s="29"/>
+      <c r="H156" s="29"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="28"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="29"/>
+      <c r="D157" s="30"/>
+      <c r="E157" s="30"/>
+      <c r="F157" s="30"/>
+      <c r="G157" s="29"/>
+      <c r="H157" s="29"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="28"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="29"/>
+      <c r="D158" s="30"/>
+      <c r="E158" s="30"/>
+      <c r="F158" s="30"/>
+      <c r="G158" s="29"/>
+      <c r="H158" s="29"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="28"/>
+      <c r="B159" s="29"/>
+      <c r="C159" s="29"/>
+      <c r="D159" s="30"/>
+      <c r="E159" s="30"/>
+      <c r="F159" s="30"/>
+      <c r="G159" s="29"/>
+      <c r="H159" s="29"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="28"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
+      <c r="D160" s="30"/>
+      <c r="E160" s="30"/>
+      <c r="F160" s="30"/>
+      <c r="G160" s="29"/>
+      <c r="H160" s="29"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="28"/>
+      <c r="B161" s="29"/>
+      <c r="C161" s="29"/>
+      <c r="D161" s="30"/>
+      <c r="E161" s="30"/>
+      <c r="F161" s="30"/>
+      <c r="G161" s="29"/>
+      <c r="H161" s="29"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="28"/>
+      <c r="B162" s="29"/>
+      <c r="C162" s="29"/>
+      <c r="D162" s="30"/>
+      <c r="E162" s="30"/>
+      <c r="F162" s="30"/>
+      <c r="G162" s="29"/>
+      <c r="H162" s="29"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="28"/>
+      <c r="B163" s="29"/>
+      <c r="C163" s="29"/>
+      <c r="D163" s="30"/>
+      <c r="E163" s="30"/>
+      <c r="F163" s="30"/>
+      <c r="G163" s="29"/>
+      <c r="H163" s="29"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="28"/>
+      <c r="B164" s="29"/>
+      <c r="C164" s="29"/>
+      <c r="D164" s="30"/>
+      <c r="E164" s="30"/>
+      <c r="F164" s="30"/>
+      <c r="G164" s="29"/>
+      <c r="H164" s="29"/>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="28"/>
+      <c r="B165" s="29"/>
+      <c r="C165" s="29"/>
+      <c r="D165" s="30"/>
+      <c r="E165" s="30"/>
+      <c r="F165" s="30"/>
+      <c r="G165" s="29"/>
+      <c r="H165" s="29"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="28"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
+      <c r="D166" s="30"/>
+      <c r="E166" s="30"/>
+      <c r="F166" s="30"/>
+      <c r="G166" s="29"/>
+      <c r="H166" s="29"/>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="28"/>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
+      <c r="D167" s="30"/>
+      <c r="E167" s="30"/>
+      <c r="F167" s="30"/>
+      <c r="G167" s="29"/>
+      <c r="H167" s="29"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="28"/>
+      <c r="B168" s="29"/>
+      <c r="C168" s="29"/>
+      <c r="D168" s="30"/>
+      <c r="E168" s="30"/>
+      <c r="F168" s="30"/>
+      <c r="G168" s="29"/>
+      <c r="H168" s="29"/>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="28"/>
+      <c r="B169" s="29"/>
+      <c r="C169" s="29"/>
+      <c r="D169" s="30"/>
+      <c r="E169" s="30"/>
+      <c r="F169" s="30"/>
+      <c r="G169" s="29"/>
+      <c r="H169" s="29"/>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="28"/>
+      <c r="B170" s="29"/>
+      <c r="C170" s="29"/>
+      <c r="D170" s="30"/>
+      <c r="E170" s="30"/>
+      <c r="F170" s="30"/>
+      <c r="G170" s="29"/>
+      <c r="H170" s="29"/>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="28"/>
+      <c r="B171" s="29"/>
+      <c r="C171" s="29"/>
+      <c r="D171" s="30"/>
+      <c r="E171" s="30"/>
+      <c r="F171" s="30"/>
+      <c r="G171" s="29"/>
+      <c r="H171" s="29"/>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="28"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
+      <c r="D172" s="30"/>
+      <c r="E172" s="30"/>
+      <c r="F172" s="30"/>
+      <c r="G172" s="29"/>
+      <c r="H172" s="29"/>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="28"/>
+      <c r="B173" s="29"/>
+      <c r="C173" s="29"/>
+      <c r="D173" s="30"/>
+      <c r="E173" s="30"/>
+      <c r="F173" s="30"/>
+      <c r="G173" s="29"/>
+      <c r="H173" s="29"/>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="28"/>
+      <c r="B174" s="29"/>
+      <c r="C174" s="29"/>
+      <c r="D174" s="30"/>
+      <c r="E174" s="30"/>
+      <c r="F174" s="30"/>
+      <c r="G174" s="29"/>
+      <c r="H174" s="29"/>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="28"/>
+      <c r="B175" s="29"/>
+      <c r="C175" s="29"/>
+      <c r="D175" s="30"/>
+      <c r="E175" s="30"/>
+      <c r="F175" s="30"/>
+      <c r="G175" s="29"/>
+      <c r="H175" s="29"/>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="28"/>
+      <c r="B176" s="29"/>
+      <c r="C176" s="29"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="28"/>
+      <c r="B177" s="29"/>
+      <c r="C177" s="29"/>
+      <c r="D177" s="30"/>
+      <c r="E177" s="30"/>
+      <c r="F177" s="30"/>
+      <c r="G177" s="29"/>
+      <c r="H177" s="29"/>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="28"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
+      <c r="D178" s="30"/>
+      <c r="E178" s="30"/>
+      <c r="F178" s="30"/>
+      <c r="G178" s="29"/>
+      <c r="H178" s="29"/>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="28"/>
+      <c r="B179" s="29"/>
+      <c r="C179" s="29"/>
+      <c r="D179" s="30"/>
+      <c r="E179" s="30"/>
+      <c r="F179" s="30"/>
+      <c r="G179" s="29"/>
+      <c r="H179" s="29"/>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="28"/>
+      <c r="B180" s="29"/>
+      <c r="C180" s="29"/>
+      <c r="D180" s="30"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="30"/>
+      <c r="G180" s="29"/>
+      <c r="H180" s="29"/>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="28"/>
+      <c r="B181" s="29"/>
+      <c r="C181" s="29"/>
+      <c r="D181" s="30"/>
+      <c r="E181" s="30"/>
+      <c r="F181" s="30"/>
+      <c r="G181" s="29"/>
+      <c r="H181" s="29"/>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="28"/>
+      <c r="B182" s="29"/>
+      <c r="C182" s="29"/>
+      <c r="D182" s="30"/>
+      <c r="E182" s="30"/>
+      <c r="F182" s="30"/>
+      <c r="G182" s="29"/>
+      <c r="H182" s="29"/>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="28"/>
+      <c r="B183" s="29"/>
+      <c r="C183" s="29"/>
+      <c r="D183" s="30"/>
+      <c r="E183" s="30"/>
+      <c r="F183" s="30"/>
+      <c r="G183" s="29"/>
+      <c r="H183" s="29"/>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="28"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
+      <c r="D184" s="30"/>
+      <c r="E184" s="30"/>
+      <c r="F184" s="30"/>
+      <c r="G184" s="29"/>
+      <c r="H184" s="29"/>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="28"/>
+      <c r="B185" s="29"/>
+      <c r="C185" s="29"/>
+      <c r="D185" s="30"/>
+      <c r="E185" s="30"/>
+      <c r="F185" s="30"/>
+      <c r="G185" s="29"/>
+      <c r="H185" s="29"/>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="28"/>
+      <c r="B186" s="29"/>
+      <c r="C186" s="29"/>
+      <c r="D186" s="30"/>
+      <c r="E186" s="30"/>
+      <c r="F186" s="30"/>
+      <c r="G186" s="29"/>
+      <c r="H186" s="29"/>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="28"/>
+      <c r="B187" s="29"/>
+      <c r="C187" s="29"/>
+      <c r="D187" s="30"/>
+      <c r="E187" s="30"/>
+      <c r="F187" s="30"/>
+      <c r="G187" s="29"/>
+      <c r="H187" s="29"/>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="28"/>
+      <c r="B188" s="29"/>
+      <c r="C188" s="29"/>
+      <c r="D188" s="30"/>
+      <c r="E188" s="30"/>
+      <c r="F188" s="30"/>
+      <c r="G188" s="29"/>
+      <c r="H188" s="29"/>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="28"/>
+      <c r="B189" s="29"/>
+      <c r="C189" s="29"/>
+      <c r="D189" s="30"/>
+      <c r="E189" s="30"/>
+      <c r="F189" s="30"/>
+      <c r="G189" s="29"/>
+      <c r="H189" s="29"/>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="28"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
+      <c r="D190" s="30"/>
+      <c r="E190" s="30"/>
+      <c r="F190" s="30"/>
+      <c r="G190" s="29"/>
+      <c r="H190" s="29"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="28"/>
+      <c r="B191" s="29"/>
+      <c r="C191" s="29"/>
+      <c r="D191" s="30"/>
+      <c r="E191" s="30"/>
+      <c r="F191" s="30"/>
+      <c r="G191" s="29"/>
+      <c r="H191" s="29"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="28"/>
+      <c r="B192" s="29"/>
+      <c r="C192" s="29"/>
+      <c r="D192" s="30"/>
+      <c r="E192" s="30"/>
+      <c r="F192" s="30"/>
+      <c r="G192" s="29"/>
+      <c r="H192" s="29"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="28"/>
+      <c r="B193" s="29"/>
+      <c r="C193" s="29"/>
+      <c r="D193" s="30"/>
+      <c r="E193" s="30"/>
+      <c r="F193" s="30"/>
+      <c r="G193" s="29"/>
+      <c r="H193" s="29"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="28"/>
+      <c r="B194" s="29"/>
+      <c r="C194" s="29"/>
+      <c r="D194" s="30"/>
+      <c r="E194" s="30"/>
+      <c r="F194" s="30"/>
+      <c r="G194" s="29"/>
+      <c r="H194" s="29"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="28"/>
+      <c r="B195" s="29"/>
+      <c r="C195" s="29"/>
+      <c r="D195" s="30"/>
+      <c r="E195" s="30"/>
+      <c r="F195" s="30"/>
+      <c r="G195" s="29"/>
+      <c r="H195" s="29"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="28"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
+      <c r="D196" s="30"/>
+      <c r="E196" s="30"/>
+      <c r="F196" s="30"/>
+      <c r="G196" s="29"/>
+      <c r="H196" s="29"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="28"/>
+      <c r="B197" s="29"/>
+      <c r="C197" s="29"/>
+      <c r="D197" s="30"/>
+      <c r="E197" s="30"/>
+      <c r="F197" s="30"/>
+      <c r="G197" s="29"/>
+      <c r="H197" s="29"/>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="28"/>
+      <c r="B198" s="29"/>
+      <c r="C198" s="29"/>
+      <c r="D198" s="30"/>
+      <c r="E198" s="30"/>
+      <c r="F198" s="30"/>
+      <c r="G198" s="29"/>
+      <c r="H198" s="29"/>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="28"/>
+      <c r="B199" s="29"/>
+      <c r="C199" s="29"/>
+      <c r="D199" s="30"/>
+      <c r="E199" s="30"/>
+      <c r="F199" s="30"/>
+      <c r="G199" s="29"/>
+      <c r="H199" s="29"/>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="28"/>
+      <c r="B200" s="29"/>
+      <c r="C200" s="29"/>
+      <c r="D200" s="30"/>
+      <c r="E200" s="30"/>
+      <c r="F200" s="30"/>
+      <c r="G200" s="29"/>
+      <c r="H200" s="29"/>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="28"/>
+      <c r="B201" s="29"/>
+      <c r="C201" s="29"/>
+      <c r="D201" s="30"/>
+      <c r="E201" s="30"/>
+      <c r="F201" s="30"/>
+      <c r="G201" s="29"/>
+      <c r="H201" s="29"/>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="28"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30"/>
+      <c r="F202" s="30"/>
+      <c r="G202" s="29"/>
+      <c r="H202" s="29"/>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="28"/>
+      <c r="B203" s="29"/>
+      <c r="C203" s="29"/>
+      <c r="D203" s="30"/>
+      <c r="E203" s="30"/>
+      <c r="F203" s="30"/>
+      <c r="G203" s="29"/>
+      <c r="H203" s="29"/>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="28"/>
+      <c r="B204" s="29"/>
+      <c r="C204" s="29"/>
+      <c r="D204" s="30"/>
+      <c r="E204" s="30"/>
+      <c r="F204" s="30"/>
+      <c r="G204" s="29"/>
+      <c r="H204" s="29"/>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="28"/>
+      <c r="B205" s="29"/>
+      <c r="C205" s="29"/>
+      <c r="D205" s="30"/>
+      <c r="E205" s="30"/>
+      <c r="F205" s="30"/>
+      <c r="G205" s="29"/>
+      <c r="H205" s="29"/>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="28"/>
+      <c r="B206" s="29"/>
+      <c r="C206" s="29"/>
+      <c r="D206" s="30"/>
+      <c r="E206" s="30"/>
+      <c r="F206" s="30"/>
+      <c r="G206" s="29"/>
+      <c r="H206" s="29"/>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="28"/>
+      <c r="B207" s="29"/>
+      <c r="C207" s="29"/>
+      <c r="D207" s="30"/>
+      <c r="E207" s="30"/>
+      <c r="F207" s="30"/>
+      <c r="G207" s="29"/>
+      <c r="H207" s="29"/>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="28"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
+      <c r="D208" s="30"/>
+      <c r="E208" s="30"/>
+      <c r="F208" s="30"/>
+      <c r="G208" s="29"/>
+      <c r="H208" s="29"/>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="28"/>
+      <c r="B209" s="29"/>
+      <c r="C209" s="29"/>
+      <c r="D209" s="30"/>
+      <c r="E209" s="30"/>
+      <c r="F209" s="30"/>
+      <c r="G209" s="29"/>
+      <c r="H209" s="29"/>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="28"/>
+      <c r="B210" s="29"/>
+      <c r="C210" s="29"/>
+      <c r="D210" s="30"/>
+      <c r="E210" s="30"/>
+      <c r="F210" s="30"/>
+      <c r="G210" s="29"/>
+      <c r="H210" s="29"/>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="28"/>
+      <c r="B211" s="29"/>
+      <c r="C211" s="29"/>
+      <c r="D211" s="30"/>
+      <c r="E211" s="30"/>
+      <c r="F211" s="30"/>
+      <c r="G211" s="29"/>
+      <c r="H211" s="29"/>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="28"/>
+      <c r="B212" s="29"/>
+      <c r="C212" s="29"/>
+      <c r="D212" s="30"/>
+      <c r="E212" s="30"/>
+      <c r="F212" s="30"/>
+      <c r="G212" s="29"/>
+      <c r="H212" s="29"/>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="28"/>
+      <c r="B213" s="29"/>
+      <c r="C213" s="29"/>
+      <c r="D213" s="30"/>
+      <c r="E213" s="30"/>
+      <c r="F213" s="30"/>
+      <c r="G213" s="29"/>
+      <c r="H213" s="29"/>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="28"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
+      <c r="D214" s="30"/>
+      <c r="E214" s="30"/>
+      <c r="F214" s="30"/>
+      <c r="G214" s="29"/>
+      <c r="H214" s="29"/>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="28"/>
+      <c r="B215" s="29"/>
+      <c r="C215" s="29"/>
+      <c r="D215" s="30"/>
+      <c r="E215" s="30"/>
+      <c r="F215" s="30"/>
+      <c r="G215" s="29"/>
+      <c r="H215" s="29"/>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="28"/>
+      <c r="B216" s="29"/>
+      <c r="C216" s="29"/>
+      <c r="D216" s="30"/>
+      <c r="E216" s="30"/>
+      <c r="F216" s="30"/>
+      <c r="G216" s="29"/>
+      <c r="H216" s="29"/>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="28"/>
+      <c r="B217" s="29"/>
+      <c r="C217" s="29"/>
+      <c r="D217" s="30"/>
+      <c r="E217" s="30"/>
+      <c r="F217" s="30"/>
+      <c r="G217" s="29"/>
+      <c r="H217" s="29"/>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="28"/>
+      <c r="B218" s="29"/>
+      <c r="C218" s="29"/>
+      <c r="D218" s="30"/>
+      <c r="E218" s="30"/>
+      <c r="F218" s="30"/>
+      <c r="G218" s="29"/>
+      <c r="H218" s="29"/>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="28"/>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29"/>
+      <c r="D219" s="30"/>
+      <c r="E219" s="30"/>
+      <c r="F219" s="30"/>
+      <c r="G219" s="29"/>
+      <c r="H219" s="29"/>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="28"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
+      <c r="D220" s="30"/>
+      <c r="E220" s="30"/>
+      <c r="F220" s="30"/>
+      <c r="G220" s="29"/>
+      <c r="H220" s="29"/>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="28"/>
+      <c r="B221" s="29"/>
+      <c r="C221" s="29"/>
+      <c r="D221" s="30"/>
+      <c r="E221" s="30"/>
+      <c r="F221" s="30"/>
+      <c r="G221" s="29"/>
+      <c r="H221" s="29"/>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="28"/>
+      <c r="B222" s="29"/>
+      <c r="C222" s="29"/>
+      <c r="D222" s="30"/>
+      <c r="E222" s="30"/>
+      <c r="F222" s="30"/>
+      <c r="G222" s="29"/>
+      <c r="H222" s="29"/>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="28"/>
+      <c r="B223" s="29"/>
+      <c r="C223" s="29"/>
+      <c r="D223" s="30"/>
+      <c r="E223" s="30"/>
+      <c r="F223" s="30"/>
+      <c r="G223" s="29"/>
+      <c r="H223" s="29"/>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="28"/>
+      <c r="B224" s="29"/>
+      <c r="C224" s="29"/>
+      <c r="D224" s="30"/>
+      <c r="E224" s="30"/>
+      <c r="F224" s="30"/>
+      <c r="G224" s="29"/>
+      <c r="H224" s="29"/>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="28"/>
+      <c r="B225" s="29"/>
+      <c r="C225" s="29"/>
+      <c r="D225" s="30"/>
+      <c r="E225" s="30"/>
+      <c r="F225" s="30"/>
+      <c r="G225" s="29"/>
+      <c r="H225" s="29"/>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="28"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
+      <c r="D226" s="30"/>
+      <c r="E226" s="30"/>
+      <c r="F226" s="30"/>
+      <c r="G226" s="29"/>
+      <c r="H226" s="29"/>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="28"/>
+      <c r="B227" s="29"/>
+      <c r="C227" s="29"/>
+      <c r="D227" s="30"/>
+      <c r="E227" s="30"/>
+      <c r="F227" s="30"/>
+      <c r="G227" s="29"/>
+      <c r="H227" s="29"/>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="28"/>
+      <c r="B228" s="29"/>
+      <c r="C228" s="29"/>
+      <c r="D228" s="30"/>
+      <c r="E228" s="30"/>
+      <c r="F228" s="30"/>
+      <c r="G228" s="29"/>
+      <c r="H228" s="29"/>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="28"/>
+      <c r="B229" s="29"/>
+      <c r="C229" s="29"/>
+      <c r="D229" s="30"/>
+      <c r="E229" s="30"/>
+      <c r="F229" s="30"/>
+      <c r="G229" s="29"/>
+      <c r="H229" s="29"/>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="28"/>
+      <c r="B230" s="29"/>
+      <c r="C230" s="29"/>
+      <c r="D230" s="30"/>
+      <c r="E230" s="30"/>
+      <c r="F230" s="30"/>
+      <c r="G230" s="29"/>
+      <c r="H230" s="29"/>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="28"/>
+      <c r="B231" s="29"/>
+      <c r="C231" s="29"/>
+      <c r="D231" s="30"/>
+      <c r="E231" s="30"/>
+      <c r="F231" s="30"/>
+      <c r="G231" s="29"/>
+      <c r="H231" s="29"/>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="28"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
+      <c r="D232" s="30"/>
+      <c r="E232" s="30"/>
+      <c r="F232" s="30"/>
+      <c r="G232" s="29"/>
+      <c r="H232" s="29"/>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="28"/>
+      <c r="B233" s="29"/>
+      <c r="C233" s="29"/>
+      <c r="D233" s="30"/>
+      <c r="E233" s="30"/>
+      <c r="F233" s="30"/>
+      <c r="G233" s="29"/>
+      <c r="H233" s="29"/>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="28"/>
+      <c r="B234" s="29"/>
+      <c r="C234" s="29"/>
+      <c r="D234" s="30"/>
+      <c r="E234" s="30"/>
+      <c r="F234" s="30"/>
+      <c r="G234" s="29"/>
+      <c r="H234" s="29"/>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="28"/>
+      <c r="B235" s="29"/>
+      <c r="C235" s="29"/>
+      <c r="D235" s="30"/>
+      <c r="E235" s="30"/>
+      <c r="F235" s="30"/>
+      <c r="G235" s="29"/>
+      <c r="H235" s="29"/>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="28"/>
+      <c r="B236" s="29"/>
+      <c r="C236" s="29"/>
+      <c r="D236" s="30"/>
+      <c r="E236" s="30"/>
+      <c r="F236" s="30"/>
+      <c r="G236" s="29"/>
+      <c r="H236" s="29"/>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="28"/>
+      <c r="B237" s="29"/>
+      <c r="C237" s="29"/>
+      <c r="D237" s="30"/>
+      <c r="E237" s="30"/>
+      <c r="F237" s="30"/>
+      <c r="G237" s="29"/>
+      <c r="H237" s="29"/>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="28"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
+      <c r="D238" s="30"/>
+      <c r="E238" s="30"/>
+      <c r="F238" s="30"/>
+      <c r="G238" s="29"/>
+      <c r="H238" s="29"/>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="28"/>
+      <c r="B239" s="29"/>
+      <c r="C239" s="29"/>
+      <c r="D239" s="30"/>
+      <c r="E239" s="30"/>
+      <c r="F239" s="30"/>
+      <c r="G239" s="29"/>
+      <c r="H239" s="29"/>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="28"/>
+      <c r="B240" s="29"/>
+      <c r="C240" s="29"/>
+      <c r="D240" s="30"/>
+      <c r="E240" s="30"/>
+      <c r="F240" s="30"/>
+      <c r="G240" s="29"/>
+      <c r="H240" s="29"/>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="28"/>
+      <c r="B241" s="29"/>
+      <c r="C241" s="29"/>
+      <c r="D241" s="30"/>
+      <c r="E241" s="30"/>
+      <c r="F241" s="30"/>
+      <c r="G241" s="29"/>
+      <c r="H241" s="29"/>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="28"/>
+      <c r="B242" s="29"/>
+      <c r="C242" s="29"/>
+      <c r="D242" s="30"/>
+      <c r="E242" s="30"/>
+      <c r="F242" s="30"/>
+      <c r="G242" s="29"/>
+      <c r="H242" s="29"/>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="28"/>
+      <c r="B243" s="29"/>
+      <c r="C243" s="29"/>
+      <c r="D243" s="30"/>
+      <c r="E243" s="30"/>
+      <c r="F243" s="30"/>
+      <c r="G243" s="29"/>
+      <c r="H243" s="29"/>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="28"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
+      <c r="D244" s="30"/>
+      <c r="E244" s="30"/>
+      <c r="F244" s="30"/>
+      <c r="G244" s="29"/>
+      <c r="H244" s="29"/>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="28"/>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29"/>
+      <c r="D245" s="30"/>
+      <c r="E245" s="30"/>
+      <c r="F245" s="30"/>
+      <c r="G245" s="29"/>
+      <c r="H245" s="29"/>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="28"/>
+      <c r="B246" s="29"/>
+      <c r="C246" s="29"/>
+      <c r="D246" s="30"/>
+      <c r="E246" s="30"/>
+      <c r="F246" s="30"/>
+      <c r="G246" s="29"/>
+      <c r="H246" s="29"/>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="28"/>
+      <c r="B247" s="29"/>
+      <c r="C247" s="29"/>
+      <c r="D247" s="30"/>
+      <c r="E247" s="30"/>
+      <c r="F247" s="30"/>
+      <c r="G247" s="29"/>
+      <c r="H247" s="29"/>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="28"/>
+      <c r="B248" s="29"/>
+      <c r="C248" s="29"/>
+      <c r="D248" s="30"/>
+      <c r="E248" s="30"/>
+      <c r="F248" s="30"/>
+      <c r="G248" s="29"/>
+      <c r="H248" s="29"/>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="28"/>
+      <c r="B249" s="29"/>
+      <c r="C249" s="29"/>
+      <c r="D249" s="30"/>
+      <c r="E249" s="30"/>
+      <c r="F249" s="30"/>
+      <c r="G249" s="29"/>
+      <c r="H249" s="29"/>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="28"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
+      <c r="D250" s="30"/>
+      <c r="E250" s="30"/>
+      <c r="F250" s="30"/>
+      <c r="G250" s="29"/>
+      <c r="H250" s="29"/>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="28"/>
+      <c r="B251" s="29"/>
+      <c r="C251" s="29"/>
+      <c r="D251" s="30"/>
+      <c r="E251" s="30"/>
+      <c r="F251" s="30"/>
+      <c r="G251" s="29"/>
+      <c r="H251" s="29"/>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="28"/>
+      <c r="B252" s="29"/>
+      <c r="C252" s="29"/>
+      <c r="D252" s="30"/>
+      <c r="E252" s="30"/>
+      <c r="F252" s="30"/>
+      <c r="G252" s="29"/>
+      <c r="H252" s="29"/>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="28"/>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29"/>
+      <c r="D253" s="30"/>
+      <c r="E253" s="30"/>
+      <c r="F253" s="30"/>
+      <c r="G253" s="29"/>
+      <c r="H253" s="29"/>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="28"/>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
+      <c r="D254" s="30"/>
+      <c r="E254" s="30"/>
+      <c r="F254" s="30"/>
+      <c r="G254" s="29"/>
+      <c r="H254" s="29"/>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="28"/>
+      <c r="B255" s="29"/>
+      <c r="C255" s="29"/>
+      <c r="D255" s="30"/>
+      <c r="E255" s="30"/>
+      <c r="F255" s="30"/>
+      <c r="G255" s="29"/>
+      <c r="H255" s="29"/>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="28"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
+      <c r="D256" s="30"/>
+      <c r="E256" s="30"/>
+      <c r="F256" s="30"/>
+      <c r="G256" s="29"/>
+      <c r="H256" s="29"/>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="28"/>
+      <c r="B257" s="29"/>
+      <c r="C257" s="29"/>
+      <c r="D257" s="30"/>
+      <c r="E257" s="30"/>
+      <c r="F257" s="30"/>
+      <c r="G257" s="29"/>
+      <c r="H257" s="29"/>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="28"/>
+      <c r="B258" s="29"/>
+      <c r="C258" s="29"/>
+      <c r="D258" s="30"/>
+      <c r="E258" s="30"/>
+      <c r="F258" s="30"/>
+      <c r="G258" s="29"/>
+      <c r="H258" s="29"/>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="28"/>
+      <c r="B259" s="29"/>
+      <c r="C259" s="29"/>
+      <c r="D259" s="30"/>
+      <c r="E259" s="30"/>
+      <c r="F259" s="30"/>
+      <c r="G259" s="29"/>
+      <c r="H259" s="29"/>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="28"/>
+      <c r="B260" s="29"/>
+      <c r="C260" s="29"/>
+      <c r="D260" s="30"/>
+      <c r="E260" s="30"/>
+      <c r="F260" s="30"/>
+      <c r="G260" s="29"/>
+      <c r="H260" s="29"/>
+    </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="28"/>
+      <c r="B261" s="29"/>
+      <c r="C261" s="29"/>
+      <c r="D261" s="30"/>
+      <c r="E261" s="30"/>
+      <c r="F261" s="30"/>
+      <c r="G261" s="29"/>
+      <c r="H261" s="29"/>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="28"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
+      <c r="D262" s="30"/>
+      <c r="E262" s="30"/>
+      <c r="F262" s="30"/>
+      <c r="G262" s="29"/>
+      <c r="H262" s="29"/>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="28"/>
+      <c r="B263" s="29"/>
+      <c r="C263" s="29"/>
+      <c r="D263" s="30"/>
+      <c r="E263" s="30"/>
+      <c r="F263" s="30"/>
+      <c r="G263" s="29"/>
+      <c r="H263" s="29"/>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="28"/>
+      <c r="B264" s="29"/>
+      <c r="C264" s="29"/>
+      <c r="D264" s="30"/>
+      <c r="E264" s="30"/>
+      <c r="F264" s="30"/>
+      <c r="G264" s="29"/>
+      <c r="H264" s="29"/>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="28"/>
+      <c r="B265" s="29"/>
+      <c r="C265" s="29"/>
+      <c r="D265" s="30"/>
+      <c r="E265" s="30"/>
+      <c r="F265" s="30"/>
+      <c r="G265" s="29"/>
+      <c r="H265" s="29"/>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="28"/>
+      <c r="B266" s="29"/>
+      <c r="C266" s="29"/>
+      <c r="D266" s="30"/>
+      <c r="E266" s="30"/>
+      <c r="F266" s="30"/>
+      <c r="G266" s="29"/>
+      <c r="H266" s="29"/>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="28"/>
+      <c r="B267" s="29"/>
+      <c r="C267" s="29"/>
+      <c r="D267" s="30"/>
+      <c r="E267" s="30"/>
+      <c r="F267" s="30"/>
+      <c r="G267" s="29"/>
+      <c r="H267" s="29"/>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="28"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
+      <c r="D268" s="30"/>
+      <c r="E268" s="30"/>
+      <c r="F268" s="30"/>
+      <c r="G268" s="29"/>
+      <c r="H268" s="29"/>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="28"/>
+      <c r="B269" s="29"/>
+      <c r="C269" s="29"/>
+      <c r="D269" s="30"/>
+      <c r="E269" s="30"/>
+      <c r="F269" s="30"/>
+      <c r="G269" s="29"/>
+      <c r="H269" s="29"/>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="28"/>
+      <c r="B270" s="29"/>
+      <c r="C270" s="29"/>
+      <c r="D270" s="30"/>
+      <c r="E270" s="30"/>
+      <c r="F270" s="30"/>
+      <c r="G270" s="29"/>
+      <c r="H270" s="29"/>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="28"/>
+      <c r="B271" s="29"/>
+      <c r="C271" s="29"/>
+      <c r="D271" s="30"/>
+      <c r="E271" s="30"/>
+      <c r="F271" s="30"/>
+      <c r="G271" s="29"/>
+      <c r="H271" s="29"/>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="28"/>
+      <c r="B272" s="29"/>
+      <c r="C272" s="29"/>
+      <c r="D272" s="30"/>
+      <c r="E272" s="30"/>
+      <c r="F272" s="30"/>
+      <c r="G272" s="29"/>
+      <c r="H272" s="29"/>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="28"/>
+      <c r="B273" s="29"/>
+      <c r="C273" s="29"/>
+      <c r="D273" s="30"/>
+      <c r="E273" s="30"/>
+      <c r="F273" s="30"/>
+      <c r="G273" s="29"/>
+      <c r="H273" s="29"/>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="28"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
+      <c r="D274" s="30"/>
+      <c r="E274" s="30"/>
+      <c r="F274" s="30"/>
+      <c r="G274" s="29"/>
+      <c r="H274" s="29"/>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="28"/>
+      <c r="B275" s="29"/>
+      <c r="C275" s="29"/>
+      <c r="D275" s="30"/>
+      <c r="E275" s="30"/>
+      <c r="F275" s="30"/>
+      <c r="G275" s="29"/>
+      <c r="H275" s="29"/>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="28"/>
+      <c r="B276" s="29"/>
+      <c r="C276" s="29"/>
+      <c r="D276" s="30"/>
+      <c r="E276" s="30"/>
+      <c r="F276" s="30"/>
+      <c r="G276" s="29"/>
+      <c r="H276" s="29"/>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="28"/>
+      <c r="B277" s="29"/>
+      <c r="C277" s="29"/>
+      <c r="D277" s="30"/>
+      <c r="E277" s="30"/>
+      <c r="F277" s="30"/>
+      <c r="G277" s="29"/>
+      <c r="H277" s="29"/>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="28"/>
+      <c r="B278" s="29"/>
+      <c r="C278" s="29"/>
+      <c r="D278" s="30"/>
+      <c r="E278" s="30"/>
+      <c r="F278" s="30"/>
+      <c r="G278" s="29"/>
+      <c r="H278" s="29"/>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="28"/>
+      <c r="B279" s="29"/>
+      <c r="C279" s="29"/>
+      <c r="D279" s="30"/>
+      <c r="E279" s="30"/>
+      <c r="F279" s="30"/>
+      <c r="G279" s="29"/>
+      <c r="H279" s="29"/>
+    </row>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="28"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
+      <c r="D280" s="30"/>
+      <c r="E280" s="30"/>
+      <c r="F280" s="30"/>
+      <c r="G280" s="29"/>
+      <c r="H280" s="29"/>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="28"/>
+      <c r="B281" s="29"/>
+      <c r="C281" s="29"/>
+      <c r="D281" s="30"/>
+      <c r="E281" s="30"/>
+      <c r="F281" s="30"/>
+      <c r="G281" s="29"/>
+      <c r="H281" s="29"/>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="28"/>
+      <c r="B282" s="29"/>
+      <c r="C282" s="29"/>
+      <c r="D282" s="30"/>
+      <c r="E282" s="30"/>
+      <c r="F282" s="30"/>
+      <c r="G282" s="29"/>
+      <c r="H282" s="29"/>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="28"/>
+      <c r="B283" s="29"/>
+      <c r="C283" s="29"/>
+      <c r="D283" s="30"/>
+      <c r="E283" s="30"/>
+      <c r="F283" s="30"/>
+      <c r="G283" s="29"/>
+      <c r="H283" s="29"/>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="28"/>
+      <c r="B284" s="29"/>
+      <c r="C284" s="29"/>
+      <c r="D284" s="30"/>
+      <c r="E284" s="30"/>
+      <c r="F284" s="30"/>
+      <c r="G284" s="29"/>
+      <c r="H284" s="29"/>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="28"/>
+      <c r="B285" s="29"/>
+      <c r="C285" s="29"/>
+      <c r="D285" s="30"/>
+      <c r="E285" s="30"/>
+      <c r="F285" s="30"/>
+      <c r="G285" s="29"/>
+      <c r="H285" s="29"/>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="28"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
+      <c r="D286" s="30"/>
+      <c r="E286" s="30"/>
+      <c r="F286" s="30"/>
+      <c r="G286" s="29"/>
+      <c r="H286" s="29"/>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="28"/>
+      <c r="B287" s="29"/>
+      <c r="C287" s="29"/>
+      <c r="D287" s="30"/>
+      <c r="E287" s="30"/>
+      <c r="F287" s="30"/>
+      <c r="G287" s="29"/>
+      <c r="H287" s="29"/>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="28"/>
+      <c r="B288" s="29"/>
+      <c r="C288" s="29"/>
+      <c r="D288" s="30"/>
+      <c r="E288" s="30"/>
+      <c r="F288" s="30"/>
+      <c r="G288" s="29"/>
+      <c r="H288" s="29"/>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="28"/>
+      <c r="B289" s="29"/>
+      <c r="C289" s="29"/>
+      <c r="D289" s="30"/>
+      <c r="E289" s="30"/>
+      <c r="F289" s="30"/>
+      <c r="G289" s="29"/>
+      <c r="H289" s="29"/>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="28"/>
+      <c r="B290" s="29"/>
+      <c r="C290" s="29"/>
+      <c r="D290" s="30"/>
+      <c r="E290" s="30"/>
+      <c r="F290" s="30"/>
+      <c r="G290" s="29"/>
+      <c r="H290" s="29"/>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="28"/>
+      <c r="B291" s="29"/>
+      <c r="C291" s="29"/>
+      <c r="D291" s="30"/>
+      <c r="E291" s="30"/>
+      <c r="F291" s="30"/>
+      <c r="G291" s="29"/>
+      <c r="H291" s="29"/>
+    </row>
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="28"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
+      <c r="D292" s="30"/>
+      <c r="E292" s="30"/>
+      <c r="F292" s="30"/>
+      <c r="G292" s="29"/>
+      <c r="H292" s="29"/>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="28"/>
+      <c r="B293" s="29"/>
+      <c r="C293" s="29"/>
+      <c r="D293" s="30"/>
+      <c r="E293" s="30"/>
+      <c r="F293" s="30"/>
+      <c r="G293" s="29"/>
+      <c r="H293" s="29"/>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="28"/>
+      <c r="B294" s="29"/>
+      <c r="C294" s="29"/>
+      <c r="D294" s="30"/>
+      <c r="E294" s="30"/>
+      <c r="F294" s="30"/>
+      <c r="G294" s="29"/>
+      <c r="H294" s="29"/>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="28"/>
+      <c r="B295" s="29"/>
+      <c r="C295" s="29"/>
+      <c r="D295" s="30"/>
+      <c r="E295" s="30"/>
+      <c r="F295" s="30"/>
+      <c r="G295" s="29"/>
+      <c r="H295" s="29"/>
+    </row>
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="28"/>
+      <c r="B296" s="29"/>
+      <c r="C296" s="29"/>
+      <c r="D296" s="30"/>
+      <c r="E296" s="30"/>
+      <c r="F296" s="30"/>
+      <c r="G296" s="29"/>
+      <c r="H296" s="29"/>
+    </row>
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="28"/>
+      <c r="B297" s="29"/>
+      <c r="C297" s="29"/>
+      <c r="D297" s="30"/>
+      <c r="E297" s="30"/>
+      <c r="F297" s="30"/>
+      <c r="G297" s="29"/>
+      <c r="H297" s="29"/>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="28"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
+      <c r="D298" s="30"/>
+      <c r="E298" s="30"/>
+      <c r="F298" s="30"/>
+      <c r="G298" s="29"/>
+      <c r="H298" s="29"/>
+    </row>
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="28"/>
+      <c r="B299" s="29"/>
+      <c r="C299" s="29"/>
+      <c r="D299" s="30"/>
+      <c r="E299" s="30"/>
+      <c r="F299" s="30"/>
+      <c r="G299" s="29"/>
+      <c r="H299" s="29"/>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="28"/>
+      <c r="B300" s="29"/>
+      <c r="C300" s="29"/>
+      <c r="D300" s="30"/>
+      <c r="E300" s="30"/>
+      <c r="F300" s="30"/>
+      <c r="G300" s="29"/>
+      <c r="H300" s="29"/>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="28"/>
+      <c r="B301" s="29"/>
+      <c r="C301" s="29"/>
+      <c r="D301" s="30"/>
+      <c r="E301" s="30"/>
+      <c r="F301" s="30"/>
+      <c r="G301" s="29"/>
+      <c r="H301" s="29"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I1004"/>
@@ -11662,56 +15977,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>67</v>
-      </c>
       <c r="G4" s="21" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="n">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C5" s="32" t="str">
         <f aca="false">IF($B5="","",IFERROR(INDEX(Produits!$B$5:$B$204,MATCH($B5,Produits!$A$5:$A$204,0)),"Code inconnu"))</f>
         <v>EXEMPLE - Riz 25 kg</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>10</v>
@@ -11729,22 +16044,22 @@
         <v/>
       </c>
       <c r="I5" s="22" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="n">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C6" s="32" t="str">
         <f aca="false">IF($B6="","",IFERROR(INDEX(Produits!$B$5:$B$204,MATCH($B6,Produits!$A$5:$A$204,0)),"Code inconnu"))</f>
         <v>EXEMPLE - Riz 25 kg</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>4</v>
@@ -11762,22 +16077,22 @@
         <v>120</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="n">
-        <v>46301</v>
+        <v>46306</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C7" s="32" t="str">
         <f aca="false">IF($B7="","",IFERROR(INDEX(Produits!$B$5:$B$204,MATCH($B7,Produits!$A$5:$A$204,0)),"Code inconnu"))</f>
         <v>EXEMPLE - Huile 5 L</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>7</v>
@@ -11795,7 +16110,7 @@
         <v>84</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
